--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Static" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Take Over Time" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -160,6 +161,33 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -222,7 +250,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -253,12 +281,56 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -378,6 +450,47 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,6 +568,510 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Role share of the take over time (%)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$8:$V$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$9:$V$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$10:$V$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$11:$V$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$12:$V$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$16:$V$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$17:$V$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$18:$V$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$19:$V$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Take Over Time'!A20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take Over Time'!$B$6:$V$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take Over Time'!$B$20:$V$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of take</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -479,6 +1096,33 @@
     </comment>
   </commentList>
 </comments>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,6 +1491,10 @@
           <t>Performance-fee rate (of profits)</t>
         </is>
       </c>
+      <c r="B5" s="59" t="n"/>
+      <c r="C5" s="59" t="n"/>
+      <c r="D5" s="59" t="n"/>
+      <c r="E5" s="60" t="n"/>
       <c r="F5" s="26" t="n">
         <v>0.2</v>
       </c>
@@ -857,6 +1505,10 @@
           <t>Firm take rate — share of perf-fee funding the comp pool</t>
         </is>
       </c>
+      <c r="B6" s="59" t="n"/>
+      <c r="C6" s="59" t="n"/>
+      <c r="D6" s="59" t="n"/>
+      <c r="E6" s="60" t="n"/>
       <c r="F6" s="26" t="n">
         <v>0.6</v>
       </c>
@@ -867,6 +1519,10 @@
           <t>AUM tier threshold (USD millions)</t>
         </is>
       </c>
+      <c r="B7" s="59" t="n"/>
+      <c r="C7" s="59" t="n"/>
+      <c r="D7" s="59" t="n"/>
+      <c r="E7" s="60" t="n"/>
       <c r="F7" s="27" t="n">
         <v>300</v>
       </c>
@@ -877,6 +1533,10 @@
           <t>Assumed gross return on AUM (drives the demo profit)</t>
         </is>
       </c>
+      <c r="B8" s="59" t="n"/>
+      <c r="C8" s="59" t="n"/>
+      <c r="D8" s="59" t="n"/>
+      <c r="E8" s="60" t="n"/>
       <c r="F8" s="26" t="n">
         <v>0.15</v>
       </c>
@@ -3347,8 +4007,8 @@
     <mergeCell ref="A94:M94"/>
     <mergeCell ref="A93:M93"/>
     <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A97:M97"/>
     <mergeCell ref="A95:M95"/>
-    <mergeCell ref="A97:M97"/>
     <mergeCell ref="A92:M92"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
@@ -3361,6 +4021,1215 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+    <col width="7" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Each role's share of the take (comp pool), over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Share = role weight × headcount ÷ total weighted units. Headcount scales with the AUM path; % sums to 100% each year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Starting AUM (USD m), compounded by Athanase net returns:</t>
+        </is>
+      </c>
+      <c r="D4" s="64" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="65" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B6" s="65" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C6" s="65" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D6" s="65" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E6" s="65" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F6" s="65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="G6" s="65" t="n">
+        <v>2011</v>
+      </c>
+      <c r="H6" s="65" t="n">
+        <v>2012</v>
+      </c>
+      <c r="I6" s="65" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J6" s="65" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K6" s="65" t="n">
+        <v>2015</v>
+      </c>
+      <c r="L6" s="65" t="n">
+        <v>2016</v>
+      </c>
+      <c r="M6" s="65" t="n">
+        <v>2017</v>
+      </c>
+      <c r="N6" s="65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="O6" s="65" t="n">
+        <v>2019</v>
+      </c>
+      <c r="P6" s="65" t="n">
+        <v>2020</v>
+      </c>
+      <c r="Q6" s="65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="R6" s="65" t="n">
+        <v>2022</v>
+      </c>
+      <c r="S6" s="65" t="n">
+        <v>2023</v>
+      </c>
+      <c r="T6" s="65" t="n">
+        <v>2024</v>
+      </c>
+      <c r="U6" s="65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="V6" s="65" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66" t="inlineStr">
+        <is>
+          <t>AUM (USD m)</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="n">
+        <v>162</v>
+      </c>
+      <c r="C7" s="67" t="n">
+        <v>149</v>
+      </c>
+      <c r="D7" s="67" t="n">
+        <v>88</v>
+      </c>
+      <c r="E7" s="67" t="n">
+        <v>159</v>
+      </c>
+      <c r="F7" s="67" t="n">
+        <v>205</v>
+      </c>
+      <c r="G7" s="67" t="n">
+        <v>201</v>
+      </c>
+      <c r="H7" s="67" t="n">
+        <v>211</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>290</v>
+      </c>
+      <c r="J7" s="67" t="n">
+        <v>350</v>
+      </c>
+      <c r="K7" s="67" t="n">
+        <v>382</v>
+      </c>
+      <c r="L7" s="67" t="n">
+        <v>484</v>
+      </c>
+      <c r="M7" s="67" t="n">
+        <v>505</v>
+      </c>
+      <c r="N7" s="67" t="n">
+        <v>441</v>
+      </c>
+      <c r="O7" s="67" t="n">
+        <v>415</v>
+      </c>
+      <c r="P7" s="67" t="n">
+        <v>485</v>
+      </c>
+      <c r="Q7" s="67" t="n">
+        <v>1457</v>
+      </c>
+      <c r="R7" s="67" t="n">
+        <v>1462</v>
+      </c>
+      <c r="S7" s="67" t="n">
+        <v>1454</v>
+      </c>
+      <c r="T7" s="67" t="n">
+        <v>1818</v>
+      </c>
+      <c r="U7" s="67" t="n">
+        <v>1892</v>
+      </c>
+      <c r="V7" s="67" t="n">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="68" t="inlineStr">
+        <is>
+          <t>Managing Partner / CIO</t>
+        </is>
+      </c>
+      <c r="B8" s="69" t="n">
+        <v>0.4058853373921867</v>
+      </c>
+      <c r="C8" s="69" t="n">
+        <v>0.4181102358089466</v>
+      </c>
+      <c r="D8" s="69" t="n">
+        <v>0.4716981132075472</v>
+      </c>
+      <c r="E8" s="69" t="n">
+        <v>0.4086636480581222</v>
+      </c>
+      <c r="F8" s="69" t="n">
+        <v>0.3710155007741043</v>
+      </c>
+      <c r="G8" s="69" t="n">
+        <v>0.3740693678369545</v>
+      </c>
+      <c r="H8" s="69" t="n">
+        <v>0.3665146064743118</v>
+      </c>
+      <c r="I8" s="69" t="n">
+        <v>0.3160774852233587</v>
+      </c>
+      <c r="J8" s="69" t="n">
+        <v>0.2834731739911558</v>
+      </c>
+      <c r="K8" s="69" t="n">
+        <v>0.2681422535657876</v>
+      </c>
+      <c r="L8" s="69" t="n">
+        <v>0.2293236143202949</v>
+      </c>
+      <c r="M8" s="69" t="n">
+        <v>0.2237103228438481</v>
+      </c>
+      <c r="N8" s="69" t="n">
+        <v>0.2442902861034774</v>
+      </c>
+      <c r="O8" s="69" t="n">
+        <v>0.2543483353706967</v>
+      </c>
+      <c r="P8" s="69" t="n">
+        <v>0.2289710921190028</v>
+      </c>
+      <c r="Q8" s="69" t="n">
+        <v>0.1639623987109049</v>
+      </c>
+      <c r="R8" s="69" t="n">
+        <v>0.1637801712085247</v>
+      </c>
+      <c r="S8" s="69" t="n">
+        <v>0.1641121949179748</v>
+      </c>
+      <c r="T8" s="69" t="n">
+        <v>0.1502131462366411</v>
+      </c>
+      <c r="U8" s="69" t="n">
+        <v>0.1476627549294869</v>
+      </c>
+      <c r="V8" s="69" t="n">
+        <v>0.1493314823247189</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>Partner / Co-PM</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="n">
+        <v>0.243531202435312</v>
+      </c>
+      <c r="C9" s="71" t="n">
+        <v>0.250866141485368</v>
+      </c>
+      <c r="D9" s="71" t="n">
+        <v>0.2830188679245283</v>
+      </c>
+      <c r="E9" s="71" t="n">
+        <v>0.2451981888348733</v>
+      </c>
+      <c r="F9" s="71" t="n">
+        <v>0.2226093004644626</v>
+      </c>
+      <c r="G9" s="71" t="n">
+        <v>0.2244416207021727</v>
+      </c>
+      <c r="H9" s="71" t="n">
+        <v>0.2199087638845871</v>
+      </c>
+      <c r="I9" s="71" t="n">
+        <v>0.1896464911340152</v>
+      </c>
+      <c r="J9" s="71" t="n">
+        <v>0.2122853784665377</v>
+      </c>
+      <c r="K9" s="71" t="n">
+        <v>0.2269733893256809</v>
+      </c>
+      <c r="L9" s="71" t="n">
+        <v>0.2641641501512013</v>
+      </c>
+      <c r="M9" s="71" t="n">
+        <v>0.2684523874126177</v>
+      </c>
+      <c r="N9" s="71" t="n">
+        <v>0.2498251129911846</v>
+      </c>
+      <c r="O9" s="71" t="n">
+        <v>0.2401888528867841</v>
+      </c>
+      <c r="P9" s="71" t="n">
+        <v>0.2645018891634069</v>
+      </c>
+      <c r="Q9" s="71" t="n">
+        <v>0.241752041400785</v>
+      </c>
+      <c r="R9" s="71" t="n">
+        <v>0.2419135772641852</v>
+      </c>
+      <c r="S9" s="71" t="n">
+        <v>0.241619254311421</v>
+      </c>
+      <c r="T9" s="71" t="n">
+        <v>0.2539400884328099</v>
+      </c>
+      <c r="U9" s="71" t="n">
+        <v>0.256200886920571</v>
+      </c>
+      <c r="V9" s="71" t="n">
+        <v>0.2547216408295717</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="68" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="B10" s="69" t="n">
+        <v>0.05073566717402334</v>
+      </c>
+      <c r="C10" s="69" t="n">
+        <v>0.04131138184910298</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="69" t="n">
+        <v>0.04859384222428394</v>
+      </c>
+      <c r="F10" s="69" t="n">
+        <v>0.07761714122141777</v>
+      </c>
+      <c r="G10" s="69" t="n">
+        <v>0.07526288734023868</v>
+      </c>
+      <c r="H10" s="69" t="n">
+        <v>0.08108692155434877</v>
+      </c>
+      <c r="I10" s="69" t="n">
+        <v>0.1199693568459926</v>
+      </c>
+      <c r="J10" s="69" t="n">
+        <v>0.1133892695964623</v>
+      </c>
+      <c r="K10" s="69" t="n">
+        <v>0.107256901426315</v>
+      </c>
+      <c r="L10" s="69" t="n">
+        <v>0.09172944572811798</v>
+      </c>
+      <c r="M10" s="69" t="n">
+        <v>0.09045271413385651</v>
+      </c>
+      <c r="N10" s="69" t="n">
+        <v>0.09771611444139094</v>
+      </c>
+      <c r="O10" s="69" t="n">
+        <v>0.1017393341482787</v>
+      </c>
+      <c r="P10" s="69" t="n">
+        <v>0.09158843684760112</v>
+      </c>
+      <c r="Q10" s="69" t="n">
+        <v>0.1611680276005233</v>
+      </c>
+      <c r="R10" s="69" t="n">
+        <v>0.1612757181761235</v>
+      </c>
+      <c r="S10" s="69" t="n">
+        <v>0.1610795028742807</v>
+      </c>
+      <c r="T10" s="69" t="n">
+        <v>0.1692933922885399</v>
+      </c>
+      <c r="U10" s="69" t="n">
+        <v>0.1708005912803806</v>
+      </c>
+      <c r="V10" s="69" t="n">
+        <v>0.1698144272197145</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>Head of Research</t>
+        </is>
+      </c>
+      <c r="B11" s="71" t="n">
+        <v>0.0380517503805175</v>
+      </c>
+      <c r="C11" s="71" t="n">
+        <v>0.03098353638682724</v>
+      </c>
+      <c r="D11" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="71" t="n">
+        <v>0.03644538166821296</v>
+      </c>
+      <c r="F11" s="71" t="n">
+        <v>0.05821285591606334</v>
+      </c>
+      <c r="G11" s="71" t="n">
+        <v>0.05644716550517902</v>
+      </c>
+      <c r="H11" s="71" t="n">
+        <v>0.06081519116576158</v>
+      </c>
+      <c r="I11" s="71" t="n">
+        <v>0.08997701763449445</v>
+      </c>
+      <c r="J11" s="71" t="n">
+        <v>0.08504195219734675</v>
+      </c>
+      <c r="K11" s="71" t="n">
+        <v>0.08044267606973626</v>
+      </c>
+      <c r="L11" s="71" t="n">
+        <v>0.06879708429608848</v>
+      </c>
+      <c r="M11" s="71" t="n">
+        <v>0.06711309685315443</v>
+      </c>
+      <c r="N11" s="71" t="n">
+        <v>0.07328708583104321</v>
+      </c>
+      <c r="O11" s="71" t="n">
+        <v>0.07630450061120903</v>
+      </c>
+      <c r="P11" s="71" t="n">
+        <v>0.06869132763570084</v>
+      </c>
+      <c r="Q11" s="71" t="n">
+        <v>0.04918871961327147</v>
+      </c>
+      <c r="R11" s="71" t="n">
+        <v>0.04913405136255741</v>
+      </c>
+      <c r="S11" s="71" t="n">
+        <v>0.04923365847539245</v>
+      </c>
+      <c r="T11" s="71" t="n">
+        <v>0.04506394387099233</v>
+      </c>
+      <c r="U11" s="71" t="n">
+        <v>0.04429882647884606</v>
+      </c>
+      <c r="V11" s="71" t="n">
+        <v>0.04479944469741567</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="68" t="inlineStr">
+        <is>
+          <t>Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B12" s="69" t="n">
+        <v>0.08117706747843734</v>
+      </c>
+      <c r="C12" s="69" t="n">
+        <v>0.08362204716178932</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>0.09433962264150944</v>
+      </c>
+      <c r="E12" s="69" t="n">
+        <v>0.08173272961162445</v>
+      </c>
+      <c r="F12" s="69" t="n">
+        <v>0.07420310015482087</v>
+      </c>
+      <c r="G12" s="69" t="n">
+        <v>0.07481387356739091</v>
+      </c>
+      <c r="H12" s="69" t="n">
+        <v>0.07330292129486236</v>
+      </c>
+      <c r="I12" s="69" t="n">
+        <v>0.06321549704467173</v>
+      </c>
+      <c r="J12" s="69" t="n">
+        <v>0.07076179282217923</v>
+      </c>
+      <c r="K12" s="69" t="n">
+        <v>0.07565779644189363</v>
+      </c>
+      <c r="L12" s="69" t="n">
+        <v>0.08805471671706708</v>
+      </c>
+      <c r="M12" s="69" t="n">
+        <v>0.08996842163569788</v>
+      </c>
+      <c r="N12" s="69" t="n">
+        <v>0.08327503766372819</v>
+      </c>
+      <c r="O12" s="69" t="n">
+        <v>0.08006295096226136</v>
+      </c>
+      <c r="P12" s="69" t="n">
+        <v>0.08816729638780231</v>
+      </c>
+      <c r="Q12" s="69" t="n">
+        <v>0.1133764935424426</v>
+      </c>
+      <c r="R12" s="69" t="n">
+        <v>0.1133938933297667</v>
+      </c>
+      <c r="S12" s="69" t="n">
+        <v>0.1133621904207353</v>
+      </c>
+      <c r="T12" s="69" t="n">
+        <v>0.1146893253915982</v>
+      </c>
+      <c r="U12" s="69" t="n">
+        <v>0.1149328466260877</v>
+      </c>
+      <c r="V12" s="69" t="n">
+        <v>0.114773510074801</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="B13" s="71" t="n">
+        <v>0.0639269406392694</v>
+      </c>
+      <c r="C13" s="71" t="n">
+        <v>0.06256664285180449</v>
+      </c>
+      <c r="D13" s="71" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="E13" s="71" t="n">
+        <v>0.06361779043425984</v>
+      </c>
+      <c r="F13" s="71" t="n">
+        <v>0.06780700245931787</v>
+      </c>
+      <c r="G13" s="71" t="n">
+        <v>0.06746719034250616</v>
+      </c>
+      <c r="H13" s="71" t="n">
+        <v>0.06830782924322205</v>
+      </c>
+      <c r="I13" s="71" t="n">
+        <v>0.07392010528060082</v>
+      </c>
+      <c r="J13" s="71" t="n">
+        <v>0.07647385657224623</v>
+      </c>
+      <c r="K13" s="71" t="n">
+        <v>0.07757174829303069</v>
+      </c>
+      <c r="L13" s="71" t="n">
+        <v>0.08035166374867565</v>
+      </c>
+      <c r="M13" s="71" t="n">
+        <v>0.08082629172268051</v>
+      </c>
+      <c r="N13" s="71" t="n">
+        <v>0.0792798569306542</v>
+      </c>
+      <c r="O13" s="71" t="n">
+        <v>0.07855957082184042</v>
+      </c>
+      <c r="P13" s="71" t="n">
+        <v>0.08037690888696172</v>
+      </c>
+      <c r="Q13" s="71" t="n">
+        <v>0.096700816560314</v>
+      </c>
+      <c r="R13" s="71" t="n">
+        <v>0.09676543090567409</v>
+      </c>
+      <c r="S13" s="71" t="n">
+        <v>0.09664770172456839</v>
+      </c>
+      <c r="T13" s="71" t="n">
+        <v>0.1015760353731239</v>
+      </c>
+      <c r="U13" s="71" t="n">
+        <v>0.1024803547682284</v>
+      </c>
+      <c r="V13" s="71" t="n">
+        <v>0.1018886563318287</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="68" t="inlineStr">
+        <is>
+          <t>Junior Analyst</t>
+        </is>
+      </c>
+      <c r="B14" s="69" t="n">
+        <v>0.0076103500761035</v>
+      </c>
+      <c r="C14" s="69" t="n">
+        <v>0.006196707277365446</v>
+      </c>
+      <c r="D14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="69" t="n">
+        <v>0.007289076333642593</v>
+      </c>
+      <c r="F14" s="69" t="n">
+        <v>0.01164257118321267</v>
+      </c>
+      <c r="G14" s="69" t="n">
+        <v>0.0112894331010358</v>
+      </c>
+      <c r="H14" s="69" t="n">
+        <v>0.01216303823315231</v>
+      </c>
+      <c r="I14" s="69" t="n">
+        <v>0.01799540352689889</v>
+      </c>
+      <c r="J14" s="69" t="n">
+        <v>0.02122853784665377</v>
+      </c>
+      <c r="K14" s="69" t="n">
+        <v>0.02269733893256809</v>
+      </c>
+      <c r="L14" s="69" t="n">
+        <v>0.02641641501512013</v>
+      </c>
+      <c r="M14" s="69" t="n">
+        <v>0.02699052649070936</v>
+      </c>
+      <c r="N14" s="69" t="n">
+        <v>0.02498251129911846</v>
+      </c>
+      <c r="O14" s="69" t="n">
+        <v>0.02401888528867841</v>
+      </c>
+      <c r="P14" s="69" t="n">
+        <v>0.02645018891634069</v>
+      </c>
+      <c r="Q14" s="69" t="n">
+        <v>0.03401294806273279</v>
+      </c>
+      <c r="R14" s="69" t="n">
+        <v>0.03401816799893</v>
+      </c>
+      <c r="S14" s="69" t="n">
+        <v>0.03400865712622059</v>
+      </c>
+      <c r="T14" s="69" t="n">
+        <v>0.03440679761747945</v>
+      </c>
+      <c r="U14" s="69" t="n">
+        <v>0.03447985398782631</v>
+      </c>
+      <c r="V14" s="69" t="n">
+        <v>0.0344320530224403</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>Head of Trading</t>
+        </is>
+      </c>
+      <c r="B15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="71" t="n">
+        <v>0.01266044222155325</v>
+      </c>
+      <c r="K15" s="71" t="n">
+        <v>0.01982641115586252</v>
+      </c>
+      <c r="L15" s="71" t="n">
+        <v>0.03797099446770729</v>
+      </c>
+      <c r="M15" s="71" t="n">
+        <v>0.04026785811189266</v>
+      </c>
+      <c r="N15" s="71" t="n">
+        <v>0.03097528239872945</v>
+      </c>
+      <c r="O15" s="71" t="n">
+        <v>0.02627395549930982</v>
+      </c>
+      <c r="P15" s="71" t="n">
+        <v>0.03813577016760158</v>
+      </c>
+      <c r="Q15" s="71" t="n">
+        <v>0.02951323176796288</v>
+      </c>
+      <c r="R15" s="71" t="n">
+        <v>0.02948043081753444</v>
+      </c>
+      <c r="S15" s="71" t="n">
+        <v>0.02954019508523547</v>
+      </c>
+      <c r="T15" s="71" t="n">
+        <v>0.0270383663225954</v>
+      </c>
+      <c r="U15" s="71" t="n">
+        <v>0.02657929588730763</v>
+      </c>
+      <c r="V15" s="71" t="n">
+        <v>0.02687966681844941</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="68" t="inlineStr">
+        <is>
+          <t>Trader / Execution</t>
+        </is>
+      </c>
+      <c r="B16" s="69" t="n">
+        <v>0.01268391679350583</v>
+      </c>
+      <c r="C16" s="69" t="n">
+        <v>0.01032784546227574</v>
+      </c>
+      <c r="D16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="69" t="n">
+        <v>0.01214846055607099</v>
+      </c>
+      <c r="F16" s="69" t="n">
+        <v>0.01940428530535444</v>
+      </c>
+      <c r="G16" s="69" t="n">
+        <v>0.01881572183505967</v>
+      </c>
+      <c r="H16" s="69" t="n">
+        <v>0.02027173038858719</v>
+      </c>
+      <c r="I16" s="69" t="n">
+        <v>0.02999233921149815</v>
+      </c>
+      <c r="J16" s="69" t="n">
+        <v>0.02834731739911558</v>
+      </c>
+      <c r="K16" s="69" t="n">
+        <v>0.02681422535657876</v>
+      </c>
+      <c r="L16" s="69" t="n">
+        <v>0.02293236143202949</v>
+      </c>
+      <c r="M16" s="69" t="n">
+        <v>0.02261317853346413</v>
+      </c>
+      <c r="N16" s="69" t="n">
+        <v>0.02442902861034774</v>
+      </c>
+      <c r="O16" s="69" t="n">
+        <v>0.02543483353706967</v>
+      </c>
+      <c r="P16" s="69" t="n">
+        <v>0.02289710921190028</v>
+      </c>
+      <c r="Q16" s="69" t="n">
+        <v>0.03279247974218098</v>
+      </c>
+      <c r="R16" s="69" t="n">
+        <v>0.03275603424170494</v>
+      </c>
+      <c r="S16" s="69" t="n">
+        <v>0.03282243898359496</v>
+      </c>
+      <c r="T16" s="69" t="n">
+        <v>0.03004262924732822</v>
+      </c>
+      <c r="U16" s="69" t="n">
+        <v>0.02953255098589737</v>
+      </c>
+      <c r="V16" s="69" t="n">
+        <v>0.02986629646494378</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>COO / Head of Operations</t>
+        </is>
+      </c>
+      <c r="B17" s="71" t="n">
+        <v>0.060882800608828</v>
+      </c>
+      <c r="C17" s="71" t="n">
+        <v>0.062716535371342</v>
+      </c>
+      <c r="D17" s="71" t="n">
+        <v>0.07075471698113207</v>
+      </c>
+      <c r="E17" s="71" t="n">
+        <v>0.06129954720871834</v>
+      </c>
+      <c r="F17" s="71" t="n">
+        <v>0.05565232511611565</v>
+      </c>
+      <c r="G17" s="71" t="n">
+        <v>0.05611040517554319</v>
+      </c>
+      <c r="H17" s="71" t="n">
+        <v>0.05497719097114678</v>
+      </c>
+      <c r="I17" s="71" t="n">
+        <v>0.0474116227835038</v>
+      </c>
+      <c r="J17" s="71" t="n">
+        <v>0.04252097609867338</v>
+      </c>
+      <c r="K17" s="71" t="n">
+        <v>0.04022133803486813</v>
+      </c>
+      <c r="L17" s="71" t="n">
+        <v>0.03439854214804424</v>
+      </c>
+      <c r="M17" s="71" t="n">
+        <v>0.03355654842657722</v>
+      </c>
+      <c r="N17" s="71" t="n">
+        <v>0.0366435429155216</v>
+      </c>
+      <c r="O17" s="71" t="n">
+        <v>0.03815225030560451</v>
+      </c>
+      <c r="P17" s="71" t="n">
+        <v>0.03434566381785042</v>
+      </c>
+      <c r="Q17" s="71" t="n">
+        <v>0.02459435980663573</v>
+      </c>
+      <c r="R17" s="71" t="n">
+        <v>0.0245670256812787</v>
+      </c>
+      <c r="S17" s="71" t="n">
+        <v>0.02461682923769622</v>
+      </c>
+      <c r="T17" s="71" t="n">
+        <v>0.02253197193549616</v>
+      </c>
+      <c r="U17" s="71" t="n">
+        <v>0.02214941323942303</v>
+      </c>
+      <c r="V17" s="71" t="n">
+        <v>0.02239972234870784</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="68" t="inlineStr">
+        <is>
+          <t>CFO / Finance</t>
+        </is>
+      </c>
+      <c r="B18" s="69" t="n">
+        <v>0.015220700152207</v>
+      </c>
+      <c r="C18" s="69" t="n">
+        <v>0.01239341455473089</v>
+      </c>
+      <c r="D18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="69" t="n">
+        <v>0.01457815266728519</v>
+      </c>
+      <c r="F18" s="69" t="n">
+        <v>0.02328514236642533</v>
+      </c>
+      <c r="G18" s="69" t="n">
+        <v>0.02257886620207161</v>
+      </c>
+      <c r="H18" s="69" t="n">
+        <v>0.02432607646630463</v>
+      </c>
+      <c r="I18" s="69" t="n">
+        <v>0.03599080705379777</v>
+      </c>
+      <c r="J18" s="69" t="n">
+        <v>0.0340167808789387</v>
+      </c>
+      <c r="K18" s="69" t="n">
+        <v>0.03217707042789451</v>
+      </c>
+      <c r="L18" s="69" t="n">
+        <v>0.02751883371843539</v>
+      </c>
+      <c r="M18" s="69" t="n">
+        <v>0.02684523874126177</v>
+      </c>
+      <c r="N18" s="69" t="n">
+        <v>0.02931483433241728</v>
+      </c>
+      <c r="O18" s="69" t="n">
+        <v>0.03052180024448361</v>
+      </c>
+      <c r="P18" s="69" t="n">
+        <v>0.02747653105428034</v>
+      </c>
+      <c r="Q18" s="69" t="n">
+        <v>0.01967548784530859</v>
+      </c>
+      <c r="R18" s="69" t="n">
+        <v>0.01965362054502296</v>
+      </c>
+      <c r="S18" s="69" t="n">
+        <v>0.01969346339015698</v>
+      </c>
+      <c r="T18" s="69" t="n">
+        <v>0.01802557754839693</v>
+      </c>
+      <c r="U18" s="69" t="n">
+        <v>0.01771953059153842</v>
+      </c>
+      <c r="V18" s="69" t="n">
+        <v>0.01791977787896627</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>Compliance / Legal</t>
+        </is>
+      </c>
+      <c r="B19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="71" t="n">
+        <v>0.00562686320957922</v>
+      </c>
+      <c r="K19" s="71" t="n">
+        <v>0.008811738291494453</v>
+      </c>
+      <c r="L19" s="71" t="n">
+        <v>0.01687599754120324</v>
+      </c>
+      <c r="M19" s="71" t="n">
+        <v>0.01789682582750785</v>
+      </c>
+      <c r="N19" s="71" t="n">
+        <v>0.01376679217721309</v>
+      </c>
+      <c r="O19" s="71" t="n">
+        <v>0.01167731355524881</v>
+      </c>
+      <c r="P19" s="71" t="n">
+        <v>0.0169492311856007</v>
+      </c>
+      <c r="Q19" s="71" t="n">
+        <v>0.01311699189687239</v>
+      </c>
+      <c r="R19" s="71" t="n">
+        <v>0.01310241369668197</v>
+      </c>
+      <c r="S19" s="71" t="n">
+        <v>0.01312897559343799</v>
+      </c>
+      <c r="T19" s="71" t="n">
+        <v>0.01201705169893129</v>
+      </c>
+      <c r="U19" s="71" t="n">
+        <v>0.01181302039435895</v>
+      </c>
+      <c r="V19" s="71" t="n">
+        <v>0.01194651858597751</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="68" t="inlineStr">
+        <is>
+          <t>Investor Relations / Ops</t>
+        </is>
+      </c>
+      <c r="B20" s="69" t="n">
+        <v>0.02029426686960933</v>
+      </c>
+      <c r="C20" s="69" t="n">
+        <v>0.02090551179044733</v>
+      </c>
+      <c r="D20" s="69" t="n">
+        <v>0.02358490566037736</v>
+      </c>
+      <c r="E20" s="69" t="n">
+        <v>0.02043318240290611</v>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>0.01855077503870522</v>
+      </c>
+      <c r="G20" s="69" t="n">
+        <v>0.01870346839184773</v>
+      </c>
+      <c r="H20" s="69" t="n">
+        <v>0.01832573032371559</v>
+      </c>
+      <c r="I20" s="69" t="n">
+        <v>0.01580387426116793</v>
+      </c>
+      <c r="J20" s="69" t="n">
+        <v>0.01417365869955779</v>
+      </c>
+      <c r="K20" s="69" t="n">
+        <v>0.01340711267828938</v>
+      </c>
+      <c r="L20" s="69" t="n">
+        <v>0.01146618071601475</v>
+      </c>
+      <c r="M20" s="69" t="n">
+        <v>0.01130658926673206</v>
+      </c>
+      <c r="N20" s="69" t="n">
+        <v>0.01221451430517387</v>
+      </c>
+      <c r="O20" s="69" t="n">
+        <v>0.01271741676853484</v>
+      </c>
+      <c r="P20" s="69" t="n">
+        <v>0.01144855460595014</v>
+      </c>
+      <c r="Q20" s="69" t="n">
+        <v>0.02014600345006541</v>
+      </c>
+      <c r="R20" s="69" t="n">
+        <v>0.02015946477201543</v>
+      </c>
+      <c r="S20" s="69" t="n">
+        <v>0.02013493785928508</v>
+      </c>
+      <c r="T20" s="69" t="n">
+        <v>0.02116167403606749</v>
+      </c>
+      <c r="U20" s="69" t="n">
+        <v>0.02135007391004758</v>
+      </c>
+      <c r="V20" s="69" t="n">
+        <v>0.02122680340246431</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="72" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B21" s="73">
+        <f>SUM(B8:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="73">
+        <f>SUM(C8:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="73">
+        <f>SUM(D8:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="73">
+        <f>SUM(E8:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="73">
+        <f>SUM(F8:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="73">
+        <f>SUM(G8:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="73">
+        <f>SUM(H8:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="73">
+        <f>SUM(I8:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="73">
+        <f>SUM(J8:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="73">
+        <f>SUM(K8:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="73">
+        <f>SUM(L8:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="73">
+        <f>SUM(M8:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="73">
+        <f>SUM(N8:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="73">
+        <f>SUM(O8:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="73">
+        <f>SUM(P8:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="73">
+        <f>SUM(Q8:Q20)</f>
+        <v/>
+      </c>
+      <c r="R21" s="73">
+        <f>SUM(R8:R20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="73">
+        <f>SUM(S8:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="73">
+        <f>SUM(T8:T20)</f>
+        <v/>
+      </c>
+      <c r="U21" s="73">
+        <f>SUM(U8:U20)</f>
+        <v/>
+      </c>
+      <c r="V21" s="73">
+        <f>SUM(V8:V20)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A1:V1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Static" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Take Over Time" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Take by AUM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -330,7 +330,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,6 +491,9 @@
     <xf numFmtId="9" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,7 +584,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Role share of the take over time (%)</a:t>
+              <a:t>Role share of the take vs AUM</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -595,7 +598,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A8</f>
+              <f>'Take by AUM'!A5</f>
             </strRef>
           </tx>
           <spPr>
@@ -613,12 +616,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$8:$V$8</f>
+              <f>'Take by AUM'!$B$5:$U$5</f>
             </numRef>
           </val>
         </ser>
@@ -627,7 +630,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A9</f>
+              <f>'Take by AUM'!A6</f>
             </strRef>
           </tx>
           <spPr>
@@ -645,12 +648,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$9:$V$9</f>
+              <f>'Take by AUM'!$B$6:$U$6</f>
             </numRef>
           </val>
         </ser>
@@ -659,7 +662,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A10</f>
+              <f>'Take by AUM'!A7</f>
             </strRef>
           </tx>
           <spPr>
@@ -677,12 +680,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$10:$V$10</f>
+              <f>'Take by AUM'!$B$7:$U$7</f>
             </numRef>
           </val>
         </ser>
@@ -691,7 +694,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A11</f>
+              <f>'Take by AUM'!A8</f>
             </strRef>
           </tx>
           <spPr>
@@ -709,12 +712,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$11:$V$11</f>
+              <f>'Take by AUM'!$B$8:$U$8</f>
             </numRef>
           </val>
         </ser>
@@ -723,7 +726,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A12</f>
+              <f>'Take by AUM'!A9</f>
             </strRef>
           </tx>
           <spPr>
@@ -741,12 +744,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$12:$V$12</f>
+              <f>'Take by AUM'!$B$9:$U$9</f>
             </numRef>
           </val>
         </ser>
@@ -755,7 +758,7 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A13</f>
+              <f>'Take by AUM'!A10</f>
             </strRef>
           </tx>
           <spPr>
@@ -773,12 +776,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$13:$V$13</f>
+              <f>'Take by AUM'!$B$10:$U$10</f>
             </numRef>
           </val>
         </ser>
@@ -787,7 +790,7 @@
           <order val="6"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A14</f>
+              <f>'Take by AUM'!A11</f>
             </strRef>
           </tx>
           <spPr>
@@ -805,12 +808,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$14:$V$14</f>
+              <f>'Take by AUM'!$B$11:$U$11</f>
             </numRef>
           </val>
         </ser>
@@ -819,7 +822,7 @@
           <order val="7"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A15</f>
+              <f>'Take by AUM'!A12</f>
             </strRef>
           </tx>
           <spPr>
@@ -837,12 +840,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$15:$V$15</f>
+              <f>'Take by AUM'!$B$12:$U$12</f>
             </numRef>
           </val>
         </ser>
@@ -851,7 +854,7 @@
           <order val="8"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A16</f>
+              <f>'Take by AUM'!A13</f>
             </strRef>
           </tx>
           <spPr>
@@ -869,12 +872,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$16:$V$16</f>
+              <f>'Take by AUM'!$B$13:$U$13</f>
             </numRef>
           </val>
         </ser>
@@ -883,7 +886,7 @@
           <order val="9"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A17</f>
+              <f>'Take by AUM'!A14</f>
             </strRef>
           </tx>
           <spPr>
@@ -901,12 +904,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$17:$V$17</f>
+              <f>'Take by AUM'!$B$14:$U$14</f>
             </numRef>
           </val>
         </ser>
@@ -915,7 +918,7 @@
           <order val="10"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A18</f>
+              <f>'Take by AUM'!A15</f>
             </strRef>
           </tx>
           <spPr>
@@ -933,12 +936,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$18:$V$18</f>
+              <f>'Take by AUM'!$B$15:$U$15</f>
             </numRef>
           </val>
         </ser>
@@ -947,7 +950,7 @@
           <order val="11"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A19</f>
+              <f>'Take by AUM'!A16</f>
             </strRef>
           </tx>
           <spPr>
@@ -965,12 +968,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$19:$V$19</f>
+              <f>'Take by AUM'!$B$16:$U$16</f>
             </numRef>
           </val>
         </ser>
@@ -979,7 +982,7 @@
           <order val="12"/>
           <tx>
             <strRef>
-              <f>'Take Over Time'!A20</f>
+              <f>'Take by AUM'!A17</f>
             </strRef>
           </tx>
           <spPr>
@@ -997,12 +1000,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Take Over Time'!$B$6:$V$6</f>
+              <f>'Take by AUM'!$B$4:$U$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Take Over Time'!$B$20:$V$20</f>
+              <f>'Take by AUM'!$B$17:$U$17</f>
             </numRef>
           </val>
         </ser>
@@ -1024,7 +1027,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Year</a:t>
+                  <a:t>AUM (USD m)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1104,7 +1107,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -4026,7 +4029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4050,1179 +4053,1051 @@
     <col width="7" customWidth="1" min="19" max="19"/>
     <col width="7" customWidth="1" min="20" max="20"/>
     <col width="7" customWidth="1" min="21" max="21"/>
-    <col width="7" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="61" t="inlineStr">
         <is>
-          <t>Each role's share of the take (comp pool), over time</t>
+          <t>Each role's share of the take (comp pool) as AUM grows $100m → $2bn</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Share = role weight × headcount ÷ total weighted units. Headcount scales with the AUM path; % sums to 100% each year.</t>
+          <t>Share = role weight × headcount ÷ total weighted units. Headcount interpolated across the AUM scenarios. Columns sum to 100%.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="63" t="inlineStr">
-        <is>
-          <t>Starting AUM (USD m), compounded by Athanase net returns:</t>
-        </is>
-      </c>
-      <c r="D4" s="64" t="n">
+      <c r="A4" s="72" t="inlineStr">
+        <is>
+          <t>AUM (USD m) →</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="n">
         <v>100</v>
       </c>
+      <c r="C4" s="74" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="74" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="74" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" s="74" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="74" t="n">
+        <v>600</v>
+      </c>
+      <c r="H4" s="74" t="n">
+        <v>700</v>
+      </c>
+      <c r="I4" s="74" t="n">
+        <v>800</v>
+      </c>
+      <c r="J4" s="74" t="n">
+        <v>900</v>
+      </c>
+      <c r="K4" s="74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="74" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M4" s="74" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N4" s="74" t="n">
+        <v>1300</v>
+      </c>
+      <c r="O4" s="74" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P4" s="74" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q4" s="74" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R4" s="74" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S4" s="74" t="n">
+        <v>1800</v>
+      </c>
+      <c r="T4" s="74" t="n">
+        <v>1900</v>
+      </c>
+      <c r="U4" s="74" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="68" t="inlineStr">
+        <is>
+          <t>Managing Partner / CIO</t>
+        </is>
+      </c>
+      <c r="B5" s="69" t="n">
+        <v>0.4716981132075472</v>
+      </c>
+      <c r="C5" s="69" t="n">
+        <v>0.3745318352059925</v>
+      </c>
+      <c r="D5" s="69" t="n">
+        <v>0.3105590062111801</v>
+      </c>
+      <c r="E5" s="69" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="F5" s="69" t="n">
+        <v>0.2242152466367713</v>
+      </c>
+      <c r="G5" s="69" t="n">
+        <v>0.2152389151958674</v>
+      </c>
+      <c r="H5" s="69" t="n">
+        <v>0.206953642384106</v>
+      </c>
+      <c r="I5" s="69" t="n">
+        <v>0.1992825827022718</v>
+      </c>
+      <c r="J5" s="69" t="n">
+        <v>0.1921598770176787</v>
+      </c>
+      <c r="K5" s="69" t="n">
+        <v>0.1855287569573284</v>
+      </c>
+      <c r="L5" s="69" t="n">
+        <v>0.1803426510369703</v>
+      </c>
+      <c r="M5" s="69" t="n">
+        <v>0.1754385964912281</v>
+      </c>
+      <c r="N5" s="69" t="n">
+        <v>0.1707941929974381</v>
+      </c>
+      <c r="O5" s="69" t="n">
+        <v>0.1663893510815308</v>
+      </c>
+      <c r="P5" s="69" t="n">
+        <v>0.16220600162206</v>
+      </c>
+      <c r="Q5" s="69" t="n">
+        <v>0.1582278481012658</v>
+      </c>
+      <c r="R5" s="69" t="n">
+        <v>0.1544401544401544</v>
+      </c>
+      <c r="S5" s="69" t="n">
+        <v>0.1508295625942685</v>
+      </c>
+      <c r="T5" s="69" t="n">
+        <v>0.1473839351510685</v>
+      </c>
+      <c r="U5" s="69" t="n">
+        <v>0.1440922190201729</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="65" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B6" s="65" t="n">
-        <v>2006</v>
-      </c>
-      <c r="C6" s="65" t="n">
-        <v>2007</v>
-      </c>
-      <c r="D6" s="65" t="n">
-        <v>2008</v>
-      </c>
-      <c r="E6" s="65" t="n">
-        <v>2009</v>
-      </c>
-      <c r="F6" s="65" t="n">
-        <v>2010</v>
-      </c>
-      <c r="G6" s="65" t="n">
-        <v>2011</v>
-      </c>
-      <c r="H6" s="65" t="n">
-        <v>2012</v>
-      </c>
-      <c r="I6" s="65" t="n">
-        <v>2013</v>
-      </c>
-      <c r="J6" s="65" t="n">
-        <v>2014</v>
-      </c>
-      <c r="K6" s="65" t="n">
-        <v>2015</v>
-      </c>
-      <c r="L6" s="65" t="n">
-        <v>2016</v>
-      </c>
-      <c r="M6" s="65" t="n">
-        <v>2017</v>
-      </c>
-      <c r="N6" s="65" t="n">
-        <v>2018</v>
-      </c>
-      <c r="O6" s="65" t="n">
-        <v>2019</v>
-      </c>
-      <c r="P6" s="65" t="n">
-        <v>2020</v>
-      </c>
-      <c r="Q6" s="65" t="n">
-        <v>2021</v>
-      </c>
-      <c r="R6" s="65" t="n">
-        <v>2022</v>
-      </c>
-      <c r="S6" s="65" t="n">
-        <v>2023</v>
-      </c>
-      <c r="T6" s="65" t="n">
-        <v>2024</v>
-      </c>
-      <c r="U6" s="65" t="n">
-        <v>2025</v>
-      </c>
-      <c r="V6" s="65" t="n">
-        <v>2026</v>
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>Partner / Co-PM</t>
+        </is>
+      </c>
+      <c r="B6" s="71" t="n">
+        <v>0.2830188679245283</v>
+      </c>
+      <c r="C6" s="71" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="D6" s="71" t="n">
+        <v>0.1863354037267081</v>
+      </c>
+      <c r="E6" s="71" t="n">
+        <v>0.234375</v>
+      </c>
+      <c r="F6" s="71" t="n">
+        <v>0.2690582959641256</v>
+      </c>
+      <c r="G6" s="71" t="n">
+        <v>0.2582866982350409</v>
+      </c>
+      <c r="H6" s="71" t="n">
+        <v>0.2483443708609272</v>
+      </c>
+      <c r="I6" s="71" t="n">
+        <v>0.2391390992427262</v>
+      </c>
+      <c r="J6" s="71" t="n">
+        <v>0.2305918524212144</v>
+      </c>
+      <c r="K6" s="71" t="n">
+        <v>0.2226345083487941</v>
+      </c>
+      <c r="L6" s="71" t="n">
+        <v>0.2272317403065825</v>
+      </c>
+      <c r="M6" s="71" t="n">
+        <v>0.2315789473684211</v>
+      </c>
+      <c r="N6" s="71" t="n">
+        <v>0.2356959863364645</v>
+      </c>
+      <c r="O6" s="71" t="n">
+        <v>0.2396006655574043</v>
+      </c>
+      <c r="P6" s="71" t="n">
+        <v>0.24330900243309</v>
+      </c>
+      <c r="Q6" s="71" t="n">
+        <v>0.2468354430379747</v>
+      </c>
+      <c r="R6" s="71" t="n">
+        <v>0.2501930501930502</v>
+      </c>
+      <c r="S6" s="71" t="n">
+        <v>0.253393665158371</v>
+      </c>
+      <c r="T6" s="71" t="n">
+        <v>0.2564480471628592</v>
+      </c>
+      <c r="U6" s="71" t="n">
+        <v>0.2593659942363112</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="66" t="inlineStr">
-        <is>
-          <t>AUM (USD m)</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="n">
-        <v>162</v>
-      </c>
-      <c r="C7" s="67" t="n">
-        <v>149</v>
-      </c>
-      <c r="D7" s="67" t="n">
-        <v>88</v>
-      </c>
-      <c r="E7" s="67" t="n">
-        <v>159</v>
-      </c>
-      <c r="F7" s="67" t="n">
-        <v>205</v>
-      </c>
-      <c r="G7" s="67" t="n">
-        <v>201</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>211</v>
-      </c>
-      <c r="I7" s="67" t="n">
-        <v>290</v>
-      </c>
-      <c r="J7" s="67" t="n">
-        <v>350</v>
-      </c>
-      <c r="K7" s="67" t="n">
-        <v>382</v>
-      </c>
-      <c r="L7" s="67" t="n">
-        <v>484</v>
-      </c>
-      <c r="M7" s="67" t="n">
-        <v>505</v>
-      </c>
-      <c r="N7" s="67" t="n">
-        <v>441</v>
-      </c>
-      <c r="O7" s="67" t="n">
-        <v>415</v>
-      </c>
-      <c r="P7" s="67" t="n">
-        <v>485</v>
-      </c>
-      <c r="Q7" s="67" t="n">
-        <v>1457</v>
-      </c>
-      <c r="R7" s="67" t="n">
-        <v>1462</v>
-      </c>
-      <c r="S7" s="67" t="n">
-        <v>1454</v>
-      </c>
-      <c r="T7" s="67" t="n">
-        <v>1818</v>
-      </c>
-      <c r="U7" s="67" t="n">
-        <v>1892</v>
-      </c>
-      <c r="V7" s="67" t="n">
-        <v>1843</v>
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="B7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="69" t="n">
+        <v>0.0749063670411985</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>0.124223602484472</v>
+      </c>
+      <c r="E7" s="69" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="F7" s="69" t="n">
+        <v>0.08968609865470852</v>
+      </c>
+      <c r="G7" s="69" t="n">
+        <v>0.1033146792940164</v>
+      </c>
+      <c r="H7" s="69" t="n">
+        <v>0.1158940397350993</v>
+      </c>
+      <c r="I7" s="69" t="n">
+        <v>0.127540852929454</v>
+      </c>
+      <c r="J7" s="69" t="n">
+        <v>0.1383551114527286</v>
+      </c>
+      <c r="K7" s="69" t="n">
+        <v>0.1484230055658627</v>
+      </c>
+      <c r="L7" s="69" t="n">
+        <v>0.151487826871055</v>
+      </c>
+      <c r="M7" s="69" t="n">
+        <v>0.1543859649122807</v>
+      </c>
+      <c r="N7" s="69" t="n">
+        <v>0.157130657557643</v>
+      </c>
+      <c r="O7" s="69" t="n">
+        <v>0.1597337770382695</v>
+      </c>
+      <c r="P7" s="69" t="n">
+        <v>0.16220600162206</v>
+      </c>
+      <c r="Q7" s="69" t="n">
+        <v>0.1645569620253164</v>
+      </c>
+      <c r="R7" s="69" t="n">
+        <v>0.1667953667953668</v>
+      </c>
+      <c r="S7" s="69" t="n">
+        <v>0.1689291101055807</v>
+      </c>
+      <c r="T7" s="69" t="n">
+        <v>0.1709653647752395</v>
+      </c>
+      <c r="U7" s="69" t="n">
+        <v>0.1729106628242075</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="68" t="inlineStr">
-        <is>
-          <t>Managing Partner / CIO</t>
-        </is>
-      </c>
-      <c r="B8" s="69" t="n">
-        <v>0.4058853373921867</v>
-      </c>
-      <c r="C8" s="69" t="n">
-        <v>0.4181102358089466</v>
-      </c>
-      <c r="D8" s="69" t="n">
-        <v>0.4716981132075472</v>
-      </c>
-      <c r="E8" s="69" t="n">
-        <v>0.4086636480581222</v>
-      </c>
-      <c r="F8" s="69" t="n">
-        <v>0.3710155007741043</v>
-      </c>
-      <c r="G8" s="69" t="n">
-        <v>0.3740693678369545</v>
-      </c>
-      <c r="H8" s="69" t="n">
-        <v>0.3665146064743118</v>
-      </c>
-      <c r="I8" s="69" t="n">
-        <v>0.3160774852233587</v>
-      </c>
-      <c r="J8" s="69" t="n">
-        <v>0.2834731739911558</v>
-      </c>
-      <c r="K8" s="69" t="n">
-        <v>0.2681422535657876</v>
-      </c>
-      <c r="L8" s="69" t="n">
-        <v>0.2293236143202949</v>
-      </c>
-      <c r="M8" s="69" t="n">
-        <v>0.2237103228438481</v>
-      </c>
-      <c r="N8" s="69" t="n">
-        <v>0.2442902861034774</v>
-      </c>
-      <c r="O8" s="69" t="n">
-        <v>0.2543483353706967</v>
-      </c>
-      <c r="P8" s="69" t="n">
-        <v>0.2289710921190028</v>
-      </c>
-      <c r="Q8" s="69" t="n">
-        <v>0.1639623987109049</v>
-      </c>
-      <c r="R8" s="69" t="n">
-        <v>0.1637801712085247</v>
-      </c>
-      <c r="S8" s="69" t="n">
-        <v>0.1641121949179748</v>
-      </c>
-      <c r="T8" s="69" t="n">
-        <v>0.1502131462366411</v>
-      </c>
-      <c r="U8" s="69" t="n">
-        <v>0.1476627549294869</v>
-      </c>
-      <c r="V8" s="69" t="n">
-        <v>0.1493314823247189</v>
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>Head of Research</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="71" t="n">
+        <v>0.05617977528089887</v>
+      </c>
+      <c r="D8" s="71" t="n">
+        <v>0.09316770186335403</v>
+      </c>
+      <c r="E8" s="71" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="F8" s="71" t="n">
+        <v>0.06726457399103139</v>
+      </c>
+      <c r="G8" s="71" t="n">
+        <v>0.06457167455876023</v>
+      </c>
+      <c r="H8" s="71" t="n">
+        <v>0.06208609271523179</v>
+      </c>
+      <c r="I8" s="71" t="n">
+        <v>0.05978477481068155</v>
+      </c>
+      <c r="J8" s="71" t="n">
+        <v>0.0576479631053036</v>
+      </c>
+      <c r="K8" s="71" t="n">
+        <v>0.05565862708719851</v>
+      </c>
+      <c r="L8" s="71" t="n">
+        <v>0.05410279531109107</v>
+      </c>
+      <c r="M8" s="71" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="N8" s="71" t="n">
+        <v>0.05123825789923143</v>
+      </c>
+      <c r="O8" s="71" t="n">
+        <v>0.04991680532445923</v>
+      </c>
+      <c r="P8" s="71" t="n">
+        <v>0.04866180048661801</v>
+      </c>
+      <c r="Q8" s="71" t="n">
+        <v>0.04746835443037975</v>
+      </c>
+      <c r="R8" s="71" t="n">
+        <v>0.04633204633204633</v>
+      </c>
+      <c r="S8" s="71" t="n">
+        <v>0.04524886877828054</v>
+      </c>
+      <c r="T8" s="71" t="n">
+        <v>0.04421518054532056</v>
+      </c>
+      <c r="U8" s="71" t="n">
+        <v>0.04322766570605188</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="70" t="inlineStr">
-        <is>
-          <t>Partner / Co-PM</t>
-        </is>
-      </c>
-      <c r="B9" s="71" t="n">
-        <v>0.243531202435312</v>
-      </c>
-      <c r="C9" s="71" t="n">
-        <v>0.250866141485368</v>
-      </c>
-      <c r="D9" s="71" t="n">
-        <v>0.2830188679245283</v>
-      </c>
-      <c r="E9" s="71" t="n">
-        <v>0.2451981888348733</v>
-      </c>
-      <c r="F9" s="71" t="n">
-        <v>0.2226093004644626</v>
-      </c>
-      <c r="G9" s="71" t="n">
-        <v>0.2244416207021727</v>
-      </c>
-      <c r="H9" s="71" t="n">
-        <v>0.2199087638845871</v>
-      </c>
-      <c r="I9" s="71" t="n">
-        <v>0.1896464911340152</v>
-      </c>
-      <c r="J9" s="71" t="n">
-        <v>0.2122853784665377</v>
-      </c>
-      <c r="K9" s="71" t="n">
-        <v>0.2269733893256809</v>
-      </c>
-      <c r="L9" s="71" t="n">
-        <v>0.2641641501512013</v>
-      </c>
-      <c r="M9" s="71" t="n">
-        <v>0.2684523874126177</v>
-      </c>
-      <c r="N9" s="71" t="n">
-        <v>0.2498251129911846</v>
-      </c>
-      <c r="O9" s="71" t="n">
-        <v>0.2401888528867841</v>
-      </c>
-      <c r="P9" s="71" t="n">
-        <v>0.2645018891634069</v>
-      </c>
-      <c r="Q9" s="71" t="n">
-        <v>0.241752041400785</v>
-      </c>
-      <c r="R9" s="71" t="n">
-        <v>0.2419135772641852</v>
-      </c>
-      <c r="S9" s="71" t="n">
-        <v>0.241619254311421</v>
-      </c>
-      <c r="T9" s="71" t="n">
-        <v>0.2539400884328099</v>
-      </c>
-      <c r="U9" s="71" t="n">
-        <v>0.256200886920571</v>
-      </c>
-      <c r="V9" s="71" t="n">
-        <v>0.2547216408295717</v>
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>Senior Analyst</t>
+        </is>
+      </c>
+      <c r="B9" s="69" t="n">
+        <v>0.09433962264150944</v>
+      </c>
+      <c r="C9" s="69" t="n">
+        <v>0.0749063670411985</v>
+      </c>
+      <c r="D9" s="69" t="n">
+        <v>0.06211180124223602</v>
+      </c>
+      <c r="E9" s="69" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="F9" s="69" t="n">
+        <v>0.08968609865470852</v>
+      </c>
+      <c r="G9" s="69" t="n">
+        <v>0.09470512268618167</v>
+      </c>
+      <c r="H9" s="69" t="n">
+        <v>0.09933774834437087</v>
+      </c>
+      <c r="I9" s="69" t="n">
+        <v>0.1036269430051813</v>
+      </c>
+      <c r="J9" s="69" t="n">
+        <v>0.1076095311299001</v>
+      </c>
+      <c r="K9" s="69" t="n">
+        <v>0.111317254174397</v>
+      </c>
+      <c r="L9" s="69" t="n">
+        <v>0.1118124436429215</v>
+      </c>
+      <c r="M9" s="69" t="n">
+        <v>0.112280701754386</v>
+      </c>
+      <c r="N9" s="69" t="n">
+        <v>0.1127241673783091</v>
+      </c>
+      <c r="O9" s="69" t="n">
+        <v>0.1131447587354409</v>
+      </c>
+      <c r="P9" s="69" t="n">
+        <v>0.113544201135442</v>
+      </c>
+      <c r="Q9" s="69" t="n">
+        <v>0.1139240506329114</v>
+      </c>
+      <c r="R9" s="69" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="S9" s="69" t="n">
+        <v>0.114630467571644</v>
+      </c>
+      <c r="T9" s="69" t="n">
+        <v>0.1149594694178335</v>
+      </c>
+      <c r="U9" s="69" t="n">
+        <v>0.1152737752161383</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
-        <is>
-          <t>Portfolio Manager</t>
-        </is>
-      </c>
-      <c r="B10" s="69" t="n">
-        <v>0.05073566717402334</v>
-      </c>
-      <c r="C10" s="69" t="n">
-        <v>0.04131138184910298</v>
-      </c>
-      <c r="D10" s="69" t="n">
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="B10" s="71" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="C10" s="71" t="n">
+        <v>0.06741573033707865</v>
+      </c>
+      <c r="D10" s="71" t="n">
+        <v>0.07453416149068323</v>
+      </c>
+      <c r="E10" s="71" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="F10" s="71" t="n">
+        <v>0.08071748878923767</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>0.0826517434352131</v>
+      </c>
+      <c r="H10" s="71" t="n">
+        <v>0.08443708609271523</v>
+      </c>
+      <c r="I10" s="71" t="n">
+        <v>0.08609007572738143</v>
+      </c>
+      <c r="J10" s="71" t="n">
+        <v>0.08762490392006146</v>
+      </c>
+      <c r="K10" s="71" t="n">
+        <v>0.08905380333951762</v>
+      </c>
+      <c r="L10" s="71" t="n">
+        <v>0.09089269612263301</v>
+      </c>
+      <c r="M10" s="71" t="n">
+        <v>0.09263157894736843</v>
+      </c>
+      <c r="N10" s="71" t="n">
+        <v>0.09427839453458582</v>
+      </c>
+      <c r="O10" s="71" t="n">
+        <v>0.09584026622296173</v>
+      </c>
+      <c r="P10" s="71" t="n">
+        <v>0.09732360097323602</v>
+      </c>
+      <c r="Q10" s="71" t="n">
+        <v>0.09873417721518989</v>
+      </c>
+      <c r="R10" s="71" t="n">
+        <v>0.1000772200772201</v>
+      </c>
+      <c r="S10" s="71" t="n">
+        <v>0.1013574660633484</v>
+      </c>
+      <c r="T10" s="71" t="n">
+        <v>0.1025792188651437</v>
+      </c>
+      <c r="U10" s="71" t="n">
+        <v>0.1037463976945245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>Junior Analyst</t>
+        </is>
+      </c>
+      <c r="B11" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="69" t="n">
-        <v>0.04859384222428394</v>
-      </c>
-      <c r="F10" s="69" t="n">
-        <v>0.07761714122141777</v>
-      </c>
-      <c r="G10" s="69" t="n">
-        <v>0.07526288734023868</v>
-      </c>
-      <c r="H10" s="69" t="n">
-        <v>0.08108692155434877</v>
-      </c>
-      <c r="I10" s="69" t="n">
-        <v>0.1199693568459926</v>
-      </c>
-      <c r="J10" s="69" t="n">
-        <v>0.1133892695964623</v>
-      </c>
-      <c r="K10" s="69" t="n">
-        <v>0.107256901426315</v>
-      </c>
-      <c r="L10" s="69" t="n">
-        <v>0.09172944572811798</v>
-      </c>
-      <c r="M10" s="69" t="n">
-        <v>0.09045271413385651</v>
-      </c>
-      <c r="N10" s="69" t="n">
-        <v>0.09771611444139094</v>
-      </c>
-      <c r="O10" s="69" t="n">
-        <v>0.1017393341482787</v>
-      </c>
-      <c r="P10" s="69" t="n">
-        <v>0.09158843684760112</v>
-      </c>
-      <c r="Q10" s="69" t="n">
-        <v>0.1611680276005233</v>
-      </c>
-      <c r="R10" s="69" t="n">
-        <v>0.1612757181761235</v>
-      </c>
-      <c r="S10" s="69" t="n">
-        <v>0.1610795028742807</v>
-      </c>
-      <c r="T10" s="69" t="n">
-        <v>0.1692933922885399</v>
-      </c>
-      <c r="U10" s="69" t="n">
-        <v>0.1708005912803806</v>
-      </c>
-      <c r="V10" s="69" t="n">
-        <v>0.1698144272197145</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="70" t="inlineStr">
-        <is>
-          <t>Head of Research</t>
-        </is>
-      </c>
-      <c r="B11" s="71" t="n">
-        <v>0.0380517503805175</v>
-      </c>
-      <c r="C11" s="71" t="n">
-        <v>0.03098353638682724</v>
-      </c>
-      <c r="D11" s="71" t="n">
+      <c r="C11" s="69" t="n">
+        <v>0.01123595505617977</v>
+      </c>
+      <c r="D11" s="69" t="n">
+        <v>0.01863354037267081</v>
+      </c>
+      <c r="E11" s="69" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="F11" s="69" t="n">
+        <v>0.02690582959641256</v>
+      </c>
+      <c r="G11" s="69" t="n">
+        <v>0.0284115368058545</v>
+      </c>
+      <c r="H11" s="69" t="n">
+        <v>0.02980132450331125</v>
+      </c>
+      <c r="I11" s="69" t="n">
+        <v>0.03108808290155441</v>
+      </c>
+      <c r="J11" s="69" t="n">
+        <v>0.03228285933897001</v>
+      </c>
+      <c r="K11" s="69" t="n">
+        <v>0.03339517625231911</v>
+      </c>
+      <c r="L11" s="69" t="n">
+        <v>0.03354373309287647</v>
+      </c>
+      <c r="M11" s="69" t="n">
+        <v>0.0336842105263158</v>
+      </c>
+      <c r="N11" s="69" t="n">
+        <v>0.03381725021349274</v>
+      </c>
+      <c r="O11" s="69" t="n">
+        <v>0.03394342762063228</v>
+      </c>
+      <c r="P11" s="69" t="n">
+        <v>0.0340632603406326</v>
+      </c>
+      <c r="Q11" s="69" t="n">
+        <v>0.03417721518987342</v>
+      </c>
+      <c r="R11" s="69" t="n">
+        <v>0.03428571428571429</v>
+      </c>
+      <c r="S11" s="69" t="n">
+        <v>0.03438914027149321</v>
+      </c>
+      <c r="T11" s="69" t="n">
+        <v>0.03448784082535004</v>
+      </c>
+      <c r="U11" s="69" t="n">
+        <v>0.0345821325648415</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>Head of Trading</t>
+        </is>
+      </c>
+      <c r="B12" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="71" t="n">
-        <v>0.03644538166821296</v>
-      </c>
-      <c r="F11" s="71" t="n">
-        <v>0.05821285591606334</v>
-      </c>
-      <c r="G11" s="71" t="n">
-        <v>0.05644716550517902</v>
-      </c>
-      <c r="H11" s="71" t="n">
-        <v>0.06081519116576158</v>
-      </c>
-      <c r="I11" s="71" t="n">
-        <v>0.08997701763449445</v>
-      </c>
-      <c r="J11" s="71" t="n">
-        <v>0.08504195219734675</v>
-      </c>
-      <c r="K11" s="71" t="n">
-        <v>0.08044267606973626</v>
-      </c>
-      <c r="L11" s="71" t="n">
-        <v>0.06879708429608848</v>
-      </c>
-      <c r="M11" s="71" t="n">
-        <v>0.06711309685315443</v>
-      </c>
-      <c r="N11" s="71" t="n">
-        <v>0.07328708583104321</v>
-      </c>
-      <c r="O11" s="71" t="n">
-        <v>0.07630450061120903</v>
-      </c>
-      <c r="P11" s="71" t="n">
-        <v>0.06869132763570084</v>
-      </c>
-      <c r="Q11" s="71" t="n">
-        <v>0.04918871961327147</v>
-      </c>
-      <c r="R11" s="71" t="n">
-        <v>0.04913405136255741</v>
-      </c>
-      <c r="S11" s="71" t="n">
-        <v>0.04923365847539245</v>
-      </c>
-      <c r="T11" s="71" t="n">
-        <v>0.04506394387099233</v>
-      </c>
-      <c r="U11" s="71" t="n">
-        <v>0.04429882647884606</v>
-      </c>
-      <c r="V11" s="71" t="n">
-        <v>0.04479944469741567</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="68" t="inlineStr">
-        <is>
-          <t>Senior Analyst</t>
-        </is>
-      </c>
-      <c r="B12" s="69" t="n">
-        <v>0.08117706747843734</v>
-      </c>
-      <c r="C12" s="69" t="n">
-        <v>0.08362204716178932</v>
-      </c>
-      <c r="D12" s="69" t="n">
-        <v>0.09433962264150944</v>
-      </c>
-      <c r="E12" s="69" t="n">
-        <v>0.08173272961162445</v>
-      </c>
-      <c r="F12" s="69" t="n">
-        <v>0.07420310015482087</v>
-      </c>
-      <c r="G12" s="69" t="n">
-        <v>0.07481387356739091</v>
-      </c>
-      <c r="H12" s="69" t="n">
-        <v>0.07330292129486236</v>
-      </c>
-      <c r="I12" s="69" t="n">
-        <v>0.06321549704467173</v>
-      </c>
-      <c r="J12" s="69" t="n">
-        <v>0.07076179282217923</v>
-      </c>
-      <c r="K12" s="69" t="n">
-        <v>0.07565779644189363</v>
-      </c>
-      <c r="L12" s="69" t="n">
-        <v>0.08805471671706708</v>
-      </c>
-      <c r="M12" s="69" t="n">
-        <v>0.08996842163569788</v>
-      </c>
-      <c r="N12" s="69" t="n">
-        <v>0.08327503766372819</v>
-      </c>
-      <c r="O12" s="69" t="n">
-        <v>0.08006295096226136</v>
-      </c>
-      <c r="P12" s="69" t="n">
-        <v>0.08816729638780231</v>
-      </c>
-      <c r="Q12" s="69" t="n">
-        <v>0.1133764935424426</v>
-      </c>
-      <c r="R12" s="69" t="n">
-        <v>0.1133938933297667</v>
-      </c>
-      <c r="S12" s="69" t="n">
-        <v>0.1133621904207353</v>
-      </c>
-      <c r="T12" s="69" t="n">
-        <v>0.1146893253915982</v>
-      </c>
-      <c r="U12" s="69" t="n">
-        <v>0.1149328466260877</v>
-      </c>
-      <c r="V12" s="69" t="n">
-        <v>0.114773510074801</v>
+      <c r="C12" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="71" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="F12" s="71" t="n">
+        <v>0.04035874439461883</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <v>0.03874300473525614</v>
+      </c>
+      <c r="H12" s="71" t="n">
+        <v>0.03725165562913908</v>
+      </c>
+      <c r="I12" s="71" t="n">
+        <v>0.03587086488640893</v>
+      </c>
+      <c r="J12" s="71" t="n">
+        <v>0.03458877786318216</v>
+      </c>
+      <c r="K12" s="71" t="n">
+        <v>0.03339517625231911</v>
+      </c>
+      <c r="L12" s="71" t="n">
+        <v>0.03246167718665464</v>
+      </c>
+      <c r="M12" s="71" t="n">
+        <v>0.03157894736842105</v>
+      </c>
+      <c r="N12" s="71" t="n">
+        <v>0.03074295473953886</v>
+      </c>
+      <c r="O12" s="71" t="n">
+        <v>0.02995008319467554</v>
+      </c>
+      <c r="P12" s="71" t="n">
+        <v>0.0291970802919708</v>
+      </c>
+      <c r="Q12" s="71" t="n">
+        <v>0.02848101265822785</v>
+      </c>
+      <c r="R12" s="71" t="n">
+        <v>0.0277992277992278</v>
+      </c>
+      <c r="S12" s="71" t="n">
+        <v>0.02714932126696833</v>
+      </c>
+      <c r="T12" s="71" t="n">
+        <v>0.02652910832719233</v>
+      </c>
+      <c r="U12" s="71" t="n">
+        <v>0.02593659942363112</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="70" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="B13" s="71" t="n">
-        <v>0.0639269406392694</v>
-      </c>
-      <c r="C13" s="71" t="n">
-        <v>0.06256664285180449</v>
-      </c>
-      <c r="D13" s="71" t="n">
-        <v>0.05660377358490566</v>
-      </c>
-      <c r="E13" s="71" t="n">
-        <v>0.06361779043425984</v>
-      </c>
-      <c r="F13" s="71" t="n">
-        <v>0.06780700245931787</v>
-      </c>
-      <c r="G13" s="71" t="n">
-        <v>0.06746719034250616</v>
-      </c>
-      <c r="H13" s="71" t="n">
-        <v>0.06830782924322205</v>
-      </c>
-      <c r="I13" s="71" t="n">
-        <v>0.07392010528060082</v>
-      </c>
-      <c r="J13" s="71" t="n">
-        <v>0.07647385657224623</v>
-      </c>
-      <c r="K13" s="71" t="n">
-        <v>0.07757174829303069</v>
-      </c>
-      <c r="L13" s="71" t="n">
-        <v>0.08035166374867565</v>
-      </c>
-      <c r="M13" s="71" t="n">
-        <v>0.08082629172268051</v>
-      </c>
-      <c r="N13" s="71" t="n">
-        <v>0.0792798569306542</v>
-      </c>
-      <c r="O13" s="71" t="n">
-        <v>0.07855957082184042</v>
-      </c>
-      <c r="P13" s="71" t="n">
-        <v>0.08037690888696172</v>
-      </c>
-      <c r="Q13" s="71" t="n">
-        <v>0.096700816560314</v>
-      </c>
-      <c r="R13" s="71" t="n">
-        <v>0.09676543090567409</v>
-      </c>
-      <c r="S13" s="71" t="n">
-        <v>0.09664770172456839</v>
-      </c>
-      <c r="T13" s="71" t="n">
-        <v>0.1015760353731239</v>
-      </c>
-      <c r="U13" s="71" t="n">
-        <v>0.1024803547682284</v>
-      </c>
-      <c r="V13" s="71" t="n">
-        <v>0.1018886563318287</v>
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t>Trader / Execution</t>
+        </is>
+      </c>
+      <c r="B13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="69" t="n">
+        <v>0.01872659176029963</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>0.03105590062111801</v>
+      </c>
+      <c r="E13" s="69" t="n">
+        <v>0.02604166666666667</v>
+      </c>
+      <c r="F13" s="69" t="n">
+        <v>0.02242152466367713</v>
+      </c>
+      <c r="G13" s="69" t="n">
+        <v>0.02582866982350409</v>
+      </c>
+      <c r="H13" s="69" t="n">
+        <v>0.02897350993377484</v>
+      </c>
+      <c r="I13" s="69" t="n">
+        <v>0.03188521323236349</v>
+      </c>
+      <c r="J13" s="69" t="n">
+        <v>0.03458877786318216</v>
+      </c>
+      <c r="K13" s="69" t="n">
+        <v>0.03710575139146568</v>
+      </c>
+      <c r="L13" s="69" t="n">
+        <v>0.03606853020739405</v>
+      </c>
+      <c r="M13" s="69" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="N13" s="69" t="n">
+        <v>0.03415883859948762</v>
+      </c>
+      <c r="O13" s="69" t="n">
+        <v>0.03327787021630615</v>
+      </c>
+      <c r="P13" s="69" t="n">
+        <v>0.032441200324412</v>
+      </c>
+      <c r="Q13" s="69" t="n">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="R13" s="69" t="n">
+        <v>0.03088803088803089</v>
+      </c>
+      <c r="S13" s="69" t="n">
+        <v>0.0301659125188537</v>
+      </c>
+      <c r="T13" s="69" t="n">
+        <v>0.02947678703021371</v>
+      </c>
+      <c r="U13" s="69" t="n">
+        <v>0.02881844380403458</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
-        <is>
-          <t>Junior Analyst</t>
-        </is>
-      </c>
-      <c r="B14" s="69" t="n">
-        <v>0.0076103500761035</v>
-      </c>
-      <c r="C14" s="69" t="n">
-        <v>0.006196707277365446</v>
-      </c>
-      <c r="D14" s="69" t="n">
+      <c r="A14" s="70" t="inlineStr">
+        <is>
+          <t>COO / Head of Operations</t>
+        </is>
+      </c>
+      <c r="B14" s="71" t="n">
+        <v>0.07075471698113207</v>
+      </c>
+      <c r="C14" s="71" t="n">
+        <v>0.05617977528089887</v>
+      </c>
+      <c r="D14" s="71" t="n">
+        <v>0.04658385093167702</v>
+      </c>
+      <c r="E14" s="71" t="n">
+        <v>0.0390625</v>
+      </c>
+      <c r="F14" s="71" t="n">
+        <v>0.0336322869955157</v>
+      </c>
+      <c r="G14" s="71" t="n">
+        <v>0.03228583727938011</v>
+      </c>
+      <c r="H14" s="71" t="n">
+        <v>0.0310430463576159</v>
+      </c>
+      <c r="I14" s="71" t="n">
+        <v>0.02989238740534077</v>
+      </c>
+      <c r="J14" s="71" t="n">
+        <v>0.0288239815526518</v>
+      </c>
+      <c r="K14" s="71" t="n">
+        <v>0.02782931354359926</v>
+      </c>
+      <c r="L14" s="71" t="n">
+        <v>0.02705139765554554</v>
+      </c>
+      <c r="M14" s="71" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="N14" s="71" t="n">
+        <v>0.02561912894961571</v>
+      </c>
+      <c r="O14" s="71" t="n">
+        <v>0.02495840266222962</v>
+      </c>
+      <c r="P14" s="71" t="n">
+        <v>0.024330900243309</v>
+      </c>
+      <c r="Q14" s="71" t="n">
+        <v>0.02373417721518987</v>
+      </c>
+      <c r="R14" s="71" t="n">
+        <v>0.02316602316602316</v>
+      </c>
+      <c r="S14" s="71" t="n">
+        <v>0.02262443438914027</v>
+      </c>
+      <c r="T14" s="71" t="n">
+        <v>0.02210759027266028</v>
+      </c>
+      <c r="U14" s="71" t="n">
+        <v>0.02161383285302594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t>CFO / Finance</t>
+        </is>
+      </c>
+      <c r="B15" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="69" t="n">
-        <v>0.007289076333642593</v>
-      </c>
-      <c r="F14" s="69" t="n">
-        <v>0.01164257118321267</v>
-      </c>
-      <c r="G14" s="69" t="n">
-        <v>0.0112894331010358</v>
-      </c>
-      <c r="H14" s="69" t="n">
-        <v>0.01216303823315231</v>
-      </c>
-      <c r="I14" s="69" t="n">
-        <v>0.01799540352689889</v>
-      </c>
-      <c r="J14" s="69" t="n">
-        <v>0.02122853784665377</v>
-      </c>
-      <c r="K14" s="69" t="n">
-        <v>0.02269733893256809</v>
-      </c>
-      <c r="L14" s="69" t="n">
-        <v>0.02641641501512013</v>
-      </c>
-      <c r="M14" s="69" t="n">
-        <v>0.02699052649070936</v>
-      </c>
-      <c r="N14" s="69" t="n">
-        <v>0.02498251129911846</v>
-      </c>
-      <c r="O14" s="69" t="n">
-        <v>0.02401888528867841</v>
-      </c>
-      <c r="P14" s="69" t="n">
-        <v>0.02645018891634069</v>
-      </c>
-      <c r="Q14" s="69" t="n">
-        <v>0.03401294806273279</v>
-      </c>
-      <c r="R14" s="69" t="n">
-        <v>0.03401816799893</v>
-      </c>
-      <c r="S14" s="69" t="n">
-        <v>0.03400865712622059</v>
-      </c>
-      <c r="T14" s="69" t="n">
-        <v>0.03440679761747945</v>
-      </c>
-      <c r="U14" s="69" t="n">
-        <v>0.03447985398782631</v>
-      </c>
-      <c r="V14" s="69" t="n">
-        <v>0.0344320530224403</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="70" t="inlineStr">
-        <is>
-          <t>Head of Trading</t>
-        </is>
-      </c>
-      <c r="B15" s="71" t="n">
+      <c r="C15" s="69" t="n">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="D15" s="69" t="n">
+        <v>0.03726708074534162</v>
+      </c>
+      <c r="E15" s="69" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="F15" s="69" t="n">
+        <v>0.02690582959641256</v>
+      </c>
+      <c r="G15" s="69" t="n">
+        <v>0.02582866982350409</v>
+      </c>
+      <c r="H15" s="69" t="n">
+        <v>0.02483443708609272</v>
+      </c>
+      <c r="I15" s="69" t="n">
+        <v>0.02391390992427262</v>
+      </c>
+      <c r="J15" s="69" t="n">
+        <v>0.02305918524212144</v>
+      </c>
+      <c r="K15" s="69" t="n">
+        <v>0.02226345083487941</v>
+      </c>
+      <c r="L15" s="69" t="n">
+        <v>0.02164111812443643</v>
+      </c>
+      <c r="M15" s="69" t="n">
+        <v>0.02105263157894737</v>
+      </c>
+      <c r="N15" s="69" t="n">
+        <v>0.02049530315969257</v>
+      </c>
+      <c r="O15" s="69" t="n">
+        <v>0.01996672212978369</v>
+      </c>
+      <c r="P15" s="69" t="n">
+        <v>0.0194647201946472</v>
+      </c>
+      <c r="Q15" s="69" t="n">
+        <v>0.0189873417721519</v>
+      </c>
+      <c r="R15" s="69" t="n">
+        <v>0.01853281853281853</v>
+      </c>
+      <c r="S15" s="69" t="n">
+        <v>0.01809954751131222</v>
+      </c>
+      <c r="T15" s="69" t="n">
+        <v>0.01768607221812822</v>
+      </c>
+      <c r="U15" s="69" t="n">
+        <v>0.01729106628242075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>Compliance / Legal</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="71" t="n">
+      <c r="C16" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="71" t="n">
+      <c r="D16" s="71" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="71" t="n">
-        <v>0.01266044222155325</v>
-      </c>
-      <c r="K15" s="71" t="n">
-        <v>0.01982641115586252</v>
-      </c>
-      <c r="L15" s="71" t="n">
-        <v>0.03797099446770729</v>
-      </c>
-      <c r="M15" s="71" t="n">
-        <v>0.04026785811189266</v>
-      </c>
-      <c r="N15" s="71" t="n">
-        <v>0.03097528239872945</v>
-      </c>
-      <c r="O15" s="71" t="n">
-        <v>0.02627395549930982</v>
-      </c>
-      <c r="P15" s="71" t="n">
-        <v>0.03813577016760158</v>
-      </c>
-      <c r="Q15" s="71" t="n">
-        <v>0.02951323176796288</v>
-      </c>
-      <c r="R15" s="71" t="n">
-        <v>0.02948043081753444</v>
-      </c>
-      <c r="S15" s="71" t="n">
-        <v>0.02954019508523547</v>
-      </c>
-      <c r="T15" s="71" t="n">
-        <v>0.0270383663225954</v>
-      </c>
-      <c r="U15" s="71" t="n">
-        <v>0.02657929588730763</v>
-      </c>
-      <c r="V15" s="71" t="n">
-        <v>0.02687966681844941</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="68" t="inlineStr">
-        <is>
-          <t>Trader / Execution</t>
-        </is>
-      </c>
-      <c r="B16" s="69" t="n">
-        <v>0.01268391679350583</v>
-      </c>
-      <c r="C16" s="69" t="n">
-        <v>0.01032784546227574</v>
-      </c>
-      <c r="D16" s="69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="69" t="n">
-        <v>0.01214846055607099</v>
-      </c>
-      <c r="F16" s="69" t="n">
-        <v>0.01940428530535444</v>
-      </c>
-      <c r="G16" s="69" t="n">
-        <v>0.01881572183505967</v>
-      </c>
-      <c r="H16" s="69" t="n">
-        <v>0.02027173038858719</v>
-      </c>
-      <c r="I16" s="69" t="n">
-        <v>0.02999233921149815</v>
-      </c>
-      <c r="J16" s="69" t="n">
-        <v>0.02834731739911558</v>
-      </c>
-      <c r="K16" s="69" t="n">
-        <v>0.02681422535657876</v>
-      </c>
-      <c r="L16" s="69" t="n">
-        <v>0.02293236143202949</v>
-      </c>
-      <c r="M16" s="69" t="n">
-        <v>0.02261317853346413</v>
-      </c>
-      <c r="N16" s="69" t="n">
-        <v>0.02442902861034774</v>
-      </c>
-      <c r="O16" s="69" t="n">
-        <v>0.02543483353706967</v>
-      </c>
-      <c r="P16" s="69" t="n">
-        <v>0.02289710921190028</v>
-      </c>
-      <c r="Q16" s="69" t="n">
-        <v>0.03279247974218098</v>
-      </c>
-      <c r="R16" s="69" t="n">
-        <v>0.03275603424170494</v>
-      </c>
-      <c r="S16" s="69" t="n">
-        <v>0.03282243898359496</v>
-      </c>
-      <c r="T16" s="69" t="n">
-        <v>0.03004262924732822</v>
-      </c>
-      <c r="U16" s="69" t="n">
-        <v>0.02953255098589737</v>
-      </c>
-      <c r="V16" s="69" t="n">
-        <v>0.02986629646494378</v>
+      <c r="E16" s="71" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="F16" s="71" t="n">
+        <v>0.0179372197309417</v>
+      </c>
+      <c r="G16" s="71" t="n">
+        <v>0.01721911321566939</v>
+      </c>
+      <c r="H16" s="71" t="n">
+        <v>0.01655629139072848</v>
+      </c>
+      <c r="I16" s="71" t="n">
+        <v>0.01594260661618175</v>
+      </c>
+      <c r="J16" s="71" t="n">
+        <v>0.01537279016141429</v>
+      </c>
+      <c r="K16" s="71" t="n">
+        <v>0.01484230055658627</v>
+      </c>
+      <c r="L16" s="71" t="n">
+        <v>0.01442741208295762</v>
+      </c>
+      <c r="M16" s="71" t="n">
+        <v>0.01403508771929825</v>
+      </c>
+      <c r="N16" s="71" t="n">
+        <v>0.01366353543979505</v>
+      </c>
+      <c r="O16" s="71" t="n">
+        <v>0.01331114808652246</v>
+      </c>
+      <c r="P16" s="71" t="n">
+        <v>0.0129764801297648</v>
+      </c>
+      <c r="Q16" s="71" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="R16" s="71" t="n">
+        <v>0.01235521235521236</v>
+      </c>
+      <c r="S16" s="71" t="n">
+        <v>0.01206636500754148</v>
+      </c>
+      <c r="T16" s="71" t="n">
+        <v>0.01179071481208548</v>
+      </c>
+      <c r="U16" s="71" t="n">
+        <v>0.01152737752161383</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="70" t="inlineStr">
-        <is>
-          <t>COO / Head of Operations</t>
-        </is>
-      </c>
-      <c r="B17" s="71" t="n">
-        <v>0.060882800608828</v>
-      </c>
-      <c r="C17" s="71" t="n">
-        <v>0.062716535371342</v>
-      </c>
-      <c r="D17" s="71" t="n">
-        <v>0.07075471698113207</v>
-      </c>
-      <c r="E17" s="71" t="n">
-        <v>0.06129954720871834</v>
-      </c>
-      <c r="F17" s="71" t="n">
-        <v>0.05565232511611565</v>
-      </c>
-      <c r="G17" s="71" t="n">
-        <v>0.05611040517554319</v>
-      </c>
-      <c r="H17" s="71" t="n">
-        <v>0.05497719097114678</v>
-      </c>
-      <c r="I17" s="71" t="n">
-        <v>0.0474116227835038</v>
-      </c>
-      <c r="J17" s="71" t="n">
-        <v>0.04252097609867338</v>
-      </c>
-      <c r="K17" s="71" t="n">
-        <v>0.04022133803486813</v>
-      </c>
-      <c r="L17" s="71" t="n">
-        <v>0.03439854214804424</v>
-      </c>
-      <c r="M17" s="71" t="n">
-        <v>0.03355654842657722</v>
-      </c>
-      <c r="N17" s="71" t="n">
-        <v>0.0366435429155216</v>
-      </c>
-      <c r="O17" s="71" t="n">
-        <v>0.03815225030560451</v>
-      </c>
-      <c r="P17" s="71" t="n">
-        <v>0.03434566381785042</v>
-      </c>
-      <c r="Q17" s="71" t="n">
-        <v>0.02459435980663573</v>
-      </c>
-      <c r="R17" s="71" t="n">
-        <v>0.0245670256812787</v>
-      </c>
-      <c r="S17" s="71" t="n">
-        <v>0.02461682923769622</v>
-      </c>
-      <c r="T17" s="71" t="n">
-        <v>0.02253197193549616</v>
-      </c>
-      <c r="U17" s="71" t="n">
-        <v>0.02214941323942303</v>
-      </c>
-      <c r="V17" s="71" t="n">
-        <v>0.02239972234870784</v>
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>Investor Relations / Ops</t>
+        </is>
+      </c>
+      <c r="B17" s="69" t="n">
+        <v>0.02358490566037736</v>
+      </c>
+      <c r="C17" s="69" t="n">
+        <v>0.01872659176029963</v>
+      </c>
+      <c r="D17" s="69" t="n">
+        <v>0.01552795031055901</v>
+      </c>
+      <c r="E17" s="69" t="n">
+        <v>0.01302083333333333</v>
+      </c>
+      <c r="F17" s="69" t="n">
+        <v>0.01121076233183856</v>
+      </c>
+      <c r="G17" s="69" t="n">
+        <v>0.01291433491175204</v>
+      </c>
+      <c r="H17" s="69" t="n">
+        <v>0.01448675496688742</v>
+      </c>
+      <c r="I17" s="69" t="n">
+        <v>0.01594260661618175</v>
+      </c>
+      <c r="J17" s="69" t="n">
+        <v>0.01729438893159108</v>
+      </c>
+      <c r="K17" s="69" t="n">
+        <v>0.01855287569573284</v>
+      </c>
+      <c r="L17" s="69" t="n">
+        <v>0.01893597835888187</v>
+      </c>
+      <c r="M17" s="69" t="n">
+        <v>0.01929824561403509</v>
+      </c>
+      <c r="N17" s="69" t="n">
+        <v>0.01964133219470538</v>
+      </c>
+      <c r="O17" s="69" t="n">
+        <v>0.01996672212978369</v>
+      </c>
+      <c r="P17" s="69" t="n">
+        <v>0.0202757502027575</v>
+      </c>
+      <c r="Q17" s="69" t="n">
+        <v>0.02056962025316456</v>
+      </c>
+      <c r="R17" s="69" t="n">
+        <v>0.02084942084942085</v>
+      </c>
+      <c r="S17" s="69" t="n">
+        <v>0.02111613876319759</v>
+      </c>
+      <c r="T17" s="69" t="n">
+        <v>0.02137067059690494</v>
+      </c>
+      <c r="U17" s="69" t="n">
+        <v>0.02161383285302594</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="68" t="inlineStr">
-        <is>
-          <t>CFO / Finance</t>
-        </is>
-      </c>
-      <c r="B18" s="69" t="n">
-        <v>0.015220700152207</v>
-      </c>
-      <c r="C18" s="69" t="n">
-        <v>0.01239341455473089</v>
-      </c>
-      <c r="D18" s="69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="69" t="n">
-        <v>0.01457815266728519</v>
-      </c>
-      <c r="F18" s="69" t="n">
-        <v>0.02328514236642533</v>
-      </c>
-      <c r="G18" s="69" t="n">
-        <v>0.02257886620207161</v>
-      </c>
-      <c r="H18" s="69" t="n">
-        <v>0.02432607646630463</v>
-      </c>
-      <c r="I18" s="69" t="n">
-        <v>0.03599080705379777</v>
-      </c>
-      <c r="J18" s="69" t="n">
-        <v>0.0340167808789387</v>
-      </c>
-      <c r="K18" s="69" t="n">
-        <v>0.03217707042789451</v>
-      </c>
-      <c r="L18" s="69" t="n">
-        <v>0.02751883371843539</v>
-      </c>
-      <c r="M18" s="69" t="n">
-        <v>0.02684523874126177</v>
-      </c>
-      <c r="N18" s="69" t="n">
-        <v>0.02931483433241728</v>
-      </c>
-      <c r="O18" s="69" t="n">
-        <v>0.03052180024448361</v>
-      </c>
-      <c r="P18" s="69" t="n">
-        <v>0.02747653105428034</v>
-      </c>
-      <c r="Q18" s="69" t="n">
-        <v>0.01967548784530859</v>
-      </c>
-      <c r="R18" s="69" t="n">
-        <v>0.01965362054502296</v>
-      </c>
-      <c r="S18" s="69" t="n">
-        <v>0.01969346339015698</v>
-      </c>
-      <c r="T18" s="69" t="n">
-        <v>0.01802557754839693</v>
-      </c>
-      <c r="U18" s="69" t="n">
-        <v>0.01771953059153842</v>
-      </c>
-      <c r="V18" s="69" t="n">
-        <v>0.01791977787896627</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="70" t="inlineStr">
-        <is>
-          <t>Compliance / Legal</t>
-        </is>
-      </c>
-      <c r="B19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="71" t="n">
-        <v>0.00562686320957922</v>
-      </c>
-      <c r="K19" s="71" t="n">
-        <v>0.008811738291494453</v>
-      </c>
-      <c r="L19" s="71" t="n">
-        <v>0.01687599754120324</v>
-      </c>
-      <c r="M19" s="71" t="n">
-        <v>0.01789682582750785</v>
-      </c>
-      <c r="N19" s="71" t="n">
-        <v>0.01376679217721309</v>
-      </c>
-      <c r="O19" s="71" t="n">
-        <v>0.01167731355524881</v>
-      </c>
-      <c r="P19" s="71" t="n">
-        <v>0.0169492311856007</v>
-      </c>
-      <c r="Q19" s="71" t="n">
-        <v>0.01311699189687239</v>
-      </c>
-      <c r="R19" s="71" t="n">
-        <v>0.01310241369668197</v>
-      </c>
-      <c r="S19" s="71" t="n">
-        <v>0.01312897559343799</v>
-      </c>
-      <c r="T19" s="71" t="n">
-        <v>0.01201705169893129</v>
-      </c>
-      <c r="U19" s="71" t="n">
-        <v>0.01181302039435895</v>
-      </c>
-      <c r="V19" s="71" t="n">
-        <v>0.01194651858597751</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="68" t="inlineStr">
-        <is>
-          <t>Investor Relations / Ops</t>
-        </is>
-      </c>
-      <c r="B20" s="69" t="n">
-        <v>0.02029426686960933</v>
-      </c>
-      <c r="C20" s="69" t="n">
-        <v>0.02090551179044733</v>
-      </c>
-      <c r="D20" s="69" t="n">
-        <v>0.02358490566037736</v>
-      </c>
-      <c r="E20" s="69" t="n">
-        <v>0.02043318240290611</v>
-      </c>
-      <c r="F20" s="69" t="n">
-        <v>0.01855077503870522</v>
-      </c>
-      <c r="G20" s="69" t="n">
-        <v>0.01870346839184773</v>
-      </c>
-      <c r="H20" s="69" t="n">
-        <v>0.01832573032371559</v>
-      </c>
-      <c r="I20" s="69" t="n">
-        <v>0.01580387426116793</v>
-      </c>
-      <c r="J20" s="69" t="n">
-        <v>0.01417365869955779</v>
-      </c>
-      <c r="K20" s="69" t="n">
-        <v>0.01340711267828938</v>
-      </c>
-      <c r="L20" s="69" t="n">
-        <v>0.01146618071601475</v>
-      </c>
-      <c r="M20" s="69" t="n">
-        <v>0.01130658926673206</v>
-      </c>
-      <c r="N20" s="69" t="n">
-        <v>0.01221451430517387</v>
-      </c>
-      <c r="O20" s="69" t="n">
-        <v>0.01271741676853484</v>
-      </c>
-      <c r="P20" s="69" t="n">
-        <v>0.01144855460595014</v>
-      </c>
-      <c r="Q20" s="69" t="n">
-        <v>0.02014600345006541</v>
-      </c>
-      <c r="R20" s="69" t="n">
-        <v>0.02015946477201543</v>
-      </c>
-      <c r="S20" s="69" t="n">
-        <v>0.02013493785928508</v>
-      </c>
-      <c r="T20" s="69" t="n">
-        <v>0.02116167403606749</v>
-      </c>
-      <c r="U20" s="69" t="n">
-        <v>0.02135007391004758</v>
-      </c>
-      <c r="V20" s="69" t="n">
-        <v>0.02122680340246431</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="72" t="inlineStr">
+      <c r="A18" s="72" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B21" s="73">
-        <f>SUM(B8:B20)</f>
-        <v/>
-      </c>
-      <c r="C21" s="73">
-        <f>SUM(C8:C20)</f>
-        <v/>
-      </c>
-      <c r="D21" s="73">
-        <f>SUM(D8:D20)</f>
-        <v/>
-      </c>
-      <c r="E21" s="73">
-        <f>SUM(E8:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="73">
-        <f>SUM(F8:F20)</f>
-        <v/>
-      </c>
-      <c r="G21" s="73">
-        <f>SUM(G8:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="73">
-        <f>SUM(H8:H20)</f>
-        <v/>
-      </c>
-      <c r="I21" s="73">
-        <f>SUM(I8:I20)</f>
-        <v/>
-      </c>
-      <c r="J21" s="73">
-        <f>SUM(J8:J20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="73">
-        <f>SUM(K8:K20)</f>
-        <v/>
-      </c>
-      <c r="L21" s="73">
-        <f>SUM(L8:L20)</f>
-        <v/>
-      </c>
-      <c r="M21" s="73">
-        <f>SUM(M8:M20)</f>
-        <v/>
-      </c>
-      <c r="N21" s="73">
-        <f>SUM(N8:N20)</f>
-        <v/>
-      </c>
-      <c r="O21" s="73">
-        <f>SUM(O8:O20)</f>
-        <v/>
-      </c>
-      <c r="P21" s="73">
-        <f>SUM(P8:P20)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="73">
-        <f>SUM(Q8:Q20)</f>
-        <v/>
-      </c>
-      <c r="R21" s="73">
-        <f>SUM(R8:R20)</f>
-        <v/>
-      </c>
-      <c r="S21" s="73">
-        <f>SUM(S8:S20)</f>
-        <v/>
-      </c>
-      <c r="T21" s="73">
-        <f>SUM(T8:T20)</f>
-        <v/>
-      </c>
-      <c r="U21" s="73">
-        <f>SUM(U8:U20)</f>
-        <v/>
-      </c>
-      <c r="V21" s="73">
-        <f>SUM(V8:V20)</f>
+      <c r="B18" s="73">
+        <f>SUM(B5:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="73">
+        <f>SUM(C5:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="73">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="73">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="73">
+        <f>SUM(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="73">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="73">
+        <f>SUM(H5:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="73">
+        <f>SUM(I5:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="73">
+        <f>SUM(J5:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="73">
+        <f>SUM(K5:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="73">
+        <f>SUM(L5:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="73">
+        <f>SUM(M5:M17)</f>
+        <v/>
+      </c>
+      <c r="N18" s="73">
+        <f>SUM(N5:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="73">
+        <f>SUM(O5:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="73">
+        <f>SUM(P5:P17)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="73">
+        <f>SUM(Q5:Q17)</f>
+        <v/>
+      </c>
+      <c r="R18" s="73">
+        <f>SUM(R5:R17)</f>
+        <v/>
+      </c>
+      <c r="S18" s="73">
+        <f>SUM(S5:S17)</f>
+        <v/>
+      </c>
+      <c r="T18" s="73">
+        <f>SUM(T5:T17)</f>
+        <v/>
+      </c>
+      <c r="U18" s="73">
+        <f>SUM(U5:U17)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A1:V1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -8,7 +8,8 @@
   <sheets>
     <sheet name="Static" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Take by AUM" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Take per Person" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -330,7 +331,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,6 +495,12 @@
     <xf numFmtId="3" fontId="25" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +580,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1075,6 +1081,510 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Per-person share of the take vs AUM</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$5:$U$5</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$6:$U$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$7:$U$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$8:$U$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$9:$U$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$10:$U$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$11:$U$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$12:$U$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$13:$U$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$14:$U$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="10"/>
+          <order val="10"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$15:$U$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$16:$U$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$17:$U$17</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>AUM (USD m)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of take per person</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -1102,6 +1612,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -5110,6 +5647,1067 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="7" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Share of the take PER PERSON, by role, as AUM grows $100m → $2bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Per-person share = role weight ÷ total weighted units. One individual's slice — declines for every role as the firm hires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="72" t="inlineStr">
+        <is>
+          <t>AUM (USD m) →</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="74" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="74" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="74" t="n">
+        <v>400</v>
+      </c>
+      <c r="F4" s="74" t="n">
+        <v>500</v>
+      </c>
+      <c r="G4" s="74" t="n">
+        <v>600</v>
+      </c>
+      <c r="H4" s="74" t="n">
+        <v>700</v>
+      </c>
+      <c r="I4" s="74" t="n">
+        <v>800</v>
+      </c>
+      <c r="J4" s="74" t="n">
+        <v>900</v>
+      </c>
+      <c r="K4" s="74" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" s="74" t="n">
+        <v>1100</v>
+      </c>
+      <c r="M4" s="74" t="n">
+        <v>1200</v>
+      </c>
+      <c r="N4" s="74" t="n">
+        <v>1300</v>
+      </c>
+      <c r="O4" s="74" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P4" s="74" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Q4" s="74" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R4" s="74" t="n">
+        <v>1700</v>
+      </c>
+      <c r="S4" s="74" t="n">
+        <v>1800</v>
+      </c>
+      <c r="T4" s="74" t="n">
+        <v>1900</v>
+      </c>
+      <c r="U4" s="74" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="68" t="inlineStr">
+        <is>
+          <t>Managing Partner / CIO  (wt 100)</t>
+        </is>
+      </c>
+      <c r="B5" s="75" t="n">
+        <v>0.4716981132075472</v>
+      </c>
+      <c r="C5" s="75" t="n">
+        <v>0.3745318352059925</v>
+      </c>
+      <c r="D5" s="75" t="n">
+        <v>0.3105590062111801</v>
+      </c>
+      <c r="E5" s="75" t="n">
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="F5" s="75" t="n">
+        <v>0.2242152466367713</v>
+      </c>
+      <c r="G5" s="75" t="n">
+        <v>0.2152389151958674</v>
+      </c>
+      <c r="H5" s="75" t="n">
+        <v>0.206953642384106</v>
+      </c>
+      <c r="I5" s="75" t="n">
+        <v>0.1992825827022718</v>
+      </c>
+      <c r="J5" s="75" t="n">
+        <v>0.1921598770176787</v>
+      </c>
+      <c r="K5" s="75" t="n">
+        <v>0.1855287569573284</v>
+      </c>
+      <c r="L5" s="75" t="n">
+        <v>0.1803426510369703</v>
+      </c>
+      <c r="M5" s="75" t="n">
+        <v>0.1754385964912281</v>
+      </c>
+      <c r="N5" s="75" t="n">
+        <v>0.1707941929974381</v>
+      </c>
+      <c r="O5" s="75" t="n">
+        <v>0.1663893510815308</v>
+      </c>
+      <c r="P5" s="75" t="n">
+        <v>0.16220600162206</v>
+      </c>
+      <c r="Q5" s="75" t="n">
+        <v>0.1582278481012658</v>
+      </c>
+      <c r="R5" s="75" t="n">
+        <v>0.1544401544401544</v>
+      </c>
+      <c r="S5" s="75" t="n">
+        <v>0.1508295625942685</v>
+      </c>
+      <c r="T5" s="75" t="n">
+        <v>0.1473839351510685</v>
+      </c>
+      <c r="U5" s="75" t="n">
+        <v>0.1440922190201729</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>Partner / Co-PM  (wt 60)</t>
+        </is>
+      </c>
+      <c r="B6" s="76" t="n">
+        <v>0.2830188679245283</v>
+      </c>
+      <c r="C6" s="76" t="n">
+        <v>0.2247191011235955</v>
+      </c>
+      <c r="D6" s="76" t="n">
+        <v>0.1863354037267081</v>
+      </c>
+      <c r="E6" s="76" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="F6" s="76" t="n">
+        <v>0.1345291479820628</v>
+      </c>
+      <c r="G6" s="76" t="n">
+        <v>0.1291433491175205</v>
+      </c>
+      <c r="H6" s="76" t="n">
+        <v>0.1241721854304636</v>
+      </c>
+      <c r="I6" s="76" t="n">
+        <v>0.1195695496213631</v>
+      </c>
+      <c r="J6" s="76" t="n">
+        <v>0.1152959262106072</v>
+      </c>
+      <c r="K6" s="76" t="n">
+        <v>0.111317254174397</v>
+      </c>
+      <c r="L6" s="76" t="n">
+        <v>0.1082055906221821</v>
+      </c>
+      <c r="M6" s="76" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="N6" s="76" t="n">
+        <v>0.1024765157984629</v>
+      </c>
+      <c r="O6" s="76" t="n">
+        <v>0.09983361064891846</v>
+      </c>
+      <c r="P6" s="76" t="n">
+        <v>0.09732360097323602</v>
+      </c>
+      <c r="Q6" s="76" t="n">
+        <v>0.0949367088607595</v>
+      </c>
+      <c r="R6" s="76" t="n">
+        <v>0.09266409266409266</v>
+      </c>
+      <c r="S6" s="76" t="n">
+        <v>0.09049773755656108</v>
+      </c>
+      <c r="T6" s="76" t="n">
+        <v>0.08843036109064112</v>
+      </c>
+      <c r="U6" s="76" t="n">
+        <v>0.08645533141210375</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="68" t="inlineStr">
+        <is>
+          <t>Portfolio Manager  (wt 40)</t>
+        </is>
+      </c>
+      <c r="B7" s="75" t="n">
+        <v>0.1886792452830189</v>
+      </c>
+      <c r="C7" s="75" t="n">
+        <v>0.149812734082397</v>
+      </c>
+      <c r="D7" s="75" t="n">
+        <v>0.124223602484472</v>
+      </c>
+      <c r="E7" s="75" t="n">
+        <v>0.1041666666666667</v>
+      </c>
+      <c r="F7" s="75" t="n">
+        <v>0.08968609865470852</v>
+      </c>
+      <c r="G7" s="75" t="n">
+        <v>0.08609556607834697</v>
+      </c>
+      <c r="H7" s="75" t="n">
+        <v>0.08278145695364239</v>
+      </c>
+      <c r="I7" s="75" t="n">
+        <v>0.07971303308090873</v>
+      </c>
+      <c r="J7" s="75" t="n">
+        <v>0.07686395080707147</v>
+      </c>
+      <c r="K7" s="75" t="n">
+        <v>0.07421150278293136</v>
+      </c>
+      <c r="L7" s="75" t="n">
+        <v>0.0721370604147881</v>
+      </c>
+      <c r="M7" s="75" t="n">
+        <v>0.07017543859649122</v>
+      </c>
+      <c r="N7" s="75" t="n">
+        <v>0.06831767719897523</v>
+      </c>
+      <c r="O7" s="75" t="n">
+        <v>0.06655574043261231</v>
+      </c>
+      <c r="P7" s="75" t="n">
+        <v>0.064882400648824</v>
+      </c>
+      <c r="Q7" s="75" t="n">
+        <v>0.06329113924050633</v>
+      </c>
+      <c r="R7" s="75" t="n">
+        <v>0.06177606177606178</v>
+      </c>
+      <c r="S7" s="75" t="n">
+        <v>0.06033182503770739</v>
+      </c>
+      <c r="T7" s="75" t="n">
+        <v>0.05895357406042741</v>
+      </c>
+      <c r="U7" s="75" t="n">
+        <v>0.05763688760806916</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>Head of Research  (wt 30)</t>
+        </is>
+      </c>
+      <c r="B8" s="76" t="n">
+        <v>0.1415094339622641</v>
+      </c>
+      <c r="C8" s="76" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="D8" s="76" t="n">
+        <v>0.09316770186335403</v>
+      </c>
+      <c r="E8" s="76" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="F8" s="76" t="n">
+        <v>0.06726457399103139</v>
+      </c>
+      <c r="G8" s="76" t="n">
+        <v>0.06457167455876023</v>
+      </c>
+      <c r="H8" s="76" t="n">
+        <v>0.06208609271523179</v>
+      </c>
+      <c r="I8" s="76" t="n">
+        <v>0.05978477481068155</v>
+      </c>
+      <c r="J8" s="76" t="n">
+        <v>0.0576479631053036</v>
+      </c>
+      <c r="K8" s="76" t="n">
+        <v>0.05565862708719851</v>
+      </c>
+      <c r="L8" s="76" t="n">
+        <v>0.05410279531109107</v>
+      </c>
+      <c r="M8" s="76" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="N8" s="76" t="n">
+        <v>0.05123825789923143</v>
+      </c>
+      <c r="O8" s="76" t="n">
+        <v>0.04991680532445923</v>
+      </c>
+      <c r="P8" s="76" t="n">
+        <v>0.04866180048661801</v>
+      </c>
+      <c r="Q8" s="76" t="n">
+        <v>0.04746835443037975</v>
+      </c>
+      <c r="R8" s="76" t="n">
+        <v>0.04633204633204633</v>
+      </c>
+      <c r="S8" s="76" t="n">
+        <v>0.04524886877828054</v>
+      </c>
+      <c r="T8" s="76" t="n">
+        <v>0.04421518054532056</v>
+      </c>
+      <c r="U8" s="76" t="n">
+        <v>0.04322766570605188</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="68" t="inlineStr">
+        <is>
+          <t>Senior Analyst  (wt 20)</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="n">
+        <v>0.09433962264150944</v>
+      </c>
+      <c r="C9" s="75" t="n">
+        <v>0.0749063670411985</v>
+      </c>
+      <c r="D9" s="75" t="n">
+        <v>0.06211180124223602</v>
+      </c>
+      <c r="E9" s="75" t="n">
+        <v>0.05208333333333334</v>
+      </c>
+      <c r="F9" s="75" t="n">
+        <v>0.04484304932735426</v>
+      </c>
+      <c r="G9" s="75" t="n">
+        <v>0.04304778303917348</v>
+      </c>
+      <c r="H9" s="75" t="n">
+        <v>0.0413907284768212</v>
+      </c>
+      <c r="I9" s="75" t="n">
+        <v>0.03985651654045436</v>
+      </c>
+      <c r="J9" s="75" t="n">
+        <v>0.03843197540353573</v>
+      </c>
+      <c r="K9" s="75" t="n">
+        <v>0.03710575139146568</v>
+      </c>
+      <c r="L9" s="75" t="n">
+        <v>0.03606853020739405</v>
+      </c>
+      <c r="M9" s="75" t="n">
+        <v>0.03508771929824561</v>
+      </c>
+      <c r="N9" s="75" t="n">
+        <v>0.03415883859948762</v>
+      </c>
+      <c r="O9" s="75" t="n">
+        <v>0.03327787021630615</v>
+      </c>
+      <c r="P9" s="75" t="n">
+        <v>0.032441200324412</v>
+      </c>
+      <c r="Q9" s="75" t="n">
+        <v>0.03164556962025317</v>
+      </c>
+      <c r="R9" s="75" t="n">
+        <v>0.03088803088803089</v>
+      </c>
+      <c r="S9" s="75" t="n">
+        <v>0.0301659125188537</v>
+      </c>
+      <c r="T9" s="75" t="n">
+        <v>0.02947678703021371</v>
+      </c>
+      <c r="U9" s="75" t="n">
+        <v>0.02881844380403458</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>Analyst  (wt 12)</t>
+        </is>
+      </c>
+      <c r="B10" s="76" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="C10" s="76" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="D10" s="76" t="n">
+        <v>0.03726708074534162</v>
+      </c>
+      <c r="E10" s="76" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="F10" s="76" t="n">
+        <v>0.02690582959641256</v>
+      </c>
+      <c r="G10" s="76" t="n">
+        <v>0.02582866982350409</v>
+      </c>
+      <c r="H10" s="76" t="n">
+        <v>0.02483443708609272</v>
+      </c>
+      <c r="I10" s="76" t="n">
+        <v>0.02391390992427262</v>
+      </c>
+      <c r="J10" s="76" t="n">
+        <v>0.02305918524212144</v>
+      </c>
+      <c r="K10" s="76" t="n">
+        <v>0.02226345083487941</v>
+      </c>
+      <c r="L10" s="76" t="n">
+        <v>0.02164111812443643</v>
+      </c>
+      <c r="M10" s="76" t="n">
+        <v>0.02105263157894737</v>
+      </c>
+      <c r="N10" s="76" t="n">
+        <v>0.02049530315969257</v>
+      </c>
+      <c r="O10" s="76" t="n">
+        <v>0.01996672212978369</v>
+      </c>
+      <c r="P10" s="76" t="n">
+        <v>0.0194647201946472</v>
+      </c>
+      <c r="Q10" s="76" t="n">
+        <v>0.0189873417721519</v>
+      </c>
+      <c r="R10" s="76" t="n">
+        <v>0.01853281853281853</v>
+      </c>
+      <c r="S10" s="76" t="n">
+        <v>0.01809954751131222</v>
+      </c>
+      <c r="T10" s="76" t="n">
+        <v>0.01768607221812822</v>
+      </c>
+      <c r="U10" s="76" t="n">
+        <v>0.01729106628242075</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="68" t="inlineStr">
+        <is>
+          <t>Junior Analyst  (wt 6)</t>
+        </is>
+      </c>
+      <c r="B11" s="75" t="n">
+        <v>0.02830188679245283</v>
+      </c>
+      <c r="C11" s="75" t="n">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="D11" s="75" t="n">
+        <v>0.01863354037267081</v>
+      </c>
+      <c r="E11" s="75" t="n">
+        <v>0.015625</v>
+      </c>
+      <c r="F11" s="75" t="n">
+        <v>0.01345291479820628</v>
+      </c>
+      <c r="G11" s="75" t="n">
+        <v>0.01291433491175204</v>
+      </c>
+      <c r="H11" s="75" t="n">
+        <v>0.01241721854304636</v>
+      </c>
+      <c r="I11" s="75" t="n">
+        <v>0.01195695496213631</v>
+      </c>
+      <c r="J11" s="75" t="n">
+        <v>0.01152959262106072</v>
+      </c>
+      <c r="K11" s="75" t="n">
+        <v>0.0111317254174397</v>
+      </c>
+      <c r="L11" s="75" t="n">
+        <v>0.01082055906221822</v>
+      </c>
+      <c r="M11" s="75" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="N11" s="75" t="n">
+        <v>0.01024765157984629</v>
+      </c>
+      <c r="O11" s="75" t="n">
+        <v>0.009983361064891847</v>
+      </c>
+      <c r="P11" s="75" t="n">
+        <v>0.009732360097323601</v>
+      </c>
+      <c r="Q11" s="75" t="n">
+        <v>0.00949367088607595</v>
+      </c>
+      <c r="R11" s="75" t="n">
+        <v>0.009266409266409266</v>
+      </c>
+      <c r="S11" s="75" t="n">
+        <v>0.009049773755656109</v>
+      </c>
+      <c r="T11" s="75" t="n">
+        <v>0.008843036109064112</v>
+      </c>
+      <c r="U11" s="75" t="n">
+        <v>0.008645533141210375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>Head of Trading  (wt 18)</t>
+        </is>
+      </c>
+      <c r="B12" s="76" t="n">
+        <v>0.08490566037735849</v>
+      </c>
+      <c r="C12" s="76" t="n">
+        <v>0.06741573033707865</v>
+      </c>
+      <c r="D12" s="76" t="n">
+        <v>0.05590062111801242</v>
+      </c>
+      <c r="E12" s="76" t="n">
+        <v>0.046875</v>
+      </c>
+      <c r="F12" s="76" t="n">
+        <v>0.04035874439461883</v>
+      </c>
+      <c r="G12" s="76" t="n">
+        <v>0.03874300473525614</v>
+      </c>
+      <c r="H12" s="76" t="n">
+        <v>0.03725165562913908</v>
+      </c>
+      <c r="I12" s="76" t="n">
+        <v>0.03587086488640893</v>
+      </c>
+      <c r="J12" s="76" t="n">
+        <v>0.03458877786318216</v>
+      </c>
+      <c r="K12" s="76" t="n">
+        <v>0.03339517625231911</v>
+      </c>
+      <c r="L12" s="76" t="n">
+        <v>0.03246167718665464</v>
+      </c>
+      <c r="M12" s="76" t="n">
+        <v>0.03157894736842105</v>
+      </c>
+      <c r="N12" s="76" t="n">
+        <v>0.03074295473953886</v>
+      </c>
+      <c r="O12" s="76" t="n">
+        <v>0.02995008319467554</v>
+      </c>
+      <c r="P12" s="76" t="n">
+        <v>0.0291970802919708</v>
+      </c>
+      <c r="Q12" s="76" t="n">
+        <v>0.02848101265822785</v>
+      </c>
+      <c r="R12" s="76" t="n">
+        <v>0.0277992277992278</v>
+      </c>
+      <c r="S12" s="76" t="n">
+        <v>0.02714932126696833</v>
+      </c>
+      <c r="T12" s="76" t="n">
+        <v>0.02652910832719233</v>
+      </c>
+      <c r="U12" s="76" t="n">
+        <v>0.02593659942363112</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="68" t="inlineStr">
+        <is>
+          <t>Trader / Execution  (wt 10)</t>
+        </is>
+      </c>
+      <c r="B13" s="75" t="n">
+        <v>0.04716981132075472</v>
+      </c>
+      <c r="C13" s="75" t="n">
+        <v>0.03745318352059925</v>
+      </c>
+      <c r="D13" s="75" t="n">
+        <v>0.03105590062111801</v>
+      </c>
+      <c r="E13" s="75" t="n">
+        <v>0.02604166666666667</v>
+      </c>
+      <c r="F13" s="75" t="n">
+        <v>0.02242152466367713</v>
+      </c>
+      <c r="G13" s="75" t="n">
+        <v>0.02152389151958674</v>
+      </c>
+      <c r="H13" s="75" t="n">
+        <v>0.0206953642384106</v>
+      </c>
+      <c r="I13" s="75" t="n">
+        <v>0.01992825827022718</v>
+      </c>
+      <c r="J13" s="75" t="n">
+        <v>0.01921598770176787</v>
+      </c>
+      <c r="K13" s="75" t="n">
+        <v>0.01855287569573284</v>
+      </c>
+      <c r="L13" s="75" t="n">
+        <v>0.01803426510369702</v>
+      </c>
+      <c r="M13" s="75" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+      <c r="N13" s="75" t="n">
+        <v>0.01707941929974381</v>
+      </c>
+      <c r="O13" s="75" t="n">
+        <v>0.01663893510815308</v>
+      </c>
+      <c r="P13" s="75" t="n">
+        <v>0.016220600162206</v>
+      </c>
+      <c r="Q13" s="75" t="n">
+        <v>0.01582278481012658</v>
+      </c>
+      <c r="R13" s="75" t="n">
+        <v>0.01544401544401544</v>
+      </c>
+      <c r="S13" s="75" t="n">
+        <v>0.01508295625942685</v>
+      </c>
+      <c r="T13" s="75" t="n">
+        <v>0.01473839351510685</v>
+      </c>
+      <c r="U13" s="75" t="n">
+        <v>0.01440922190201729</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="70" t="inlineStr">
+        <is>
+          <t>COO / Head of Operations  (wt 15)</t>
+        </is>
+      </c>
+      <c r="B14" s="76" t="n">
+        <v>0.07075471698113207</v>
+      </c>
+      <c r="C14" s="76" t="n">
+        <v>0.05617977528089887</v>
+      </c>
+      <c r="D14" s="76" t="n">
+        <v>0.04658385093167702</v>
+      </c>
+      <c r="E14" s="76" t="n">
+        <v>0.0390625</v>
+      </c>
+      <c r="F14" s="76" t="n">
+        <v>0.0336322869955157</v>
+      </c>
+      <c r="G14" s="76" t="n">
+        <v>0.03228583727938011</v>
+      </c>
+      <c r="H14" s="76" t="n">
+        <v>0.0310430463576159</v>
+      </c>
+      <c r="I14" s="76" t="n">
+        <v>0.02989238740534077</v>
+      </c>
+      <c r="J14" s="76" t="n">
+        <v>0.0288239815526518</v>
+      </c>
+      <c r="K14" s="76" t="n">
+        <v>0.02782931354359926</v>
+      </c>
+      <c r="L14" s="76" t="n">
+        <v>0.02705139765554554</v>
+      </c>
+      <c r="M14" s="76" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="N14" s="76" t="n">
+        <v>0.02561912894961571</v>
+      </c>
+      <c r="O14" s="76" t="n">
+        <v>0.02495840266222962</v>
+      </c>
+      <c r="P14" s="76" t="n">
+        <v>0.024330900243309</v>
+      </c>
+      <c r="Q14" s="76" t="n">
+        <v>0.02373417721518987</v>
+      </c>
+      <c r="R14" s="76" t="n">
+        <v>0.02316602316602316</v>
+      </c>
+      <c r="S14" s="76" t="n">
+        <v>0.02262443438914027</v>
+      </c>
+      <c r="T14" s="76" t="n">
+        <v>0.02210759027266028</v>
+      </c>
+      <c r="U14" s="76" t="n">
+        <v>0.02161383285302594</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="68" t="inlineStr">
+        <is>
+          <t>CFO / Finance  (wt 12)</t>
+        </is>
+      </c>
+      <c r="B15" s="75" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="C15" s="75" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="D15" s="75" t="n">
+        <v>0.03726708074534162</v>
+      </c>
+      <c r="E15" s="75" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="F15" s="75" t="n">
+        <v>0.02690582959641256</v>
+      </c>
+      <c r="G15" s="75" t="n">
+        <v>0.02582866982350409</v>
+      </c>
+      <c r="H15" s="75" t="n">
+        <v>0.02483443708609272</v>
+      </c>
+      <c r="I15" s="75" t="n">
+        <v>0.02391390992427262</v>
+      </c>
+      <c r="J15" s="75" t="n">
+        <v>0.02305918524212144</v>
+      </c>
+      <c r="K15" s="75" t="n">
+        <v>0.02226345083487941</v>
+      </c>
+      <c r="L15" s="75" t="n">
+        <v>0.02164111812443643</v>
+      </c>
+      <c r="M15" s="75" t="n">
+        <v>0.02105263157894737</v>
+      </c>
+      <c r="N15" s="75" t="n">
+        <v>0.02049530315969257</v>
+      </c>
+      <c r="O15" s="75" t="n">
+        <v>0.01996672212978369</v>
+      </c>
+      <c r="P15" s="75" t="n">
+        <v>0.0194647201946472</v>
+      </c>
+      <c r="Q15" s="75" t="n">
+        <v>0.0189873417721519</v>
+      </c>
+      <c r="R15" s="75" t="n">
+        <v>0.01853281853281853</v>
+      </c>
+      <c r="S15" s="75" t="n">
+        <v>0.01809954751131222</v>
+      </c>
+      <c r="T15" s="75" t="n">
+        <v>0.01768607221812822</v>
+      </c>
+      <c r="U15" s="75" t="n">
+        <v>0.01729106628242075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>Compliance / Legal  (wt 8)</t>
+        </is>
+      </c>
+      <c r="B16" s="76" t="n">
+        <v>0.03773584905660377</v>
+      </c>
+      <c r="C16" s="76" t="n">
+        <v>0.0299625468164794</v>
+      </c>
+      <c r="D16" s="76" t="n">
+        <v>0.02484472049689441</v>
+      </c>
+      <c r="E16" s="76" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="F16" s="76" t="n">
+        <v>0.0179372197309417</v>
+      </c>
+      <c r="G16" s="76" t="n">
+        <v>0.01721911321566939</v>
+      </c>
+      <c r="H16" s="76" t="n">
+        <v>0.01655629139072848</v>
+      </c>
+      <c r="I16" s="76" t="n">
+        <v>0.01594260661618175</v>
+      </c>
+      <c r="J16" s="76" t="n">
+        <v>0.01537279016141429</v>
+      </c>
+      <c r="K16" s="76" t="n">
+        <v>0.01484230055658627</v>
+      </c>
+      <c r="L16" s="76" t="n">
+        <v>0.01442741208295762</v>
+      </c>
+      <c r="M16" s="76" t="n">
+        <v>0.01403508771929825</v>
+      </c>
+      <c r="N16" s="76" t="n">
+        <v>0.01366353543979505</v>
+      </c>
+      <c r="O16" s="76" t="n">
+        <v>0.01331114808652246</v>
+      </c>
+      <c r="P16" s="76" t="n">
+        <v>0.0129764801297648</v>
+      </c>
+      <c r="Q16" s="76" t="n">
+        <v>0.01265822784810127</v>
+      </c>
+      <c r="R16" s="76" t="n">
+        <v>0.01235521235521236</v>
+      </c>
+      <c r="S16" s="76" t="n">
+        <v>0.01206636500754148</v>
+      </c>
+      <c r="T16" s="76" t="n">
+        <v>0.01179071481208548</v>
+      </c>
+      <c r="U16" s="76" t="n">
+        <v>0.01152737752161383</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="68" t="inlineStr">
+        <is>
+          <t>Investor Relations / Ops  (wt 5)</t>
+        </is>
+      </c>
+      <c r="B17" s="75" t="n">
+        <v>0.02358490566037736</v>
+      </c>
+      <c r="C17" s="75" t="n">
+        <v>0.01872659176029963</v>
+      </c>
+      <c r="D17" s="75" t="n">
+        <v>0.01552795031055901</v>
+      </c>
+      <c r="E17" s="75" t="n">
+        <v>0.01302083333333333</v>
+      </c>
+      <c r="F17" s="75" t="n">
+        <v>0.01121076233183856</v>
+      </c>
+      <c r="G17" s="75" t="n">
+        <v>0.01076194575979337</v>
+      </c>
+      <c r="H17" s="75" t="n">
+        <v>0.0103476821192053</v>
+      </c>
+      <c r="I17" s="75" t="n">
+        <v>0.009964129135113591</v>
+      </c>
+      <c r="J17" s="75" t="n">
+        <v>0.009607993850883933</v>
+      </c>
+      <c r="K17" s="75" t="n">
+        <v>0.00927643784786642</v>
+      </c>
+      <c r="L17" s="75" t="n">
+        <v>0.009017132551848512</v>
+      </c>
+      <c r="M17" s="75" t="n">
+        <v>0.008771929824561403</v>
+      </c>
+      <c r="N17" s="75" t="n">
+        <v>0.008539709649871904</v>
+      </c>
+      <c r="O17" s="75" t="n">
+        <v>0.008319467554076539</v>
+      </c>
+      <c r="P17" s="75" t="n">
+        <v>0.008110300081103</v>
+      </c>
+      <c r="Q17" s="75" t="n">
+        <v>0.007911392405063292</v>
+      </c>
+      <c r="R17" s="75" t="n">
+        <v>0.007722007722007722</v>
+      </c>
+      <c r="S17" s="75" t="n">
+        <v>0.007541478129713424</v>
+      </c>
+      <c r="T17" s="75" t="n">
+        <v>0.007369196757553427</v>
+      </c>
+      <c r="U17" s="75" t="n">
+        <v>0.007204610951008645</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="72" t="inlineStr">
+        <is>
+          <t>Total units (denominator)</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="n">
+        <v>212</v>
+      </c>
+      <c r="C18" s="74" t="n">
+        <v>267</v>
+      </c>
+      <c r="D18" s="74" t="n">
+        <v>322</v>
+      </c>
+      <c r="E18" s="74" t="n">
+        <v>384</v>
+      </c>
+      <c r="F18" s="74" t="n">
+        <v>446</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>465</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <v>483</v>
+      </c>
+      <c r="I18" s="74" t="n">
+        <v>502</v>
+      </c>
+      <c r="J18" s="74" t="n">
+        <v>520</v>
+      </c>
+      <c r="K18" s="74" t="n">
+        <v>539</v>
+      </c>
+      <c r="L18" s="74" t="n">
+        <v>554</v>
+      </c>
+      <c r="M18" s="74" t="n">
+        <v>570</v>
+      </c>
+      <c r="N18" s="74" t="n">
+        <v>586</v>
+      </c>
+      <c r="O18" s="74" t="n">
+        <v>601</v>
+      </c>
+      <c r="P18" s="74" t="n">
+        <v>616</v>
+      </c>
+      <c r="Q18" s="74" t="n">
+        <v>632</v>
+      </c>
+      <c r="R18" s="74" t="n">
+        <v>648</v>
+      </c>
+      <c r="S18" s="74" t="n">
+        <v>663</v>
+      </c>
+      <c r="T18" s="74" t="n">
+        <v>678</v>
+      </c>
+      <c r="U18" s="74" t="n">
+        <v>694</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:U1"/>
+    <mergeCell ref="A2:U2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <sheetData>

--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -719,6 +719,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Take by AUM'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take by AUM'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take by AUM'!$B$16:$U$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Take by AUM'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take by AUM'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take by AUM'!$B$17:$U$17</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1159,6 +1223,70 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="11"/>
+          <order val="11"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$16:$U$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="12"/>
+          <order val="12"/>
+          <tx>
+            <strRef>
+              <f>'Take per Person'!A17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Take per Person'!$B$4:$U$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Take per Person'!$B$17:$U$17</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1231,7 +1359,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1258,7 +1386,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9360000" cy="3960000"/>
@@ -1568,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1975,17 +2103,17 @@
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Junior PM</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="18" t="n">
         <v>0.2</v>
       </c>
       <c r="D23" s="19" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="E23" s="20" t="inlineStr"/>
       <c r="F23" s="20" t="inlineStr"/>
@@ -1994,41 +2122,41 @@
         <v>0</v>
       </c>
       <c r="I23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L23" s="19" t="n">
-        <v>8</v>
-      </c>
       <c r="M23" s="19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Senior Analyst</t>
         </is>
       </c>
       <c r="B24" s="18" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D24" s="19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E24" s="21" t="inlineStr"/>
       <c r="F24" s="21" t="inlineStr"/>
       <c r="G24" s="21" t="inlineStr"/>
       <c r="H24" s="19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="19" t="n">
         <v>1</v>
@@ -2037,78 +2165,78 @@
         <v>1</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M24" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D25" s="19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E25" s="20" t="inlineStr"/>
       <c r="F25" s="20" t="inlineStr"/>
       <c r="G25" s="20" t="inlineStr"/>
       <c r="H25" s="19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I25" s="19" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M25" s="19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="D26" s="19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="21" t="inlineStr"/>
       <c r="F26" s="21" t="inlineStr"/>
       <c r="G26" s="21" t="inlineStr"/>
       <c r="H26" s="19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K26" s="19" t="n">
         <v>1</v>
@@ -2123,54 +2251,54 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>CFO</t>
         </is>
       </c>
       <c r="B27" s="18" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C27" s="18" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="D27" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" s="20" t="inlineStr"/>
       <c r="F27" s="20" t="inlineStr"/>
       <c r="G27" s="20" t="inlineStr"/>
       <c r="H27" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I27" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J27" s="19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K27" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="19" t="n">
-        <v>2</v>
-      </c>
       <c r="L27" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Support</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B28" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="D28" s="19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="21" t="inlineStr"/>
       <c r="F28" s="21" t="inlineStr"/>
@@ -2197,66 +2325,66 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B29" s="18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="D29" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="20" t="inlineStr"/>
       <c r="F29" s="20" t="inlineStr"/>
       <c r="G29" s="20" t="inlineStr"/>
       <c r="H29" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Support</t>
         </is>
       </c>
       <c r="B30" s="18" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="D30" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="21" t="inlineStr"/>
       <c r="F30" s="21" t="inlineStr"/>
       <c r="G30" s="21" t="inlineStr"/>
       <c r="H30" s="19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K30" s="19" t="n">
         <v>1</v>
@@ -2271,7 +2399,7 @@
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B31" s="18" t="n">
@@ -2281,7 +2409,7 @@
         <v>0.2</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="20" t="inlineStr"/>
       <c r="F31" s="20" t="inlineStr"/>
@@ -2306,1427 +2434,1705 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="22" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D32" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" s="21" t="inlineStr"/>
+      <c r="F32" s="21" t="inlineStr"/>
+      <c r="G32" s="21" t="inlineStr"/>
+      <c r="H32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="20" t="inlineStr"/>
+      <c r="F33" s="20" t="inlineStr"/>
+      <c r="G33" s="20" t="inlineStr"/>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Total performance units</t>
         </is>
       </c>
-      <c r="B32" s="23" t="inlineStr"/>
-      <c r="C32" s="23" t="inlineStr"/>
-      <c r="D32" s="23" t="inlineStr"/>
-      <c r="E32" s="23" t="inlineStr"/>
-      <c r="F32" s="23" t="inlineStr"/>
-      <c r="G32" s="24" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr"/>
+      <c r="C34" s="23" t="inlineStr"/>
+      <c r="D34" s="23" t="inlineStr"/>
+      <c r="E34" s="23" t="inlineStr"/>
+      <c r="F34" s="23" t="inlineStr"/>
+      <c r="G34" s="24" t="inlineStr">
         <is>
           <t>Σ weight×HC →</t>
         </is>
       </c>
-      <c r="H32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,H21:H31)</f>
-        <v/>
-      </c>
-      <c r="I32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,I21:I31)</f>
-        <v/>
-      </c>
-      <c r="J32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,J21:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,K21:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,L21:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="25">
-        <f>SUMPRODUCT($D$21:$D$31,M21:M31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="H34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,H21:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,I21:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,J21:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,K21:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,L21:L33)</f>
+        <v/>
+      </c>
+      <c r="M34" s="25">
+        <f>SUMPRODUCT($D$21:$D$33,M21:M33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Value per performance unit (millions)</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr"/>
-      <c r="C33" s="26" t="inlineStr"/>
-      <c r="D33" s="26" t="inlineStr"/>
-      <c r="E33" s="26" t="inlineStr"/>
-      <c r="F33" s="26" t="inlineStr"/>
-      <c r="G33" s="27" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr"/>
+      <c r="C35" s="26" t="inlineStr"/>
+      <c r="D35" s="26" t="inlineStr"/>
+      <c r="E35" s="26" t="inlineStr"/>
+      <c r="F35" s="26" t="inlineStr"/>
+      <c r="G35" s="27" t="inlineStr">
         <is>
           <t>pool ÷ units →</t>
         </is>
       </c>
-      <c r="H33" s="28">
-        <f>IF(H32=0,0,H18/H32)</f>
-        <v/>
-      </c>
-      <c r="I33" s="28">
-        <f>IF(I32=0,0,I18/I32)</f>
-        <v/>
-      </c>
-      <c r="J33" s="28">
-        <f>IF(J32=0,0,J18/J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="28">
-        <f>IF(K32=0,0,K18/K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="28">
-        <f>IF(L32=0,0,L18/L32)</f>
-        <v/>
-      </c>
-      <c r="M33" s="28">
-        <f>IF(M32=0,0,M18/M32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="H35" s="28">
+        <f>IF(H34=0,0,H18/H34)</f>
+        <v/>
+      </c>
+      <c r="I35" s="28">
+        <f>IF(I34=0,0,I18/I34)</f>
+        <v/>
+      </c>
+      <c r="J35" s="28">
+        <f>IF(J34=0,0,J18/J34)</f>
+        <v/>
+      </c>
+      <c r="K35" s="28">
+        <f>IF(K34=0,0,K18/K34)</f>
+        <v/>
+      </c>
+      <c r="L35" s="28">
+        <f>IF(L34=0,0,L18/L34)</f>
+        <v/>
+      </c>
+      <c r="M35" s="28">
+        <f>IF(M34=0,0,M18/M34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Total fixed payroll, loaded (millions)</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr"/>
-      <c r="C34" s="29" t="inlineStr"/>
-      <c r="D34" s="29" t="inlineStr"/>
-      <c r="E34" s="29" t="inlineStr"/>
-      <c r="F34" s="29" t="inlineStr"/>
-      <c r="G34" s="29" t="inlineStr"/>
-      <c r="H34" s="30">
-        <f>IF(H15&lt;$F$9,SUMPRODUCT($B$21:$B$31,H21:H31),SUMPRODUCT($C$21:$C$31,H21:H31))*$F$10</f>
-        <v/>
-      </c>
-      <c r="I34" s="30">
-        <f>IF(I15&lt;$F$9,SUMPRODUCT($B$21:$B$31,I21:I31),SUMPRODUCT($C$21:$C$31,I21:I31))*$F$10</f>
-        <v/>
-      </c>
-      <c r="J34" s="30">
-        <f>IF(J15&lt;$F$9,SUMPRODUCT($B$21:$B$31,J21:J31),SUMPRODUCT($C$21:$C$31,J21:J31))*$F$10</f>
-        <v/>
-      </c>
-      <c r="K34" s="30">
-        <f>IF(K15&lt;$F$9,SUMPRODUCT($B$21:$B$31,K21:K31),SUMPRODUCT($C$21:$C$31,K21:K31))*$F$10</f>
-        <v/>
-      </c>
-      <c r="L34" s="30">
-        <f>IF(L15&lt;$F$9,SUMPRODUCT($B$21:$B$31,L21:L31),SUMPRODUCT($C$21:$C$31,L21:L31))*$F$10</f>
-        <v/>
-      </c>
-      <c r="M34" s="30">
-        <f>IF(M15&lt;$F$9,SUMPRODUCT($B$21:$B$31,M21:M31),SUMPRODUCT($C$21:$C$31,M21:M31))*$F$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr"/>
+      <c r="C36" s="29" t="inlineStr"/>
+      <c r="D36" s="29" t="inlineStr"/>
+      <c r="E36" s="29" t="inlineStr"/>
+      <c r="F36" s="29" t="inlineStr"/>
+      <c r="G36" s="29" t="inlineStr"/>
+      <c r="H36" s="30">
+        <f>IF(H15&lt;$F$9,SUMPRODUCT($B$21:$B$33,H21:H33),SUMPRODUCT($C$21:$C$33,H21:H33))*$F$10</f>
+        <v/>
+      </c>
+      <c r="I36" s="30">
+        <f>IF(I15&lt;$F$9,SUMPRODUCT($B$21:$B$33,I21:I33),SUMPRODUCT($C$21:$C$33,I21:I33))*$F$10</f>
+        <v/>
+      </c>
+      <c r="J36" s="30">
+        <f>IF(J15&lt;$F$9,SUMPRODUCT($B$21:$B$33,J21:J33),SUMPRODUCT($C$21:$C$33,J21:J33))*$F$10</f>
+        <v/>
+      </c>
+      <c r="K36" s="30">
+        <f>IF(K15&lt;$F$9,SUMPRODUCT($B$21:$B$33,K21:K33),SUMPRODUCT($C$21:$C$33,K21:K33))*$F$10</f>
+        <v/>
+      </c>
+      <c r="L36" s="30">
+        <f>IF(L15&lt;$F$9,SUMPRODUCT($B$21:$B$33,L21:L33),SUMPRODUCT($C$21:$C$33,L21:L33))*$F$10</f>
+        <v/>
+      </c>
+      <c r="M36" s="30">
+        <f>IF(M15&lt;$F$9,SUMPRODUCT($B$21:$B$33,M21:M33),SUMPRODUCT($C$21:$C$33,M21:M33))*$F$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Total headcount</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr"/>
-      <c r="C35" s="29" t="inlineStr"/>
-      <c r="D35" s="29" t="inlineStr"/>
-      <c r="E35" s="29" t="inlineStr"/>
-      <c r="F35" s="29" t="inlineStr"/>
-      <c r="G35" s="29" t="inlineStr"/>
-      <c r="H35" s="31">
-        <f>SUM(H21:H31)</f>
-        <v/>
-      </c>
-      <c r="I35" s="31">
-        <f>SUM(I21:I31)</f>
-        <v/>
-      </c>
-      <c r="J35" s="31">
-        <f>SUM(J21:J31)</f>
-        <v/>
-      </c>
-      <c r="K35" s="31">
-        <f>SUM(K21:K31)</f>
-        <v/>
-      </c>
-      <c r="L35" s="31">
-        <f>SUM(L21:L31)</f>
-        <v/>
-      </c>
-      <c r="M35" s="31">
-        <f>SUM(M21:M31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="B37" s="29" t="inlineStr"/>
+      <c r="C37" s="29" t="inlineStr"/>
+      <c r="D37" s="29" t="inlineStr"/>
+      <c r="E37" s="29" t="inlineStr"/>
+      <c r="F37" s="29" t="inlineStr"/>
+      <c r="G37" s="29" t="inlineStr"/>
+      <c r="H37" s="31">
+        <f>SUM(H21:H33)</f>
+        <v/>
+      </c>
+      <c r="I37" s="31">
+        <f>SUM(I21:I33)</f>
+        <v/>
+      </c>
+      <c r="J37" s="31">
+        <f>SUM(J21:J33)</f>
+        <v/>
+      </c>
+      <c r="K37" s="31">
+        <f>SUM(K21:K33)</f>
+        <v/>
+      </c>
+      <c r="L37" s="31">
+        <f>SUM(L21:L33)</f>
+        <v/>
+      </c>
+      <c r="M37" s="31">
+        <f>SUM(M21:M33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>4.  Performance payout PER PERSON, by scenario  (millions — absolute, grows with AUM)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>@ $20m</t>
         </is>
       </c>
-      <c r="I38" s="16" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>@ $300m</t>
         </is>
       </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="J40" s="16" t="inlineStr">
         <is>
           <t>@ $500m</t>
         </is>
       </c>
-      <c r="K38" s="16" t="inlineStr">
+      <c r="K40" s="16" t="inlineStr">
         <is>
           <t>@ $1,000m</t>
         </is>
       </c>
-      <c r="L38" s="16" t="inlineStr">
+      <c r="L40" s="16" t="inlineStr">
         <is>
           <t>@ $2,000m</t>
         </is>
       </c>
-      <c r="M38" s="16" t="inlineStr">
+      <c r="M40" s="16" t="inlineStr">
         <is>
           <t>@ $5,000m</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17">
-        <f>A21</f>
-        <v/>
-      </c>
-      <c r="D39" s="33">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="H39" s="34">
-        <f>$D21*H$33</f>
-        <v/>
-      </c>
-      <c r="I39" s="34">
-        <f>$D21*I$33</f>
-        <v/>
-      </c>
-      <c r="J39" s="34">
-        <f>$D21*J$33</f>
-        <v/>
-      </c>
-      <c r="K39" s="34">
-        <f>$D21*K$33</f>
-        <v/>
-      </c>
-      <c r="L39" s="34">
-        <f>$D21*L$33</f>
-        <v/>
-      </c>
-      <c r="M39" s="34">
-        <f>$D21*M$33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12">
-        <f>A22</f>
-        <v/>
-      </c>
-      <c r="D40" s="35">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="H40" s="36">
-        <f>$D22*H$33</f>
-        <v/>
-      </c>
-      <c r="I40" s="36">
-        <f>$D22*I$33</f>
-        <v/>
-      </c>
-      <c r="J40" s="36">
-        <f>$D22*J$33</f>
-        <v/>
-      </c>
-      <c r="K40" s="36">
-        <f>$D22*K$33</f>
-        <v/>
-      </c>
-      <c r="L40" s="36">
-        <f>$D22*L$33</f>
-        <v/>
-      </c>
-      <c r="M40" s="36">
-        <f>$D22*M$33</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="17">
-        <f>A23</f>
+        <f>A21</f>
         <v/>
       </c>
       <c r="D41" s="33">
-        <f>D23</f>
+        <f>D21</f>
         <v/>
       </c>
       <c r="H41" s="34">
-        <f>$D23*H$33</f>
+        <f>$D21*H$35</f>
         <v/>
       </c>
       <c r="I41" s="34">
-        <f>$D23*I$33</f>
+        <f>$D21*I$35</f>
         <v/>
       </c>
       <c r="J41" s="34">
-        <f>$D23*J$33</f>
+        <f>$D21*J$35</f>
         <v/>
       </c>
       <c r="K41" s="34">
-        <f>$D23*K$33</f>
+        <f>$D21*K$35</f>
         <v/>
       </c>
       <c r="L41" s="34">
-        <f>$D23*L$33</f>
+        <f>$D21*L$35</f>
         <v/>
       </c>
       <c r="M41" s="34">
-        <f>$D23*M$33</f>
+        <f>$D21*M$35</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12">
-        <f>A24</f>
+        <f>A22</f>
         <v/>
       </c>
       <c r="D42" s="35">
-        <f>D24</f>
+        <f>D22</f>
         <v/>
       </c>
       <c r="H42" s="36">
-        <f>$D24*H$33</f>
+        <f>$D22*H$35</f>
         <v/>
       </c>
       <c r="I42" s="36">
-        <f>$D24*I$33</f>
+        <f>$D22*I$35</f>
         <v/>
       </c>
       <c r="J42" s="36">
-        <f>$D24*J$33</f>
+        <f>$D22*J$35</f>
         <v/>
       </c>
       <c r="K42" s="36">
-        <f>$D24*K$33</f>
+        <f>$D22*K$35</f>
         <v/>
       </c>
       <c r="L42" s="36">
-        <f>$D24*L$33</f>
+        <f>$D22*L$35</f>
         <v/>
       </c>
       <c r="M42" s="36">
-        <f>$D24*M$33</f>
+        <f>$D22*M$35</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="17">
-        <f>A25</f>
+        <f>A23</f>
         <v/>
       </c>
       <c r="D43" s="33">
-        <f>D25</f>
+        <f>D23</f>
         <v/>
       </c>
       <c r="H43" s="34">
-        <f>$D25*H$33</f>
+        <f>$D23*H$35</f>
         <v/>
       </c>
       <c r="I43" s="34">
-        <f>$D25*I$33</f>
+        <f>$D23*I$35</f>
         <v/>
       </c>
       <c r="J43" s="34">
-        <f>$D25*J$33</f>
+        <f>$D23*J$35</f>
         <v/>
       </c>
       <c r="K43" s="34">
-        <f>$D25*K$33</f>
+        <f>$D23*K$35</f>
         <v/>
       </c>
       <c r="L43" s="34">
-        <f>$D25*L$33</f>
+        <f>$D23*L$35</f>
         <v/>
       </c>
       <c r="M43" s="34">
-        <f>$D25*M$33</f>
+        <f>$D23*M$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12">
-        <f>A26</f>
+        <f>A24</f>
         <v/>
       </c>
       <c r="D44" s="35">
-        <f>D26</f>
+        <f>D24</f>
         <v/>
       </c>
       <c r="H44" s="36">
-        <f>$D26*H$33</f>
+        <f>$D24*H$35</f>
         <v/>
       </c>
       <c r="I44" s="36">
-        <f>$D26*I$33</f>
+        <f>$D24*I$35</f>
         <v/>
       </c>
       <c r="J44" s="36">
-        <f>$D26*J$33</f>
+        <f>$D24*J$35</f>
         <v/>
       </c>
       <c r="K44" s="36">
-        <f>$D26*K$33</f>
+        <f>$D24*K$35</f>
         <v/>
       </c>
       <c r="L44" s="36">
-        <f>$D26*L$33</f>
+        <f>$D24*L$35</f>
         <v/>
       </c>
       <c r="M44" s="36">
-        <f>$D26*M$33</f>
+        <f>$D24*M$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="17">
-        <f>A27</f>
+        <f>A25</f>
         <v/>
       </c>
       <c r="D45" s="33">
-        <f>D27</f>
+        <f>D25</f>
         <v/>
       </c>
       <c r="H45" s="34">
-        <f>$D27*H$33</f>
+        <f>$D25*H$35</f>
         <v/>
       </c>
       <c r="I45" s="34">
-        <f>$D27*I$33</f>
+        <f>$D25*I$35</f>
         <v/>
       </c>
       <c r="J45" s="34">
-        <f>$D27*J$33</f>
+        <f>$D25*J$35</f>
         <v/>
       </c>
       <c r="K45" s="34">
-        <f>$D27*K$33</f>
+        <f>$D25*K$35</f>
         <v/>
       </c>
       <c r="L45" s="34">
-        <f>$D27*L$33</f>
+        <f>$D25*L$35</f>
         <v/>
       </c>
       <c r="M45" s="34">
-        <f>$D27*M$33</f>
+        <f>$D25*M$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12">
-        <f>A28</f>
+        <f>A26</f>
         <v/>
       </c>
       <c r="D46" s="35">
-        <f>D28</f>
+        <f>D26</f>
         <v/>
       </c>
       <c r="H46" s="36">
-        <f>$D28*H$33</f>
+        <f>$D26*H$35</f>
         <v/>
       </c>
       <c r="I46" s="36">
-        <f>$D28*I$33</f>
+        <f>$D26*I$35</f>
         <v/>
       </c>
       <c r="J46" s="36">
-        <f>$D28*J$33</f>
+        <f>$D26*J$35</f>
         <v/>
       </c>
       <c r="K46" s="36">
-        <f>$D28*K$33</f>
+        <f>$D26*K$35</f>
         <v/>
       </c>
       <c r="L46" s="36">
-        <f>$D28*L$33</f>
+        <f>$D26*L$35</f>
         <v/>
       </c>
       <c r="M46" s="36">
-        <f>$D28*M$33</f>
+        <f>$D26*M$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="17">
-        <f>A29</f>
+        <f>A27</f>
         <v/>
       </c>
       <c r="D47" s="33">
-        <f>D29</f>
+        <f>D27</f>
         <v/>
       </c>
       <c r="H47" s="34">
-        <f>$D29*H$33</f>
+        <f>$D27*H$35</f>
         <v/>
       </c>
       <c r="I47" s="34">
-        <f>$D29*I$33</f>
+        <f>$D27*I$35</f>
         <v/>
       </c>
       <c r="J47" s="34">
-        <f>$D29*J$33</f>
+        <f>$D27*J$35</f>
         <v/>
       </c>
       <c r="K47" s="34">
-        <f>$D29*K$33</f>
+        <f>$D27*K$35</f>
         <v/>
       </c>
       <c r="L47" s="34">
-        <f>$D29*L$33</f>
+        <f>$D27*L$35</f>
         <v/>
       </c>
       <c r="M47" s="34">
-        <f>$D29*M$33</f>
+        <f>$D27*M$35</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12">
-        <f>A30</f>
+        <f>A28</f>
         <v/>
       </c>
       <c r="D48" s="35">
-        <f>D30</f>
+        <f>D28</f>
         <v/>
       </c>
       <c r="H48" s="36">
-        <f>$D30*H$33</f>
+        <f>$D28*H$35</f>
         <v/>
       </c>
       <c r="I48" s="36">
-        <f>$D30*I$33</f>
+        <f>$D28*I$35</f>
         <v/>
       </c>
       <c r="J48" s="36">
-        <f>$D30*J$33</f>
+        <f>$D28*J$35</f>
         <v/>
       </c>
       <c r="K48" s="36">
-        <f>$D30*K$33</f>
+        <f>$D28*K$35</f>
         <v/>
       </c>
       <c r="L48" s="36">
-        <f>$D30*L$33</f>
+        <f>$D28*L$35</f>
         <v/>
       </c>
       <c r="M48" s="36">
-        <f>$D30*M$33</f>
+        <f>$D28*M$35</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="17">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="D49" s="33">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="H49" s="34">
+        <f>$D29*H$35</f>
+        <v/>
+      </c>
+      <c r="I49" s="34">
+        <f>$D29*I$35</f>
+        <v/>
+      </c>
+      <c r="J49" s="34">
+        <f>$D29*J$35</f>
+        <v/>
+      </c>
+      <c r="K49" s="34">
+        <f>$D29*K$35</f>
+        <v/>
+      </c>
+      <c r="L49" s="34">
+        <f>$D29*L$35</f>
+        <v/>
+      </c>
+      <c r="M49" s="34">
+        <f>$D29*M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="D50" s="35">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="H50" s="36">
+        <f>$D30*H$35</f>
+        <v/>
+      </c>
+      <c r="I50" s="36">
+        <f>$D30*I$35</f>
+        <v/>
+      </c>
+      <c r="J50" s="36">
+        <f>$D30*J$35</f>
+        <v/>
+      </c>
+      <c r="K50" s="36">
+        <f>$D30*K$35</f>
+        <v/>
+      </c>
+      <c r="L50" s="36">
+        <f>$D30*L$35</f>
+        <v/>
+      </c>
+      <c r="M50" s="36">
+        <f>$D30*M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17">
         <f>A31</f>
         <v/>
       </c>
-      <c r="D49" s="33">
+      <c r="D51" s="33">
         <f>D31</f>
         <v/>
       </c>
-      <c r="H49" s="34">
-        <f>$D31*H$33</f>
-        <v/>
-      </c>
-      <c r="I49" s="34">
-        <f>$D31*I$33</f>
-        <v/>
-      </c>
-      <c r="J49" s="34">
-        <f>$D31*J$33</f>
-        <v/>
-      </c>
-      <c r="K49" s="34">
-        <f>$D31*K$33</f>
-        <v/>
-      </c>
-      <c r="L49" s="34">
-        <f>$D31*L$33</f>
-        <v/>
-      </c>
-      <c r="M49" s="34">
-        <f>$D31*M$33</f>
+      <c r="H51" s="34">
+        <f>$D31*H$35</f>
+        <v/>
+      </c>
+      <c r="I51" s="34">
+        <f>$D31*I$35</f>
+        <v/>
+      </c>
+      <c r="J51" s="34">
+        <f>$D31*J$35</f>
+        <v/>
+      </c>
+      <c r="K51" s="34">
+        <f>$D31*K$35</f>
+        <v/>
+      </c>
+      <c r="L51" s="34">
+        <f>$D31*L$35</f>
+        <v/>
+      </c>
+      <c r="M51" s="34">
+        <f>$D31*M$35</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="12">
+        <f>A32</f>
+        <v/>
+      </c>
+      <c r="D52" s="35">
+        <f>D32</f>
+        <v/>
+      </c>
+      <c r="H52" s="36">
+        <f>$D32*H$35</f>
+        <v/>
+      </c>
+      <c r="I52" s="36">
+        <f>$D32*I$35</f>
+        <v/>
+      </c>
+      <c r="J52" s="36">
+        <f>$D32*J$35</f>
+        <v/>
+      </c>
+      <c r="K52" s="36">
+        <f>$D32*K$35</f>
+        <v/>
+      </c>
+      <c r="L52" s="36">
+        <f>$D32*L$35</f>
+        <v/>
+      </c>
+      <c r="M52" s="36">
+        <f>$D32*M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17">
+        <f>A33</f>
+        <v/>
+      </c>
+      <c r="D53" s="33">
+        <f>D33</f>
+        <v/>
+      </c>
+      <c r="H53" s="34">
+        <f>$D33*H$35</f>
+        <v/>
+      </c>
+      <c r="I53" s="34">
+        <f>$D33*I$35</f>
+        <v/>
+      </c>
+      <c r="J53" s="34">
+        <f>$D33*J$35</f>
+        <v/>
+      </c>
+      <c r="K53" s="34">
+        <f>$D33*K$35</f>
+        <v/>
+      </c>
+      <c r="L53" s="34">
+        <f>$D33*L$35</f>
+        <v/>
+      </c>
+      <c r="M53" s="34">
+        <f>$D33*M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>5.  Each role's SHARE of the take  (% — falls as the firm grows)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="32" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="H53" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>@ $20m</t>
         </is>
       </c>
-      <c r="I53" s="16" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>@ $300m</t>
         </is>
       </c>
-      <c r="J53" s="16" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>@ $500m</t>
         </is>
       </c>
-      <c r="K53" s="16" t="inlineStr">
+      <c r="K57" s="16" t="inlineStr">
         <is>
           <t>@ $1,000m</t>
         </is>
       </c>
-      <c r="L53" s="16" t="inlineStr">
+      <c r="L57" s="16" t="inlineStr">
         <is>
           <t>@ $2,000m</t>
         </is>
       </c>
-      <c r="M53" s="16" t="inlineStr">
+      <c r="M57" s="16" t="inlineStr">
         <is>
           <t>@ $5,000m</t>
         </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17">
-        <f>A21</f>
-        <v/>
-      </c>
-      <c r="D54" s="33">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="H54" s="37">
-        <f>IF(H$32=0,0,H21*$D21/H$32)</f>
-        <v/>
-      </c>
-      <c r="I54" s="37">
-        <f>IF(I$32=0,0,I21*$D21/I$32)</f>
-        <v/>
-      </c>
-      <c r="J54" s="37">
-        <f>IF(J$32=0,0,J21*$D21/J$32)</f>
-        <v/>
-      </c>
-      <c r="K54" s="37">
-        <f>IF(K$32=0,0,K21*$D21/K$32)</f>
-        <v/>
-      </c>
-      <c r="L54" s="37">
-        <f>IF(L$32=0,0,L21*$D21/L$32)</f>
-        <v/>
-      </c>
-      <c r="M54" s="37">
-        <f>IF(M$32=0,0,M21*$D21/M$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="12">
-        <f>A22</f>
-        <v/>
-      </c>
-      <c r="D55" s="35">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="H55" s="38">
-        <f>IF(H$32=0,0,H22*$D22/H$32)</f>
-        <v/>
-      </c>
-      <c r="I55" s="38">
-        <f>IF(I$32=0,0,I22*$D22/I$32)</f>
-        <v/>
-      </c>
-      <c r="J55" s="38">
-        <f>IF(J$32=0,0,J22*$D22/J$32)</f>
-        <v/>
-      </c>
-      <c r="K55" s="38">
-        <f>IF(K$32=0,0,K22*$D22/K$32)</f>
-        <v/>
-      </c>
-      <c r="L55" s="38">
-        <f>IF(L$32=0,0,L22*$D22/L$32)</f>
-        <v/>
-      </c>
-      <c r="M55" s="38">
-        <f>IF(M$32=0,0,M22*$D22/M$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17">
-        <f>A23</f>
-        <v/>
-      </c>
-      <c r="D56" s="33">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="H56" s="37">
-        <f>IF(H$32=0,0,H23*$D23/H$32)</f>
-        <v/>
-      </c>
-      <c r="I56" s="37">
-        <f>IF(I$32=0,0,I23*$D23/I$32)</f>
-        <v/>
-      </c>
-      <c r="J56" s="37">
-        <f>IF(J$32=0,0,J23*$D23/J$32)</f>
-        <v/>
-      </c>
-      <c r="K56" s="37">
-        <f>IF(K$32=0,0,K23*$D23/K$32)</f>
-        <v/>
-      </c>
-      <c r="L56" s="37">
-        <f>IF(L$32=0,0,L23*$D23/L$32)</f>
-        <v/>
-      </c>
-      <c r="M56" s="37">
-        <f>IF(M$32=0,0,M23*$D23/M$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="12">
-        <f>A24</f>
-        <v/>
-      </c>
-      <c r="D57" s="35">
-        <f>D24</f>
-        <v/>
-      </c>
-      <c r="H57" s="38">
-        <f>IF(H$32=0,0,H24*$D24/H$32)</f>
-        <v/>
-      </c>
-      <c r="I57" s="38">
-        <f>IF(I$32=0,0,I24*$D24/I$32)</f>
-        <v/>
-      </c>
-      <c r="J57" s="38">
-        <f>IF(J$32=0,0,J24*$D24/J$32)</f>
-        <v/>
-      </c>
-      <c r="K57" s="38">
-        <f>IF(K$32=0,0,K24*$D24/K$32)</f>
-        <v/>
-      </c>
-      <c r="L57" s="38">
-        <f>IF(L$32=0,0,L24*$D24/L$32)</f>
-        <v/>
-      </c>
-      <c r="M57" s="38">
-        <f>IF(M$32=0,0,M24*$D24/M$32)</f>
-        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="17">
-        <f>A25</f>
+        <f>A21</f>
         <v/>
       </c>
       <c r="D58" s="33">
-        <f>D25</f>
+        <f>D21</f>
         <v/>
       </c>
       <c r="H58" s="37">
-        <f>IF(H$32=0,0,H25*$D25/H$32)</f>
+        <f>IF(H$34=0,0,H21*$D21/H$34)</f>
         <v/>
       </c>
       <c r="I58" s="37">
-        <f>IF(I$32=0,0,I25*$D25/I$32)</f>
+        <f>IF(I$34=0,0,I21*$D21/I$34)</f>
         <v/>
       </c>
       <c r="J58" s="37">
-        <f>IF(J$32=0,0,J25*$D25/J$32)</f>
+        <f>IF(J$34=0,0,J21*$D21/J$34)</f>
         <v/>
       </c>
       <c r="K58" s="37">
-        <f>IF(K$32=0,0,K25*$D25/K$32)</f>
+        <f>IF(K$34=0,0,K21*$D21/K$34)</f>
         <v/>
       </c>
       <c r="L58" s="37">
-        <f>IF(L$32=0,0,L25*$D25/L$32)</f>
+        <f>IF(L$34=0,0,L21*$D21/L$34)</f>
         <v/>
       </c>
       <c r="M58" s="37">
-        <f>IF(M$32=0,0,M25*$D25/M$32)</f>
+        <f>IF(M$34=0,0,M21*$D21/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12">
-        <f>A26</f>
+        <f>A22</f>
         <v/>
       </c>
       <c r="D59" s="35">
-        <f>D26</f>
+        <f>D22</f>
         <v/>
       </c>
       <c r="H59" s="38">
-        <f>IF(H$32=0,0,H26*$D26/H$32)</f>
+        <f>IF(H$34=0,0,H22*$D22/H$34)</f>
         <v/>
       </c>
       <c r="I59" s="38">
-        <f>IF(I$32=0,0,I26*$D26/I$32)</f>
+        <f>IF(I$34=0,0,I22*$D22/I$34)</f>
         <v/>
       </c>
       <c r="J59" s="38">
-        <f>IF(J$32=0,0,J26*$D26/J$32)</f>
+        <f>IF(J$34=0,0,J22*$D22/J$34)</f>
         <v/>
       </c>
       <c r="K59" s="38">
-        <f>IF(K$32=0,0,K26*$D26/K$32)</f>
+        <f>IF(K$34=0,0,K22*$D22/K$34)</f>
         <v/>
       </c>
       <c r="L59" s="38">
-        <f>IF(L$32=0,0,L26*$D26/L$32)</f>
+        <f>IF(L$34=0,0,L22*$D22/L$34)</f>
         <v/>
       </c>
       <c r="M59" s="38">
-        <f>IF(M$32=0,0,M26*$D26/M$32)</f>
+        <f>IF(M$34=0,0,M22*$D22/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="17">
-        <f>A27</f>
+        <f>A23</f>
         <v/>
       </c>
       <c r="D60" s="33">
-        <f>D27</f>
+        <f>D23</f>
         <v/>
       </c>
       <c r="H60" s="37">
-        <f>IF(H$32=0,0,H27*$D27/H$32)</f>
+        <f>IF(H$34=0,0,H23*$D23/H$34)</f>
         <v/>
       </c>
       <c r="I60" s="37">
-        <f>IF(I$32=0,0,I27*$D27/I$32)</f>
+        <f>IF(I$34=0,0,I23*$D23/I$34)</f>
         <v/>
       </c>
       <c r="J60" s="37">
-        <f>IF(J$32=0,0,J27*$D27/J$32)</f>
+        <f>IF(J$34=0,0,J23*$D23/J$34)</f>
         <v/>
       </c>
       <c r="K60" s="37">
-        <f>IF(K$32=0,0,K27*$D27/K$32)</f>
+        <f>IF(K$34=0,0,K23*$D23/K$34)</f>
         <v/>
       </c>
       <c r="L60" s="37">
-        <f>IF(L$32=0,0,L27*$D27/L$32)</f>
+        <f>IF(L$34=0,0,L23*$D23/L$34)</f>
         <v/>
       </c>
       <c r="M60" s="37">
-        <f>IF(M$32=0,0,M27*$D27/M$32)</f>
+        <f>IF(M$34=0,0,M23*$D23/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12">
-        <f>A28</f>
+        <f>A24</f>
         <v/>
       </c>
       <c r="D61" s="35">
-        <f>D28</f>
+        <f>D24</f>
         <v/>
       </c>
       <c r="H61" s="38">
-        <f>IF(H$32=0,0,H28*$D28/H$32)</f>
+        <f>IF(H$34=0,0,H24*$D24/H$34)</f>
         <v/>
       </c>
       <c r="I61" s="38">
-        <f>IF(I$32=0,0,I28*$D28/I$32)</f>
+        <f>IF(I$34=0,0,I24*$D24/I$34)</f>
         <v/>
       </c>
       <c r="J61" s="38">
-        <f>IF(J$32=0,0,J28*$D28/J$32)</f>
+        <f>IF(J$34=0,0,J24*$D24/J$34)</f>
         <v/>
       </c>
       <c r="K61" s="38">
-        <f>IF(K$32=0,0,K28*$D28/K$32)</f>
+        <f>IF(K$34=0,0,K24*$D24/K$34)</f>
         <v/>
       </c>
       <c r="L61" s="38">
-        <f>IF(L$32=0,0,L28*$D28/L$32)</f>
+        <f>IF(L$34=0,0,L24*$D24/L$34)</f>
         <v/>
       </c>
       <c r="M61" s="38">
-        <f>IF(M$32=0,0,M28*$D28/M$32)</f>
+        <f>IF(M$34=0,0,M24*$D24/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="17">
-        <f>A29</f>
+        <f>A25</f>
         <v/>
       </c>
       <c r="D62" s="33">
-        <f>D29</f>
+        <f>D25</f>
         <v/>
       </c>
       <c r="H62" s="37">
-        <f>IF(H$32=0,0,H29*$D29/H$32)</f>
+        <f>IF(H$34=0,0,H25*$D25/H$34)</f>
         <v/>
       </c>
       <c r="I62" s="37">
-        <f>IF(I$32=0,0,I29*$D29/I$32)</f>
+        <f>IF(I$34=0,0,I25*$D25/I$34)</f>
         <v/>
       </c>
       <c r="J62" s="37">
-        <f>IF(J$32=0,0,J29*$D29/J$32)</f>
+        <f>IF(J$34=0,0,J25*$D25/J$34)</f>
         <v/>
       </c>
       <c r="K62" s="37">
-        <f>IF(K$32=0,0,K29*$D29/K$32)</f>
+        <f>IF(K$34=0,0,K25*$D25/K$34)</f>
         <v/>
       </c>
       <c r="L62" s="37">
-        <f>IF(L$32=0,0,L29*$D29/L$32)</f>
+        <f>IF(L$34=0,0,L25*$D25/L$34)</f>
         <v/>
       </c>
       <c r="M62" s="37">
-        <f>IF(M$32=0,0,M29*$D29/M$32)</f>
+        <f>IF(M$34=0,0,M25*$D25/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12">
-        <f>A30</f>
+        <f>A26</f>
         <v/>
       </c>
       <c r="D63" s="35">
-        <f>D30</f>
+        <f>D26</f>
         <v/>
       </c>
       <c r="H63" s="38">
-        <f>IF(H$32=0,0,H30*$D30/H$32)</f>
+        <f>IF(H$34=0,0,H26*$D26/H$34)</f>
         <v/>
       </c>
       <c r="I63" s="38">
-        <f>IF(I$32=0,0,I30*$D30/I$32)</f>
+        <f>IF(I$34=0,0,I26*$D26/I$34)</f>
         <v/>
       </c>
       <c r="J63" s="38">
-        <f>IF(J$32=0,0,J30*$D30/J$32)</f>
+        <f>IF(J$34=0,0,J26*$D26/J$34)</f>
         <v/>
       </c>
       <c r="K63" s="38">
-        <f>IF(K$32=0,0,K30*$D30/K$32)</f>
+        <f>IF(K$34=0,0,K26*$D26/K$34)</f>
         <v/>
       </c>
       <c r="L63" s="38">
-        <f>IF(L$32=0,0,L30*$D30/L$32)</f>
+        <f>IF(L$34=0,0,L26*$D26/L$34)</f>
         <v/>
       </c>
       <c r="M63" s="38">
-        <f>IF(M$32=0,0,M30*$D30/M$32)</f>
+        <f>IF(M$34=0,0,M26*$D26/M$34)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="17">
+        <f>A27</f>
+        <v/>
+      </c>
+      <c r="D64" s="33">
+        <f>D27</f>
+        <v/>
+      </c>
+      <c r="H64" s="37">
+        <f>IF(H$34=0,0,H27*$D27/H$34)</f>
+        <v/>
+      </c>
+      <c r="I64" s="37">
+        <f>IF(I$34=0,0,I27*$D27/I$34)</f>
+        <v/>
+      </c>
+      <c r="J64" s="37">
+        <f>IF(J$34=0,0,J27*$D27/J$34)</f>
+        <v/>
+      </c>
+      <c r="K64" s="37">
+        <f>IF(K$34=0,0,K27*$D27/K$34)</f>
+        <v/>
+      </c>
+      <c r="L64" s="37">
+        <f>IF(L$34=0,0,L27*$D27/L$34)</f>
+        <v/>
+      </c>
+      <c r="M64" s="37">
+        <f>IF(M$34=0,0,M27*$D27/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="D65" s="35">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="H65" s="38">
+        <f>IF(H$34=0,0,H28*$D28/H$34)</f>
+        <v/>
+      </c>
+      <c r="I65" s="38">
+        <f>IF(I$34=0,0,I28*$D28/I$34)</f>
+        <v/>
+      </c>
+      <c r="J65" s="38">
+        <f>IF(J$34=0,0,J28*$D28/J$34)</f>
+        <v/>
+      </c>
+      <c r="K65" s="38">
+        <f>IF(K$34=0,0,K28*$D28/K$34)</f>
+        <v/>
+      </c>
+      <c r="L65" s="38">
+        <f>IF(L$34=0,0,L28*$D28/L$34)</f>
+        <v/>
+      </c>
+      <c r="M65" s="38">
+        <f>IF(M$34=0,0,M28*$D28/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="D66" s="33">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="H66" s="37">
+        <f>IF(H$34=0,0,H29*$D29/H$34)</f>
+        <v/>
+      </c>
+      <c r="I66" s="37">
+        <f>IF(I$34=0,0,I29*$D29/I$34)</f>
+        <v/>
+      </c>
+      <c r="J66" s="37">
+        <f>IF(J$34=0,0,J29*$D29/J$34)</f>
+        <v/>
+      </c>
+      <c r="K66" s="37">
+        <f>IF(K$34=0,0,K29*$D29/K$34)</f>
+        <v/>
+      </c>
+      <c r="L66" s="37">
+        <f>IF(L$34=0,0,L29*$D29/L$34)</f>
+        <v/>
+      </c>
+      <c r="M66" s="37">
+        <f>IF(M$34=0,0,M29*$D29/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="D67" s="35">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="H67" s="38">
+        <f>IF(H$34=0,0,H30*$D30/H$34)</f>
+        <v/>
+      </c>
+      <c r="I67" s="38">
+        <f>IF(I$34=0,0,I30*$D30/I$34)</f>
+        <v/>
+      </c>
+      <c r="J67" s="38">
+        <f>IF(J$34=0,0,J30*$D30/J$34)</f>
+        <v/>
+      </c>
+      <c r="K67" s="38">
+        <f>IF(K$34=0,0,K30*$D30/K$34)</f>
+        <v/>
+      </c>
+      <c r="L67" s="38">
+        <f>IF(L$34=0,0,L30*$D30/L$34)</f>
+        <v/>
+      </c>
+      <c r="M67" s="38">
+        <f>IF(M$34=0,0,M30*$D30/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17">
         <f>A31</f>
         <v/>
       </c>
-      <c r="D64" s="33">
+      <c r="D68" s="33">
         <f>D31</f>
         <v/>
       </c>
-      <c r="H64" s="37">
-        <f>IF(H$32=0,0,H31*$D31/H$32)</f>
-        <v/>
-      </c>
-      <c r="I64" s="37">
-        <f>IF(I$32=0,0,I31*$D31/I$32)</f>
-        <v/>
-      </c>
-      <c r="J64" s="37">
-        <f>IF(J$32=0,0,J31*$D31/J$32)</f>
-        <v/>
-      </c>
-      <c r="K64" s="37">
-        <f>IF(K$32=0,0,K31*$D31/K$32)</f>
-        <v/>
-      </c>
-      <c r="L64" s="37">
-        <f>IF(L$32=0,0,L31*$D31/L$32)</f>
-        <v/>
-      </c>
-      <c r="M64" s="37">
-        <f>IF(M$32=0,0,M31*$D31/M$32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="H68" s="37">
+        <f>IF(H$34=0,0,H31*$D31/H$34)</f>
+        <v/>
+      </c>
+      <c r="I68" s="37">
+        <f>IF(I$34=0,0,I31*$D31/I$34)</f>
+        <v/>
+      </c>
+      <c r="J68" s="37">
+        <f>IF(J$34=0,0,J31*$D31/J$34)</f>
+        <v/>
+      </c>
+      <c r="K68" s="37">
+        <f>IF(K$34=0,0,K31*$D31/K$34)</f>
+        <v/>
+      </c>
+      <c r="L68" s="37">
+        <f>IF(L$34=0,0,L31*$D31/L$34)</f>
+        <v/>
+      </c>
+      <c r="M68" s="37">
+        <f>IF(M$34=0,0,M31*$D31/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12">
+        <f>A32</f>
+        <v/>
+      </c>
+      <c r="D69" s="35">
+        <f>D32</f>
+        <v/>
+      </c>
+      <c r="H69" s="38">
+        <f>IF(H$34=0,0,H32*$D32/H$34)</f>
+        <v/>
+      </c>
+      <c r="I69" s="38">
+        <f>IF(I$34=0,0,I32*$D32/I$34)</f>
+        <v/>
+      </c>
+      <c r="J69" s="38">
+        <f>IF(J$34=0,0,J32*$D32/J$34)</f>
+        <v/>
+      </c>
+      <c r="K69" s="38">
+        <f>IF(K$34=0,0,K32*$D32/K$34)</f>
+        <v/>
+      </c>
+      <c r="L69" s="38">
+        <f>IF(L$34=0,0,L32*$D32/L$34)</f>
+        <v/>
+      </c>
+      <c r="M69" s="38">
+        <f>IF(M$34=0,0,M32*$D32/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17">
+        <f>A33</f>
+        <v/>
+      </c>
+      <c r="D70" s="33">
+        <f>D33</f>
+        <v/>
+      </c>
+      <c r="H70" s="37">
+        <f>IF(H$34=0,0,H33*$D33/H$34)</f>
+        <v/>
+      </c>
+      <c r="I70" s="37">
+        <f>IF(I$34=0,0,I33*$D33/I$34)</f>
+        <v/>
+      </c>
+      <c r="J70" s="37">
+        <f>IF(J$34=0,0,J33*$D33/J$34)</f>
+        <v/>
+      </c>
+      <c r="K70" s="37">
+        <f>IF(K$34=0,0,K33*$D33/K$34)</f>
+        <v/>
+      </c>
+      <c r="L70" s="37">
+        <f>IF(L$34=0,0,L33*$D33/L$34)</f>
+        <v/>
+      </c>
+      <c r="M70" s="37">
+        <f>IF(M$34=0,0,M33*$D33/M$34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>6.  Share of the take PER PERSON  (% — one individual's slice)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="32" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="H68" s="16" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>@ $20m</t>
         </is>
       </c>
-      <c r="I68" s="16" t="inlineStr">
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>@ $300m</t>
         </is>
       </c>
-      <c r="J68" s="16" t="inlineStr">
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>@ $500m</t>
         </is>
       </c>
-      <c r="K68" s="16" t="inlineStr">
+      <c r="K74" s="16" t="inlineStr">
         <is>
           <t>@ $1,000m</t>
         </is>
       </c>
-      <c r="L68" s="16" t="inlineStr">
+      <c r="L74" s="16" t="inlineStr">
         <is>
           <t>@ $2,000m</t>
         </is>
       </c>
-      <c r="M68" s="16" t="inlineStr">
+      <c r="M74" s="16" t="inlineStr">
         <is>
           <t>@ $5,000m</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="17">
-        <f>A21</f>
-        <v/>
-      </c>
-      <c r="D69" s="33">
-        <f>D21</f>
-        <v/>
-      </c>
-      <c r="H69" s="39">
-        <f>$D21/H$32</f>
-        <v/>
-      </c>
-      <c r="I69" s="39">
-        <f>$D21/I$32</f>
-        <v/>
-      </c>
-      <c r="J69" s="39">
-        <f>$D21/J$32</f>
-        <v/>
-      </c>
-      <c r="K69" s="39">
-        <f>$D21/K$32</f>
-        <v/>
-      </c>
-      <c r="L69" s="39">
-        <f>$D21/L$32</f>
-        <v/>
-      </c>
-      <c r="M69" s="39">
-        <f>$D21/M$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="12">
-        <f>A22</f>
-        <v/>
-      </c>
-      <c r="D70" s="35">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="H70" s="40">
-        <f>$D22/H$32</f>
-        <v/>
-      </c>
-      <c r="I70" s="40">
-        <f>$D22/I$32</f>
-        <v/>
-      </c>
-      <c r="J70" s="40">
-        <f>$D22/J$32</f>
-        <v/>
-      </c>
-      <c r="K70" s="40">
-        <f>$D22/K$32</f>
-        <v/>
-      </c>
-      <c r="L70" s="40">
-        <f>$D22/L$32</f>
-        <v/>
-      </c>
-      <c r="M70" s="40">
-        <f>$D22/M$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="17">
-        <f>A23</f>
-        <v/>
-      </c>
-      <c r="D71" s="33">
-        <f>D23</f>
-        <v/>
-      </c>
-      <c r="H71" s="39">
-        <f>$D23/H$32</f>
-        <v/>
-      </c>
-      <c r="I71" s="39">
-        <f>$D23/I$32</f>
-        <v/>
-      </c>
-      <c r="J71" s="39">
-        <f>$D23/J$32</f>
-        <v/>
-      </c>
-      <c r="K71" s="39">
-        <f>$D23/K$32</f>
-        <v/>
-      </c>
-      <c r="L71" s="39">
-        <f>$D23/L$32</f>
-        <v/>
-      </c>
-      <c r="M71" s="39">
-        <f>$D23/M$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12">
-        <f>A24</f>
-        <v/>
-      </c>
-      <c r="D72" s="35">
-        <f>D24</f>
-        <v/>
-      </c>
-      <c r="H72" s="40">
-        <f>$D24/H$32</f>
-        <v/>
-      </c>
-      <c r="I72" s="40">
-        <f>$D24/I$32</f>
-        <v/>
-      </c>
-      <c r="J72" s="40">
-        <f>$D24/J$32</f>
-        <v/>
-      </c>
-      <c r="K72" s="40">
-        <f>$D24/K$32</f>
-        <v/>
-      </c>
-      <c r="L72" s="40">
-        <f>$D24/L$32</f>
-        <v/>
-      </c>
-      <c r="M72" s="40">
-        <f>$D24/M$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17">
-        <f>A25</f>
-        <v/>
-      </c>
-      <c r="D73" s="33">
-        <f>D25</f>
-        <v/>
-      </c>
-      <c r="H73" s="39">
-        <f>$D25/H$32</f>
-        <v/>
-      </c>
-      <c r="I73" s="39">
-        <f>$D25/I$32</f>
-        <v/>
-      </c>
-      <c r="J73" s="39">
-        <f>$D25/J$32</f>
-        <v/>
-      </c>
-      <c r="K73" s="39">
-        <f>$D25/K$32</f>
-        <v/>
-      </c>
-      <c r="L73" s="39">
-        <f>$D25/L$32</f>
-        <v/>
-      </c>
-      <c r="M73" s="39">
-        <f>$D25/M$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12">
-        <f>A26</f>
-        <v/>
-      </c>
-      <c r="D74" s="35">
-        <f>D26</f>
-        <v/>
-      </c>
-      <c r="H74" s="40">
-        <f>$D26/H$32</f>
-        <v/>
-      </c>
-      <c r="I74" s="40">
-        <f>$D26/I$32</f>
-        <v/>
-      </c>
-      <c r="J74" s="40">
-        <f>$D26/J$32</f>
-        <v/>
-      </c>
-      <c r="K74" s="40">
-        <f>$D26/K$32</f>
-        <v/>
-      </c>
-      <c r="L74" s="40">
-        <f>$D26/L$32</f>
-        <v/>
-      </c>
-      <c r="M74" s="40">
-        <f>$D26/M$32</f>
-        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="17">
-        <f>A27</f>
+        <f>A21</f>
         <v/>
       </c>
       <c r="D75" s="33">
-        <f>D27</f>
+        <f>D21</f>
         <v/>
       </c>
       <c r="H75" s="39">
-        <f>$D27/H$32</f>
+        <f>$D21/H$34</f>
         <v/>
       </c>
       <c r="I75" s="39">
-        <f>$D27/I$32</f>
+        <f>$D21/I$34</f>
         <v/>
       </c>
       <c r="J75" s="39">
-        <f>$D27/J$32</f>
+        <f>$D21/J$34</f>
         <v/>
       </c>
       <c r="K75" s="39">
-        <f>$D27/K$32</f>
+        <f>$D21/K$34</f>
         <v/>
       </c>
       <c r="L75" s="39">
-        <f>$D27/L$32</f>
+        <f>$D21/L$34</f>
         <v/>
       </c>
       <c r="M75" s="39">
-        <f>$D27/M$32</f>
+        <f>$D21/M$34</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12">
-        <f>A28</f>
+        <f>A22</f>
         <v/>
       </c>
       <c r="D76" s="35">
-        <f>D28</f>
+        <f>D22</f>
         <v/>
       </c>
       <c r="H76" s="40">
-        <f>$D28/H$32</f>
+        <f>$D22/H$34</f>
         <v/>
       </c>
       <c r="I76" s="40">
-        <f>$D28/I$32</f>
+        <f>$D22/I$34</f>
         <v/>
       </c>
       <c r="J76" s="40">
-        <f>$D28/J$32</f>
+        <f>$D22/J$34</f>
         <v/>
       </c>
       <c r="K76" s="40">
-        <f>$D28/K$32</f>
+        <f>$D22/K$34</f>
         <v/>
       </c>
       <c r="L76" s="40">
-        <f>$D28/L$32</f>
+        <f>$D22/L$34</f>
         <v/>
       </c>
       <c r="M76" s="40">
-        <f>$D28/M$32</f>
+        <f>$D22/M$34</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="17">
-        <f>A29</f>
+        <f>A23</f>
         <v/>
       </c>
       <c r="D77" s="33">
-        <f>D29</f>
+        <f>D23</f>
         <v/>
       </c>
       <c r="H77" s="39">
-        <f>$D29/H$32</f>
+        <f>$D23/H$34</f>
         <v/>
       </c>
       <c r="I77" s="39">
-        <f>$D29/I$32</f>
+        <f>$D23/I$34</f>
         <v/>
       </c>
       <c r="J77" s="39">
-        <f>$D29/J$32</f>
+        <f>$D23/J$34</f>
         <v/>
       </c>
       <c r="K77" s="39">
-        <f>$D29/K$32</f>
+        <f>$D23/K$34</f>
         <v/>
       </c>
       <c r="L77" s="39">
-        <f>$D29/L$32</f>
+        <f>$D23/L$34</f>
         <v/>
       </c>
       <c r="M77" s="39">
-        <f>$D29/M$32</f>
+        <f>$D23/M$34</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12">
-        <f>A30</f>
+        <f>A24</f>
         <v/>
       </c>
       <c r="D78" s="35">
-        <f>D30</f>
+        <f>D24</f>
         <v/>
       </c>
       <c r="H78" s="40">
-        <f>$D30/H$32</f>
+        <f>$D24/H$34</f>
         <v/>
       </c>
       <c r="I78" s="40">
-        <f>$D30/I$32</f>
+        <f>$D24/I$34</f>
         <v/>
       </c>
       <c r="J78" s="40">
-        <f>$D30/J$32</f>
+        <f>$D24/J$34</f>
         <v/>
       </c>
       <c r="K78" s="40">
-        <f>$D30/K$32</f>
+        <f>$D24/K$34</f>
         <v/>
       </c>
       <c r="L78" s="40">
-        <f>$D30/L$32</f>
+        <f>$D24/L$34</f>
         <v/>
       </c>
       <c r="M78" s="40">
-        <f>$D30/M$32</f>
+        <f>$D24/M$34</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="17">
+        <f>A25</f>
+        <v/>
+      </c>
+      <c r="D79" s="33">
+        <f>D25</f>
+        <v/>
+      </c>
+      <c r="H79" s="39">
+        <f>$D25/H$34</f>
+        <v/>
+      </c>
+      <c r="I79" s="39">
+        <f>$D25/I$34</f>
+        <v/>
+      </c>
+      <c r="J79" s="39">
+        <f>$D25/J$34</f>
+        <v/>
+      </c>
+      <c r="K79" s="39">
+        <f>$D25/K$34</f>
+        <v/>
+      </c>
+      <c r="L79" s="39">
+        <f>$D25/L$34</f>
+        <v/>
+      </c>
+      <c r="M79" s="39">
+        <f>$D25/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12">
+        <f>A26</f>
+        <v/>
+      </c>
+      <c r="D80" s="35">
+        <f>D26</f>
+        <v/>
+      </c>
+      <c r="H80" s="40">
+        <f>$D26/H$34</f>
+        <v/>
+      </c>
+      <c r="I80" s="40">
+        <f>$D26/I$34</f>
+        <v/>
+      </c>
+      <c r="J80" s="40">
+        <f>$D26/J$34</f>
+        <v/>
+      </c>
+      <c r="K80" s="40">
+        <f>$D26/K$34</f>
+        <v/>
+      </c>
+      <c r="L80" s="40">
+        <f>$D26/L$34</f>
+        <v/>
+      </c>
+      <c r="M80" s="40">
+        <f>$D26/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17">
+        <f>A27</f>
+        <v/>
+      </c>
+      <c r="D81" s="33">
+        <f>D27</f>
+        <v/>
+      </c>
+      <c r="H81" s="39">
+        <f>$D27/H$34</f>
+        <v/>
+      </c>
+      <c r="I81" s="39">
+        <f>$D27/I$34</f>
+        <v/>
+      </c>
+      <c r="J81" s="39">
+        <f>$D27/J$34</f>
+        <v/>
+      </c>
+      <c r="K81" s="39">
+        <f>$D27/K$34</f>
+        <v/>
+      </c>
+      <c r="L81" s="39">
+        <f>$D27/L$34</f>
+        <v/>
+      </c>
+      <c r="M81" s="39">
+        <f>$D27/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="D82" s="35">
+        <f>D28</f>
+        <v/>
+      </c>
+      <c r="H82" s="40">
+        <f>$D28/H$34</f>
+        <v/>
+      </c>
+      <c r="I82" s="40">
+        <f>$D28/I$34</f>
+        <v/>
+      </c>
+      <c r="J82" s="40">
+        <f>$D28/J$34</f>
+        <v/>
+      </c>
+      <c r="K82" s="40">
+        <f>$D28/K$34</f>
+        <v/>
+      </c>
+      <c r="L82" s="40">
+        <f>$D28/L$34</f>
+        <v/>
+      </c>
+      <c r="M82" s="40">
+        <f>$D28/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="D83" s="33">
+        <f>D29</f>
+        <v/>
+      </c>
+      <c r="H83" s="39">
+        <f>$D29/H$34</f>
+        <v/>
+      </c>
+      <c r="I83" s="39">
+        <f>$D29/I$34</f>
+        <v/>
+      </c>
+      <c r="J83" s="39">
+        <f>$D29/J$34</f>
+        <v/>
+      </c>
+      <c r="K83" s="39">
+        <f>$D29/K$34</f>
+        <v/>
+      </c>
+      <c r="L83" s="39">
+        <f>$D29/L$34</f>
+        <v/>
+      </c>
+      <c r="M83" s="39">
+        <f>$D29/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="D84" s="35">
+        <f>D30</f>
+        <v/>
+      </c>
+      <c r="H84" s="40">
+        <f>$D30/H$34</f>
+        <v/>
+      </c>
+      <c r="I84" s="40">
+        <f>$D30/I$34</f>
+        <v/>
+      </c>
+      <c r="J84" s="40">
+        <f>$D30/J$34</f>
+        <v/>
+      </c>
+      <c r="K84" s="40">
+        <f>$D30/K$34</f>
+        <v/>
+      </c>
+      <c r="L84" s="40">
+        <f>$D30/L$34</f>
+        <v/>
+      </c>
+      <c r="M84" s="40">
+        <f>$D30/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17">
         <f>A31</f>
         <v/>
       </c>
-      <c r="D79" s="33">
+      <c r="D85" s="33">
         <f>D31</f>
         <v/>
       </c>
-      <c r="H79" s="39">
-        <f>$D31/H$32</f>
-        <v/>
-      </c>
-      <c r="I79" s="39">
-        <f>$D31/I$32</f>
-        <v/>
-      </c>
-      <c r="J79" s="39">
-        <f>$D31/J$32</f>
-        <v/>
-      </c>
-      <c r="K79" s="39">
-        <f>$D31/K$32</f>
-        <v/>
-      </c>
-      <c r="L79" s="39">
-        <f>$D31/L$32</f>
-        <v/>
-      </c>
-      <c r="M79" s="39">
-        <f>$D31/M$32</f>
+      <c r="H85" s="39">
+        <f>$D31/H$34</f>
+        <v/>
+      </c>
+      <c r="I85" s="39">
+        <f>$D31/I$34</f>
+        <v/>
+      </c>
+      <c r="J85" s="39">
+        <f>$D31/J$34</f>
+        <v/>
+      </c>
+      <c r="K85" s="39">
+        <f>$D31/K$34</f>
+        <v/>
+      </c>
+      <c r="L85" s="39">
+        <f>$D31/L$34</f>
+        <v/>
+      </c>
+      <c r="M85" s="39">
+        <f>$D31/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12">
+        <f>A32</f>
+        <v/>
+      </c>
+      <c r="D86" s="35">
+        <f>D32</f>
+        <v/>
+      </c>
+      <c r="H86" s="40">
+        <f>$D32/H$34</f>
+        <v/>
+      </c>
+      <c r="I86" s="40">
+        <f>$D32/I$34</f>
+        <v/>
+      </c>
+      <c r="J86" s="40">
+        <f>$D32/J$34</f>
+        <v/>
+      </c>
+      <c r="K86" s="40">
+        <f>$D32/K$34</f>
+        <v/>
+      </c>
+      <c r="L86" s="40">
+        <f>$D32/L$34</f>
+        <v/>
+      </c>
+      <c r="M86" s="40">
+        <f>$D32/M$34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17">
+        <f>A33</f>
+        <v/>
+      </c>
+      <c r="D87" s="33">
+        <f>D33</f>
+        <v/>
+      </c>
+      <c r="H87" s="39">
+        <f>$D33/H$34</f>
+        <v/>
+      </c>
+      <c r="I87" s="39">
+        <f>$D33/I$34</f>
+        <v/>
+      </c>
+      <c r="J87" s="39">
+        <f>$D33/J$34</f>
+        <v/>
+      </c>
+      <c r="K87" s="39">
+        <f>$D33/K$34</f>
+        <v/>
+      </c>
+      <c r="L87" s="39">
+        <f>$D33/L$34</f>
+        <v/>
+      </c>
+      <c r="M87" s="39">
+        <f>$D33/M$34</f>
         <v/>
       </c>
     </row>
@@ -3751,7 +4157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3865,64 +4271,64 @@
         </is>
       </c>
       <c r="B5" s="37" t="n">
-        <v>0.3530895334174022</v>
+        <v>0.3444034440344403</v>
       </c>
       <c r="C5" s="37" t="n">
-        <v>0.3371462974111981</v>
+        <v>0.3198172472872644</v>
       </c>
       <c r="D5" s="37" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.2985074626865671</v>
       </c>
       <c r="E5" s="37" t="n">
-        <v>0.2917046490428441</v>
+        <v>0.2586903799514956</v>
       </c>
       <c r="F5" s="37" t="n">
-        <v>0.2662229617304492</v>
+        <v>0.2282453637660485</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>0.2560819462227913</v>
+        <v>0.2183406113537118</v>
       </c>
       <c r="H5" s="37" t="n">
-        <v>0.2466851680542707</v>
+        <v>0.209259743656814</v>
       </c>
       <c r="I5" s="37" t="n">
-        <v>0.2379535990481856</v>
+        <v>0.2009040683073832</v>
       </c>
       <c r="J5" s="37" t="n">
-        <v>0.2298190175237001</v>
+        <v>0.1931900507123883</v>
       </c>
       <c r="K5" s="37" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="L5" s="37" t="n">
-        <v>0.2168021680216802</v>
+        <v>0.1801801801801802</v>
       </c>
       <c r="M5" s="37" t="n">
-        <v>0.2116402116402117</v>
+        <v>0.1746724890829695</v>
       </c>
       <c r="N5" s="37" t="n">
-        <v>0.20671834625323</v>
+        <v>0.1694915254237288</v>
       </c>
       <c r="O5" s="37" t="n">
-        <v>0.202020202020202</v>
+        <v>0.1646090534979424</v>
       </c>
       <c r="P5" s="37" t="n">
-        <v>0.1975308641975309</v>
+        <v>0.16</v>
       </c>
       <c r="Q5" s="37" t="n">
-        <v>0.1932367149758454</v>
+        <v>0.1556420233463035</v>
       </c>
       <c r="R5" s="37" t="n">
-        <v>0.1891252955082743</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="S5" s="37" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1476014760147601</v>
       </c>
       <c r="T5" s="37" t="n">
-        <v>0.18140589569161</v>
+        <v>0.1438848920863309</v>
       </c>
       <c r="U5" s="37" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.1403508771929824</v>
       </c>
     </row>
     <row r="6">
@@ -3932,606 +4338,606 @@
         </is>
       </c>
       <c r="B6" s="38" t="n">
-        <v>0.3530895334174022</v>
+        <v>0.3444034440344403</v>
       </c>
       <c r="C6" s="38" t="n">
-        <v>0.3371462974111981</v>
+        <v>0.3198172472872644</v>
       </c>
       <c r="D6" s="38" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.2985074626865671</v>
       </c>
       <c r="E6" s="38" t="n">
-        <v>0.3646308113035551</v>
+        <v>0.3233629749393694</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>0.3993344425956739</v>
+        <v>0.3423680456490728</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>0.384122919334187</v>
+        <v>0.3275109170305677</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>0.370027752081406</v>
+        <v>0.313889615485221</v>
       </c>
       <c r="I6" s="38" t="n">
-        <v>0.3569303985722784</v>
+        <v>0.3013561024610748</v>
       </c>
       <c r="J6" s="38" t="n">
-        <v>0.3447285262855502</v>
+        <v>0.2897850760685825</v>
       </c>
       <c r="K6" s="38" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="L6" s="38" t="n">
-        <v>0.3360433604336043</v>
+        <v>0.2792792792792793</v>
       </c>
       <c r="M6" s="38" t="n">
-        <v>0.3386243386243387</v>
+        <v>0.2794759825327511</v>
       </c>
       <c r="N6" s="38" t="n">
-        <v>0.3410852713178294</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="O6" s="38" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.2798353909465021</v>
       </c>
       <c r="P6" s="38" t="n">
-        <v>0.345679012345679</v>
+        <v>0.28</v>
       </c>
       <c r="Q6" s="38" t="n">
-        <v>0.3478260869565218</v>
+        <v>0.2801556420233463</v>
       </c>
       <c r="R6" s="38" t="n">
-        <v>0.3498817966903074</v>
+        <v>0.2803030303030303</v>
       </c>
       <c r="S6" s="38" t="n">
-        <v>0.3518518518518518</v>
+        <v>0.2804428044280443</v>
       </c>
       <c r="T6" s="38" t="n">
-        <v>0.3537414965986395</v>
+        <v>0.2805755395683453</v>
       </c>
       <c r="U6" s="38" t="n">
-        <v>0.3555555555555556</v>
+        <v>0.2807017543859649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Analyst  (wt 2.5)</t>
+          <t>Junior PM  (wt 6)</t>
         </is>
       </c>
       <c r="B7" s="37" t="n">
-        <v>0.03152585119798234</v>
+        <v>0</v>
       </c>
       <c r="C7" s="37" t="n">
-        <v>0.06773028296207104</v>
+        <v>0</v>
       </c>
       <c r="D7" s="37" t="n">
-        <v>0.1008064516129032</v>
+        <v>0</v>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.113947128532361</v>
+        <v>0.04850444624090541</v>
       </c>
       <c r="F7" s="37" t="n">
-        <v>0.1247920133111481</v>
+        <v>0.0855920114122682</v>
       </c>
       <c r="G7" s="37" t="n">
-        <v>0.1280409731113956</v>
+        <v>0.08187772925764192</v>
       </c>
       <c r="H7" s="37" t="n">
-        <v>0.1310514955288313</v>
+        <v>0.07847240387130526</v>
       </c>
       <c r="I7" s="37" t="n">
-        <v>0.1338488994646044</v>
+        <v>0.0753390256152687</v>
       </c>
       <c r="J7" s="37" t="n">
-        <v>0.1364550416546969</v>
+        <v>0.07244626901714563</v>
       </c>
       <c r="K7" s="37" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.06976744186046512</v>
       </c>
       <c r="L7" s="37" t="n">
-        <v>0.1490514905149052</v>
+        <v>0.07432432432432433</v>
       </c>
       <c r="M7" s="37" t="n">
-        <v>0.1587301587301587</v>
+        <v>0.07860262008733625</v>
       </c>
       <c r="N7" s="37" t="n">
-        <v>0.1679586563307493</v>
+        <v>0.0826271186440678</v>
       </c>
       <c r="O7" s="37" t="n">
-        <v>0.1767676767676768</v>
+        <v>0.08641975308641973</v>
       </c>
       <c r="P7" s="37" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.09</v>
       </c>
       <c r="Q7" s="37" t="n">
-        <v>0.1932367149758454</v>
+        <v>0.09338521400778212</v>
       </c>
       <c r="R7" s="37" t="n">
-        <v>0.2009456264775414</v>
+        <v>0.09659090909090909</v>
       </c>
       <c r="S7" s="37" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.0996309963099631</v>
       </c>
       <c r="T7" s="37" t="n">
-        <v>0.2154195011337868</v>
+        <v>0.1025179856115108</v>
       </c>
       <c r="U7" s="37" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>CEO  (wt 8)</t>
+          <t>Senior Analyst  (wt 4)</t>
         </is>
       </c>
       <c r="B8" s="38" t="n">
-        <v>0.1765447667087011</v>
+        <v>0.02460024600246002</v>
       </c>
       <c r="C8" s="38" t="n">
-        <v>0.168573148705599</v>
+        <v>0.05139920045688178</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="E8" s="38" t="n">
-        <v>0.145852324521422</v>
+        <v>0.06467259498787389</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>0.1331114808652246</v>
+        <v>0.05706134094151213</v>
       </c>
       <c r="G8" s="38" t="n">
-        <v>0.1280409731113956</v>
+        <v>0.06550218340611354</v>
       </c>
       <c r="H8" s="38" t="n">
-        <v>0.1233425840271353</v>
+        <v>0.07324091027988491</v>
       </c>
       <c r="I8" s="38" t="n">
-        <v>0.1189767995240928</v>
+        <v>0.08036162732295328</v>
       </c>
       <c r="J8" s="38" t="n">
-        <v>0.1149095087618501</v>
+        <v>0.08693552282057475</v>
       </c>
       <c r="K8" s="38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="L8" s="38" t="n">
-        <v>0.1084010840108401</v>
+        <v>0.0945945945945946</v>
       </c>
       <c r="M8" s="38" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.0960698689956332</v>
       </c>
       <c r="N8" s="38" t="n">
-        <v>0.103359173126615</v>
+        <v>0.09745762711864406</v>
       </c>
       <c r="O8" s="38" t="n">
-        <v>0.101010101010101</v>
+        <v>0.09876543209876543</v>
       </c>
       <c r="P8" s="38" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.1</v>
       </c>
       <c r="Q8" s="38" t="n">
-        <v>0.0966183574879227</v>
+        <v>0.1011673151750973</v>
       </c>
       <c r="R8" s="38" t="n">
-        <v>0.09456264775413713</v>
+        <v>0.1022727272727273</v>
       </c>
       <c r="S8" s="38" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.1033210332103321</v>
       </c>
       <c r="T8" s="38" t="n">
-        <v>0.09070294784580499</v>
+        <v>0.1043165467625899</v>
       </c>
       <c r="U8" s="38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.1052631578947368</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>CFO  (wt 3)</t>
+          <t>Analyst  (wt 2.5)</t>
         </is>
       </c>
       <c r="B9" s="37" t="n">
-        <v>0.01324085750315259</v>
+        <v>0.03075030750307502</v>
       </c>
       <c r="C9" s="37" t="n">
-        <v>0.01264298615291993</v>
+        <v>0.06424900057110222</v>
       </c>
       <c r="D9" s="37" t="n">
-        <v>0.01209677419354839</v>
+        <v>0.09328358208955223</v>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.01093892433910666</v>
+        <v>0.1010509296685529</v>
       </c>
       <c r="F9" s="37" t="n">
-        <v>0.009983361064891848</v>
+        <v>0.1069900142653352</v>
       </c>
       <c r="G9" s="37" t="n">
-        <v>0.01728553137003841</v>
+        <v>0.1091703056768559</v>
       </c>
       <c r="H9" s="37" t="n">
-        <v>0.02405180388529139</v>
+        <v>0.1111692388176825</v>
       </c>
       <c r="I9" s="37" t="n">
-        <v>0.03033908387864367</v>
+        <v>0.113008538422903</v>
       </c>
       <c r="J9" s="37" t="n">
-        <v>0.03619649525998277</v>
+        <v>0.1147065926104806</v>
       </c>
       <c r="K9" s="37" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.1162790697674419</v>
       </c>
       <c r="L9" s="37" t="n">
-        <v>0.04065040650406504</v>
+        <v>0.1238738738738739</v>
       </c>
       <c r="M9" s="37" t="n">
-        <v>0.03968253968253969</v>
+        <v>0.1310043668122271</v>
       </c>
       <c r="N9" s="37" t="n">
-        <v>0.03875968992248062</v>
+        <v>0.1377118644067797</v>
       </c>
       <c r="O9" s="37" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.1440329218106996</v>
       </c>
       <c r="P9" s="37" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.15</v>
       </c>
       <c r="Q9" s="37" t="n">
-        <v>0.03623188405797102</v>
+        <v>0.1556420233463035</v>
       </c>
       <c r="R9" s="37" t="n">
-        <v>0.03546099290780142</v>
+        <v>0.1609848484848485</v>
       </c>
       <c r="S9" s="37" t="n">
-        <v>0.03472222222222222</v>
+        <v>0.1660516605166052</v>
       </c>
       <c r="T9" s="37" t="n">
-        <v>0.03401360544217687</v>
+        <v>0.170863309352518</v>
       </c>
       <c r="U9" s="37" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.1754385964912281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>COO  (wt 3)</t>
+          <t>CEO  (wt 8)</t>
         </is>
       </c>
       <c r="B10" s="38" t="n">
-        <v>0.03310214375788146</v>
+        <v>0.1722017220172201</v>
       </c>
       <c r="C10" s="38" t="n">
-        <v>0.03160746538229982</v>
+        <v>0.1599086236436322</v>
       </c>
       <c r="D10" s="38" t="n">
-        <v>0.03024193548387097</v>
+        <v>0.1492537313432836</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>0.02734731084776663</v>
+        <v>0.1293451899757478</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>0.02495840266222962</v>
+        <v>0.1141226818830243</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>0.02880921895006402</v>
+        <v>0.1091703056768559</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>0.03237742830712302</v>
+        <v>0.104629871828407</v>
       </c>
       <c r="I10" s="38" t="n">
-        <v>0.03569303985722785</v>
+        <v>0.1004520341536916</v>
       </c>
       <c r="J10" s="38" t="n">
-        <v>0.0387819592071244</v>
+        <v>0.09659502535619416</v>
       </c>
       <c r="K10" s="38" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="L10" s="38" t="n">
-        <v>0.04065040650406504</v>
+        <v>0.0900900900900901</v>
       </c>
       <c r="M10" s="38" t="n">
-        <v>0.03968253968253969</v>
+        <v>0.08733624454148473</v>
       </c>
       <c r="N10" s="38" t="n">
-        <v>0.03875968992248062</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="O10" s="38" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.08230452674897119</v>
       </c>
       <c r="P10" s="38" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.08</v>
       </c>
       <c r="Q10" s="38" t="n">
-        <v>0.03623188405797102</v>
+        <v>0.07782101167315175</v>
       </c>
       <c r="R10" s="38" t="n">
-        <v>0.03546099290780142</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="S10" s="38" t="n">
-        <v>0.03472222222222222</v>
+        <v>0.07380073800738007</v>
       </c>
       <c r="T10" s="38" t="n">
-        <v>0.03401360544217687</v>
+        <v>0.07194244604316546</v>
       </c>
       <c r="U10" s="38" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>IR  (wt 1)</t>
+          <t>CFO  (wt 3)</t>
         </is>
       </c>
       <c r="B11" s="37" t="n">
-        <v>0.02837326607818411</v>
+        <v>0.01291512915129151</v>
       </c>
       <c r="C11" s="37" t="n">
-        <v>0.03461770018061408</v>
+        <v>0.01199314677327242</v>
       </c>
       <c r="D11" s="37" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.01119402985074627</v>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.03646308113035551</v>
+        <v>0.009700889248181084</v>
       </c>
       <c r="F11" s="37" t="n">
-        <v>0.03327787021630615</v>
+        <v>0.008559201141226821</v>
       </c>
       <c r="G11" s="37" t="n">
-        <v>0.03201024327784891</v>
+        <v>0.01473799126637555</v>
       </c>
       <c r="H11" s="37" t="n">
-        <v>0.03083564600678384</v>
+        <v>0.02040282500653937</v>
       </c>
       <c r="I11" s="37" t="n">
-        <v>0.0297441998810232</v>
+        <v>0.02561526870919136</v>
       </c>
       <c r="J11" s="37" t="n">
-        <v>0.02872737719046252</v>
+        <v>0.03042743298720117</v>
       </c>
       <c r="K11" s="37" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.03488372093023256</v>
       </c>
       <c r="L11" s="37" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M11" s="37" t="n">
-        <v>0.02645502645502646</v>
+        <v>0.03275109170305677</v>
       </c>
       <c r="N11" s="37" t="n">
-        <v>0.02583979328165375</v>
+        <v>0.03177966101694915</v>
       </c>
       <c r="O11" s="37" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.0308641975308642</v>
       </c>
       <c r="P11" s="37" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.03</v>
       </c>
       <c r="Q11" s="37" t="n">
-        <v>0.02415458937198068</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="R11" s="37" t="n">
-        <v>0.02364066193853428</v>
+        <v>0.02840909090909091</v>
       </c>
       <c r="S11" s="37" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.02767527675276753</v>
       </c>
       <c r="T11" s="37" t="n">
-        <v>0.02267573696145125</v>
+        <v>0.02697841726618705</v>
       </c>
       <c r="U11" s="37" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Support  (wt 1)</t>
+          <t>COO  (wt 3)</t>
         </is>
       </c>
       <c r="B12" s="38" t="n">
-        <v>0.01103404791929382</v>
+        <v>0.03228782287822878</v>
       </c>
       <c r="C12" s="38" t="n">
-        <v>0.01053582179409994</v>
+        <v>0.02998286693318104</v>
       </c>
       <c r="D12" s="38" t="n">
-        <v>0.01008064516129032</v>
+        <v>0.02798507462686567</v>
       </c>
       <c r="E12" s="38" t="n">
-        <v>0.009115770282588878</v>
+        <v>0.02425222312045271</v>
       </c>
       <c r="F12" s="38" t="n">
-        <v>0.008319467554076539</v>
+        <v>0.02139800285306705</v>
       </c>
       <c r="G12" s="38" t="n">
-        <v>0.009603072983354674</v>
+        <v>0.02456331877729257</v>
       </c>
       <c r="H12" s="38" t="n">
-        <v>0.01079247610237434</v>
+        <v>0.02746534135495684</v>
       </c>
       <c r="I12" s="38" t="n">
-        <v>0.01189767995240928</v>
+        <v>0.03013561024610748</v>
       </c>
       <c r="J12" s="38" t="n">
-        <v>0.01292731973570813</v>
+        <v>0.03260082105771554</v>
       </c>
       <c r="K12" s="38" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.03488372093023256</v>
       </c>
       <c r="L12" s="38" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M12" s="38" t="n">
-        <v>0.01322751322751323</v>
+        <v>0.03275109170305677</v>
       </c>
       <c r="N12" s="38" t="n">
-        <v>0.01291989664082687</v>
+        <v>0.03177966101694915</v>
       </c>
       <c r="O12" s="38" t="n">
-        <v>0.01262626262626263</v>
+        <v>0.0308641975308642</v>
       </c>
       <c r="P12" s="38" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.03</v>
       </c>
       <c r="Q12" s="38" t="n">
-        <v>0.01207729468599034</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="R12" s="38" t="n">
-        <v>0.01182033096926714</v>
+        <v>0.02840909090909091</v>
       </c>
       <c r="S12" s="38" t="n">
-        <v>0.01157407407407407</v>
+        <v>0.02767527675276753</v>
       </c>
       <c r="T12" s="38" t="n">
-        <v>0.01133786848072562</v>
+        <v>0.02697841726618705</v>
       </c>
       <c r="U12" s="38" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Execution  (wt 2)</t>
+          <t>IR  (wt 1)</t>
         </is>
       </c>
       <c r="B13" s="37" t="n">
-        <v>0</v>
+        <v>0.02767527675276752</v>
       </c>
       <c r="C13" s="37" t="n">
-        <v>0</v>
+        <v>0.03283837806967447</v>
       </c>
       <c r="D13" s="37" t="n">
-        <v>0</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0</v>
+        <v>0.03233629749393695</v>
       </c>
       <c r="F13" s="37" t="n">
-        <v>0</v>
+        <v>0.02853067047075606</v>
       </c>
       <c r="G13" s="37" t="n">
-        <v>0.006402048655569783</v>
+        <v>0.02729257641921397</v>
       </c>
       <c r="H13" s="37" t="n">
-        <v>0.01233425840271354</v>
+        <v>0.02615746795710176</v>
       </c>
       <c r="I13" s="37" t="n">
-        <v>0.01784651992861392</v>
+        <v>0.0251130085384229</v>
       </c>
       <c r="J13" s="37" t="n">
-        <v>0.02298190175237001</v>
+        <v>0.02414875633904854</v>
       </c>
       <c r="K13" s="37" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="L13" s="37" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.02252252252252252</v>
       </c>
       <c r="M13" s="37" t="n">
-        <v>0.02645502645502646</v>
+        <v>0.02183406113537118</v>
       </c>
       <c r="N13" s="37" t="n">
-        <v>0.02583979328165375</v>
+        <v>0.0211864406779661</v>
       </c>
       <c r="O13" s="37" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.0205761316872428</v>
       </c>
       <c r="P13" s="37" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.02</v>
       </c>
       <c r="Q13" s="37" t="n">
-        <v>0.02415458937198068</v>
+        <v>0.01945525291828794</v>
       </c>
       <c r="R13" s="37" t="n">
-        <v>0.02364066193853428</v>
+        <v>0.01893939393939394</v>
       </c>
       <c r="S13" s="37" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.01845018450184502</v>
       </c>
       <c r="T13" s="37" t="n">
-        <v>0.02267573696145125</v>
+        <v>0.01798561151079137</v>
       </c>
       <c r="U13" s="37" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.01754385964912281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Risk  (wt 2)</t>
+          <t>Support  (wt 1)</t>
         </is>
       </c>
       <c r="B14" s="38" t="n">
-        <v>0</v>
+        <v>0.01076260762607626</v>
       </c>
       <c r="C14" s="38" t="n">
-        <v>0</v>
+        <v>0.009994288977727013</v>
       </c>
       <c r="D14" s="38" t="n">
-        <v>0</v>
+        <v>0.009328358208955223</v>
       </c>
       <c r="E14" s="38" t="n">
-        <v>0</v>
+        <v>0.008084074373484237</v>
       </c>
       <c r="F14" s="38" t="n">
-        <v>0</v>
+        <v>0.007132667617689016</v>
       </c>
       <c r="G14" s="38" t="n">
-        <v>0.006402048655569783</v>
+        <v>0.008187772925764192</v>
       </c>
       <c r="H14" s="38" t="n">
-        <v>0.01233425840271354</v>
+        <v>0.009155113784985614</v>
       </c>
       <c r="I14" s="38" t="n">
-        <v>0.01784651992861392</v>
+        <v>0.01004520341536916</v>
       </c>
       <c r="J14" s="38" t="n">
-        <v>0.02298190175237001</v>
+        <v>0.01086694035257184</v>
       </c>
       <c r="K14" s="38" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.01162790697674419</v>
       </c>
       <c r="L14" s="38" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.01126126126126126</v>
       </c>
       <c r="M14" s="38" t="n">
-        <v>0.02645502645502646</v>
+        <v>0.01091703056768559</v>
       </c>
       <c r="N14" s="38" t="n">
-        <v>0.02583979328165375</v>
+        <v>0.01059322033898305</v>
       </c>
       <c r="O14" s="38" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.0102880658436214</v>
       </c>
       <c r="P14" s="38" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.01</v>
       </c>
       <c r="Q14" s="38" t="n">
-        <v>0.02415458937198068</v>
+        <v>0.009727626459143969</v>
       </c>
       <c r="R14" s="38" t="n">
-        <v>0.02364066193853428</v>
+        <v>0.00946969696969697</v>
       </c>
       <c r="S14" s="38" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.009225092250922509</v>
       </c>
       <c r="T14" s="38" t="n">
-        <v>0.02267573696145125</v>
+        <v>0.008992805755395683</v>
       </c>
       <c r="U14" s="38" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.008771929824561403</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>Compliance  (wt 1)</t>
+          <t>Execution  (wt 2)</t>
         </is>
       </c>
       <c r="B15" s="37" t="n">
@@ -4550,135 +4956,269 @@
         <v>0</v>
       </c>
       <c r="G15" s="37" t="n">
-        <v>0.003201024327784891</v>
+        <v>0.005458515283842795</v>
       </c>
       <c r="H15" s="37" t="n">
-        <v>0.006167129201356768</v>
+        <v>0.0104629871828407</v>
       </c>
       <c r="I15" s="37" t="n">
-        <v>0.00892325996430696</v>
+        <v>0.01506780512305374</v>
       </c>
       <c r="J15" s="37" t="n">
-        <v>0.01149095087618501</v>
+        <v>0.01931900507123883</v>
       </c>
       <c r="K15" s="37" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="L15" s="37" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.02252252252252252</v>
       </c>
       <c r="M15" s="37" t="n">
-        <v>0.01322751322751323</v>
+        <v>0.02183406113537118</v>
       </c>
       <c r="N15" s="37" t="n">
-        <v>0.01291989664082687</v>
+        <v>0.0211864406779661</v>
       </c>
       <c r="O15" s="37" t="n">
-        <v>0.01262626262626263</v>
+        <v>0.0205761316872428</v>
       </c>
       <c r="P15" s="37" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.02</v>
       </c>
       <c r="Q15" s="37" t="n">
-        <v>0.01207729468599034</v>
+        <v>0.01945525291828794</v>
       </c>
       <c r="R15" s="37" t="n">
-        <v>0.01182033096926714</v>
+        <v>0.01893939393939394</v>
       </c>
       <c r="S15" s="37" t="n">
-        <v>0.01157407407407407</v>
+        <v>0.01845018450184502</v>
       </c>
       <c r="T15" s="37" t="n">
-        <v>0.01133786848072562</v>
+        <v>0.01798561151079137</v>
       </c>
       <c r="U15" s="37" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.01754385964912281</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Risk  (wt 2)</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>0.005458515283842795</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>0.0104629871828407</v>
+      </c>
+      <c r="I16" s="38" t="n">
+        <v>0.01506780512305374</v>
+      </c>
+      <c r="J16" s="38" t="n">
+        <v>0.01931900507123883</v>
+      </c>
+      <c r="K16" s="38" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="L16" s="38" t="n">
+        <v>0.02252252252252252</v>
+      </c>
+      <c r="M16" s="38" t="n">
+        <v>0.02183406113537118</v>
+      </c>
+      <c r="N16" s="38" t="n">
+        <v>0.0211864406779661</v>
+      </c>
+      <c r="O16" s="38" t="n">
+        <v>0.0205761316872428</v>
+      </c>
+      <c r="P16" s="38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q16" s="38" t="n">
+        <v>0.01945525291828794</v>
+      </c>
+      <c r="R16" s="38" t="n">
+        <v>0.01893939393939394</v>
+      </c>
+      <c r="S16" s="38" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="T16" s="38" t="n">
+        <v>0.01798561151079137</v>
+      </c>
+      <c r="U16" s="38" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Compliance  (wt 1)</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="37" t="n">
+        <v>0.002729257641921398</v>
+      </c>
+      <c r="H17" s="37" t="n">
+        <v>0.005231493591420351</v>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>0.00753390256152687</v>
+      </c>
+      <c r="J17" s="37" t="n">
+        <v>0.009659502535619417</v>
+      </c>
+      <c r="K17" s="37" t="n">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="L17" s="37" t="n">
+        <v>0.01126126126126126</v>
+      </c>
+      <c r="M17" s="37" t="n">
+        <v>0.01091703056768559</v>
+      </c>
+      <c r="N17" s="37" t="n">
+        <v>0.01059322033898305</v>
+      </c>
+      <c r="O17" s="37" t="n">
+        <v>0.0102880658436214</v>
+      </c>
+      <c r="P17" s="37" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q17" s="37" t="n">
+        <v>0.009727626459143969</v>
+      </c>
+      <c r="R17" s="37" t="n">
+        <v>0.00946969696969697</v>
+      </c>
+      <c r="S17" s="37" t="n">
+        <v>0.009225092250922509</v>
+      </c>
+      <c r="T17" s="37" t="n">
+        <v>0.008992805755395683</v>
+      </c>
+      <c r="U17" s="37" t="n">
+        <v>0.008771929824561403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>Total (check)</t>
         </is>
       </c>
-      <c r="B16" s="43">
-        <f>SUM(B5:B15)</f>
-        <v/>
-      </c>
-      <c r="C16" s="43">
-        <f>SUM(C5:C15)</f>
-        <v/>
-      </c>
-      <c r="D16" s="43">
-        <f>SUM(D5:D15)</f>
-        <v/>
-      </c>
-      <c r="E16" s="43">
-        <f>SUM(E5:E15)</f>
-        <v/>
-      </c>
-      <c r="F16" s="43">
-        <f>SUM(F5:F15)</f>
-        <v/>
-      </c>
-      <c r="G16" s="43">
-        <f>SUM(G5:G15)</f>
-        <v/>
-      </c>
-      <c r="H16" s="43">
-        <f>SUM(H5:H15)</f>
-        <v/>
-      </c>
-      <c r="I16" s="43">
-        <f>SUM(I5:I15)</f>
-        <v/>
-      </c>
-      <c r="J16" s="43">
-        <f>SUM(J5:J15)</f>
-        <v/>
-      </c>
-      <c r="K16" s="43">
-        <f>SUM(K5:K15)</f>
-        <v/>
-      </c>
-      <c r="L16" s="43">
-        <f>SUM(L5:L15)</f>
-        <v/>
-      </c>
-      <c r="M16" s="43">
-        <f>SUM(M5:M15)</f>
-        <v/>
-      </c>
-      <c r="N16" s="43">
-        <f>SUM(N5:N15)</f>
-        <v/>
-      </c>
-      <c r="O16" s="43">
-        <f>SUM(O5:O15)</f>
-        <v/>
-      </c>
-      <c r="P16" s="43">
-        <f>SUM(P5:P15)</f>
-        <v/>
-      </c>
-      <c r="Q16" s="43">
-        <f>SUM(Q5:Q15)</f>
-        <v/>
-      </c>
-      <c r="R16" s="43">
-        <f>SUM(R5:R15)</f>
-        <v/>
-      </c>
-      <c r="S16" s="43">
-        <f>SUM(S5:S15)</f>
-        <v/>
-      </c>
-      <c r="T16" s="43">
-        <f>SUM(T5:T15)</f>
-        <v/>
-      </c>
-      <c r="U16" s="43">
-        <f>SUM(U5:U15)</f>
+      <c r="B18" s="43">
+        <f>SUM(B5:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="43">
+        <f>SUM(C5:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="43">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="43">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="43">
+        <f>SUM(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="43">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="43">
+        <f>SUM(H5:H17)</f>
+        <v/>
+      </c>
+      <c r="I18" s="43">
+        <f>SUM(I5:I17)</f>
+        <v/>
+      </c>
+      <c r="J18" s="43">
+        <f>SUM(J5:J17)</f>
+        <v/>
+      </c>
+      <c r="K18" s="43">
+        <f>SUM(K5:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="43">
+        <f>SUM(L5:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="43">
+        <f>SUM(M5:M17)</f>
+        <v/>
+      </c>
+      <c r="N18" s="43">
+        <f>SUM(N5:N17)</f>
+        <v/>
+      </c>
+      <c r="O18" s="43">
+        <f>SUM(O5:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="43">
+        <f>SUM(P5:P17)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="43">
+        <f>SUM(Q5:Q17)</f>
+        <v/>
+      </c>
+      <c r="R18" s="43">
+        <f>SUM(R5:R17)</f>
+        <v/>
+      </c>
+      <c r="S18" s="43">
+        <f>SUM(S5:S17)</f>
+        <v/>
+      </c>
+      <c r="T18" s="43">
+        <f>SUM(T5:T17)</f>
+        <v/>
+      </c>
+      <c r="U18" s="43">
+        <f>SUM(U5:U17)</f>
         <v/>
       </c>
     </row>
@@ -4698,7 +5238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4812,64 +5352,64 @@
         </is>
       </c>
       <c r="B5" s="39" t="n">
-        <v>0.3530895334174022</v>
+        <v>0.3444034440344403</v>
       </c>
       <c r="C5" s="39" t="n">
-        <v>0.3371462974111981</v>
+        <v>0.3198172472872644</v>
       </c>
       <c r="D5" s="39" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.2985074626865671</v>
       </c>
       <c r="E5" s="39" t="n">
-        <v>0.2917046490428441</v>
+        <v>0.2586903799514956</v>
       </c>
       <c r="F5" s="39" t="n">
-        <v>0.2662229617304492</v>
+        <v>0.2282453637660485</v>
       </c>
       <c r="G5" s="39" t="n">
-        <v>0.2560819462227913</v>
+        <v>0.2183406113537118</v>
       </c>
       <c r="H5" s="39" t="n">
-        <v>0.2466851680542707</v>
+        <v>0.209259743656814</v>
       </c>
       <c r="I5" s="39" t="n">
-        <v>0.2379535990481856</v>
+        <v>0.2009040683073832</v>
       </c>
       <c r="J5" s="39" t="n">
-        <v>0.2298190175237001</v>
+        <v>0.1931900507123883</v>
       </c>
       <c r="K5" s="39" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="L5" s="39" t="n">
-        <v>0.2168021680216802</v>
+        <v>0.1801801801801802</v>
       </c>
       <c r="M5" s="39" t="n">
-        <v>0.2116402116402117</v>
+        <v>0.1746724890829695</v>
       </c>
       <c r="N5" s="39" t="n">
-        <v>0.20671834625323</v>
+        <v>0.1694915254237288</v>
       </c>
       <c r="O5" s="39" t="n">
-        <v>0.202020202020202</v>
+        <v>0.1646090534979424</v>
       </c>
       <c r="P5" s="39" t="n">
-        <v>0.1975308641975309</v>
+        <v>0.16</v>
       </c>
       <c r="Q5" s="39" t="n">
-        <v>0.1932367149758454</v>
+        <v>0.1556420233463035</v>
       </c>
       <c r="R5" s="39" t="n">
-        <v>0.1891252955082743</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="S5" s="39" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1476014760147601</v>
       </c>
       <c r="T5" s="39" t="n">
-        <v>0.18140589569161</v>
+        <v>0.1438848920863309</v>
       </c>
       <c r="U5" s="39" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.1403508771929824</v>
       </c>
     </row>
     <row r="6">
@@ -4879,734 +5419,868 @@
         </is>
       </c>
       <c r="B6" s="40" t="n">
-        <v>0.1765447667087011</v>
+        <v>0.1722017220172201</v>
       </c>
       <c r="C6" s="40" t="n">
-        <v>0.168573148705599</v>
+        <v>0.1599086236436322</v>
       </c>
       <c r="D6" s="40" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.1492537313432836</v>
       </c>
       <c r="E6" s="40" t="n">
-        <v>0.145852324521422</v>
+        <v>0.1293451899757478</v>
       </c>
       <c r="F6" s="40" t="n">
-        <v>0.1331114808652246</v>
+        <v>0.1141226818830243</v>
       </c>
       <c r="G6" s="40" t="n">
-        <v>0.1280409731113956</v>
+        <v>0.1091703056768559</v>
       </c>
       <c r="H6" s="40" t="n">
-        <v>0.1233425840271353</v>
+        <v>0.104629871828407</v>
       </c>
       <c r="I6" s="40" t="n">
-        <v>0.1189767995240928</v>
+        <v>0.1004520341536916</v>
       </c>
       <c r="J6" s="40" t="n">
-        <v>0.1149095087618501</v>
+        <v>0.09659502535619416</v>
       </c>
       <c r="K6" s="40" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="L6" s="40" t="n">
-        <v>0.1084010840108401</v>
+        <v>0.0900900900900901</v>
       </c>
       <c r="M6" s="40" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.08733624454148473</v>
       </c>
       <c r="N6" s="40" t="n">
-        <v>0.103359173126615</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="O6" s="40" t="n">
-        <v>0.101010101010101</v>
+        <v>0.08230452674897119</v>
       </c>
       <c r="P6" s="40" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.08</v>
       </c>
       <c r="Q6" s="40" t="n">
-        <v>0.0966183574879227</v>
+        <v>0.07782101167315175</v>
       </c>
       <c r="R6" s="40" t="n">
-        <v>0.09456264775413713</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="S6" s="40" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.07380073800738007</v>
       </c>
       <c r="T6" s="40" t="n">
-        <v>0.09070294784580499</v>
+        <v>0.07194244604316546</v>
       </c>
       <c r="U6" s="40" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>Analyst  (wt 2.5)</t>
+          <t>Junior PM  (wt 6)</t>
         </is>
       </c>
       <c r="B7" s="39" t="n">
-        <v>0.0551702395964691</v>
+        <v>0.1291512915129151</v>
       </c>
       <c r="C7" s="39" t="n">
-        <v>0.05267910897049969</v>
+        <v>0.1199314677327241</v>
       </c>
       <c r="D7" s="39" t="n">
-        <v>0.05040322580645161</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="E7" s="39" t="n">
-        <v>0.04557885141294439</v>
+        <v>0.09700889248181083</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>0.04159733777038269</v>
+        <v>0.0855920114122682</v>
       </c>
       <c r="G7" s="39" t="n">
-        <v>0.04001280409731114</v>
+        <v>0.08187772925764192</v>
       </c>
       <c r="H7" s="39" t="n">
-        <v>0.03854455750847979</v>
+        <v>0.07847240387130526</v>
       </c>
       <c r="I7" s="39" t="n">
-        <v>0.037180249851279</v>
+        <v>0.0753390256152687</v>
       </c>
       <c r="J7" s="39" t="n">
-        <v>0.03590922148807815</v>
+        <v>0.07244626901714563</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>0.03472222222222222</v>
+        <v>0.06976744186046512</v>
       </c>
       <c r="L7" s="39" t="n">
-        <v>0.03387533875338754</v>
+        <v>0.06756756756756757</v>
       </c>
       <c r="M7" s="39" t="n">
-        <v>0.03306878306878307</v>
+        <v>0.06550218340611354</v>
       </c>
       <c r="N7" s="39" t="n">
-        <v>0.03229974160206718</v>
+        <v>0.0635593220338983</v>
       </c>
       <c r="O7" s="39" t="n">
-        <v>0.03156565656565657</v>
+        <v>0.06172839506172839</v>
       </c>
       <c r="P7" s="39" t="n">
-        <v>0.0308641975308642</v>
+        <v>0.06</v>
       </c>
       <c r="Q7" s="39" t="n">
-        <v>0.03019323671497585</v>
+        <v>0.05836575875486381</v>
       </c>
       <c r="R7" s="39" t="n">
-        <v>0.02955082742316785</v>
+        <v>0.05681818181818182</v>
       </c>
       <c r="S7" s="39" t="n">
-        <v>0.02893518518518518</v>
+        <v>0.05535055350553506</v>
       </c>
       <c r="T7" s="39" t="n">
-        <v>0.02834467120181406</v>
+        <v>0.0539568345323741</v>
       </c>
       <c r="U7" s="39" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.05263157894736842</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>CEO  (wt 8)</t>
+          <t>Senior Analyst  (wt 4)</t>
         </is>
       </c>
       <c r="B8" s="40" t="n">
-        <v>0.1765447667087011</v>
+        <v>0.08610086100861007</v>
       </c>
       <c r="C8" s="40" t="n">
-        <v>0.168573148705599</v>
+        <v>0.0799543118218161</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0.1612903225806452</v>
+        <v>0.07462686567164178</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>0.145852324521422</v>
+        <v>0.06467259498787389</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>0.1331114808652246</v>
+        <v>0.05706134094151213</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>0.1280409731113956</v>
+        <v>0.05458515283842795</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>0.1233425840271353</v>
+        <v>0.05231493591420351</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>0.1189767995240928</v>
+        <v>0.0502260170768458</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>0.1149095087618501</v>
+        <v>0.04829751267809708</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.04651162790697674</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>0.1084010840108401</v>
+        <v>0.04504504504504505</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>0.1058201058201058</v>
+        <v>0.04366812227074236</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>0.103359173126615</v>
+        <v>0.0423728813559322</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>0.101010101010101</v>
+        <v>0.0411522633744856</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>0.09876543209876543</v>
+        <v>0.04</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>0.0966183574879227</v>
+        <v>0.03891050583657588</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>0.09456264775413713</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>0.09259259259259259</v>
+        <v>0.03690036900369004</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>0.09070294784580499</v>
+        <v>0.03597122302158273</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.03508771929824561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>CFO  (wt 3)</t>
+          <t>Analyst  (wt 2.5)</t>
         </is>
       </c>
       <c r="B9" s="39" t="n">
-        <v>0.06620428751576292</v>
+        <v>0.0538130381303813</v>
       </c>
       <c r="C9" s="39" t="n">
-        <v>0.06321493076459964</v>
+        <v>0.04997144488863507</v>
       </c>
       <c r="D9" s="39" t="n">
-        <v>0.06048387096774193</v>
+        <v>0.04664179104477612</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>0.05469462169553327</v>
+        <v>0.04042037186742118</v>
       </c>
       <c r="F9" s="39" t="n">
-        <v>0.04991680532445923</v>
+        <v>0.03566333808844508</v>
       </c>
       <c r="G9" s="39" t="n">
-        <v>0.04801536491677337</v>
+        <v>0.03411572052401746</v>
       </c>
       <c r="H9" s="39" t="n">
-        <v>0.04625346901017575</v>
+        <v>0.03269683494637719</v>
       </c>
       <c r="I9" s="39" t="n">
-        <v>0.0446162998215348</v>
+        <v>0.03139126067302862</v>
       </c>
       <c r="J9" s="39" t="n">
-        <v>0.04309106578569377</v>
+        <v>0.03018594542381068</v>
       </c>
       <c r="K9" s="39" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.02906976744186046</v>
       </c>
       <c r="L9" s="39" t="n">
-        <v>0.04065040650406504</v>
+        <v>0.02815315315315315</v>
       </c>
       <c r="M9" s="39" t="n">
-        <v>0.03968253968253969</v>
+        <v>0.02729257641921397</v>
       </c>
       <c r="N9" s="39" t="n">
-        <v>0.03875968992248062</v>
+        <v>0.02648305084745763</v>
       </c>
       <c r="O9" s="39" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.0257201646090535</v>
       </c>
       <c r="P9" s="39" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.025</v>
       </c>
       <c r="Q9" s="39" t="n">
-        <v>0.03623188405797102</v>
+        <v>0.02431906614785992</v>
       </c>
       <c r="R9" s="39" t="n">
-        <v>0.03546099290780142</v>
+        <v>0.02367424242424242</v>
       </c>
       <c r="S9" s="39" t="n">
-        <v>0.03472222222222222</v>
+        <v>0.02306273062730627</v>
       </c>
       <c r="T9" s="39" t="n">
-        <v>0.03401360544217687</v>
+        <v>0.02248201438848921</v>
       </c>
       <c r="U9" s="39" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.02192982456140351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>COO  (wt 3)</t>
+          <t>CEO  (wt 8)</t>
         </is>
       </c>
       <c r="B10" s="40" t="n">
-        <v>0.06620428751576292</v>
+        <v>0.1722017220172201</v>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0.06321493076459964</v>
+        <v>0.1599086236436322</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0.06048387096774193</v>
+        <v>0.1492537313432836</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>0.05469462169553327</v>
+        <v>0.1293451899757478</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>0.04991680532445923</v>
+        <v>0.1141226818830243</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>0.04801536491677337</v>
+        <v>0.1091703056768559</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>0.04625346901017575</v>
+        <v>0.104629871828407</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>0.0446162998215348</v>
+        <v>0.1004520341536916</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>0.04309106578569377</v>
+        <v>0.09659502535619416</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>0.04065040650406504</v>
+        <v>0.0900900900900901</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>0.03968253968253969</v>
+        <v>0.08733624454148473</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>0.03875968992248062</v>
+        <v>0.0847457627118644</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.08230452674897119</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.08</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>0.03623188405797102</v>
+        <v>0.07782101167315175</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>0.03546099290780142</v>
+        <v>0.07575757575757576</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>0.03472222222222222</v>
+        <v>0.07380073800738007</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>0.03401360544217687</v>
+        <v>0.07194244604316546</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>0.03333333333333333</v>
+        <v>0.07017543859649122</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>IR  (wt 1)</t>
+          <t>CFO  (wt 3)</t>
         </is>
       </c>
       <c r="B11" s="39" t="n">
-        <v>0.02206809583858764</v>
+        <v>0.06457564575645755</v>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.02107164358819988</v>
+        <v>0.05996573386636207</v>
       </c>
       <c r="D11" s="39" t="n">
-        <v>0.02016129032258064</v>
+        <v>0.05597014925373135</v>
       </c>
       <c r="E11" s="39" t="n">
-        <v>0.01823154056517776</v>
+        <v>0.04850444624090541</v>
       </c>
       <c r="F11" s="39" t="n">
-        <v>0.01663893510815308</v>
+        <v>0.0427960057061341</v>
       </c>
       <c r="G11" s="39" t="n">
-        <v>0.01600512163892446</v>
+        <v>0.04093886462882096</v>
       </c>
       <c r="H11" s="39" t="n">
-        <v>0.01541782300339192</v>
+        <v>0.03923620193565263</v>
       </c>
       <c r="I11" s="39" t="n">
-        <v>0.0148720999405116</v>
+        <v>0.03766951280763435</v>
       </c>
       <c r="J11" s="39" t="n">
-        <v>0.01436368859523126</v>
+        <v>0.03622313450857281</v>
       </c>
       <c r="K11" s="39" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.03488372093023256</v>
       </c>
       <c r="L11" s="39" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M11" s="39" t="n">
-        <v>0.01322751322751323</v>
+        <v>0.03275109170305677</v>
       </c>
       <c r="N11" s="39" t="n">
-        <v>0.01291989664082687</v>
+        <v>0.03177966101694915</v>
       </c>
       <c r="O11" s="39" t="n">
-        <v>0.01262626262626263</v>
+        <v>0.0308641975308642</v>
       </c>
       <c r="P11" s="39" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.03</v>
       </c>
       <c r="Q11" s="39" t="n">
-        <v>0.01207729468599034</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="R11" s="39" t="n">
-        <v>0.01182033096926714</v>
+        <v>0.02840909090909091</v>
       </c>
       <c r="S11" s="39" t="n">
-        <v>0.01157407407407407</v>
+        <v>0.02767527675276753</v>
       </c>
       <c r="T11" s="39" t="n">
-        <v>0.01133786848072562</v>
+        <v>0.02697841726618705</v>
       </c>
       <c r="U11" s="39" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Support  (wt 1)</t>
+          <t>COO  (wt 3)</t>
         </is>
       </c>
       <c r="B12" s="40" t="n">
-        <v>0.02206809583858764</v>
+        <v>0.06457564575645755</v>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0.02107164358819988</v>
+        <v>0.05996573386636207</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0.02016129032258064</v>
+        <v>0.05597014925373135</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>0.01823154056517776</v>
+        <v>0.04850444624090541</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>0.01663893510815308</v>
+        <v>0.0427960057061341</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>0.01600512163892446</v>
+        <v>0.04093886462882096</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>0.01541782300339192</v>
+        <v>0.03923620193565263</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>0.0148720999405116</v>
+        <v>0.03766951280763435</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>0.01436368859523126</v>
+        <v>0.03622313450857281</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>0.01388888888888889</v>
+        <v>0.03488372093023256</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>0.01355013550135501</v>
+        <v>0.03378378378378379</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>0.01322751322751323</v>
+        <v>0.03275109170305677</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>0.01291989664082687</v>
+        <v>0.03177966101694915</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>0.01262626262626263</v>
+        <v>0.0308641975308642</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>0.01234567901234568</v>
+        <v>0.03</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>0.01207729468599034</v>
+        <v>0.02918287937743191</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>0.01182033096926714</v>
+        <v>0.02840909090909091</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>0.01157407407407407</v>
+        <v>0.02767527675276753</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>0.01133786848072562</v>
+        <v>0.02697841726618705</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>0.01111111111111111</v>
+        <v>0.02631578947368421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>Execution  (wt 2)</t>
+          <t>IR  (wt 1)</t>
         </is>
       </c>
       <c r="B13" s="39" t="n">
-        <v>0.04413619167717528</v>
+        <v>0.02152521525215252</v>
       </c>
       <c r="C13" s="39" t="n">
-        <v>0.04214328717639976</v>
+        <v>0.01998857795545403</v>
       </c>
       <c r="D13" s="39" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.01865671641791045</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>0.03646308113035551</v>
+        <v>0.01616814874696847</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>0.03327787021630615</v>
+        <v>0.01426533523537803</v>
       </c>
       <c r="G13" s="39" t="n">
-        <v>0.03201024327784891</v>
+        <v>0.01364628820960699</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>0.03083564600678384</v>
+        <v>0.01307873397855088</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>0.0297441998810232</v>
+        <v>0.01255650426921145</v>
       </c>
       <c r="J13" s="39" t="n">
-        <v>0.02872737719046252</v>
+        <v>0.01207437816952427</v>
       </c>
       <c r="K13" s="39" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.01162790697674419</v>
       </c>
       <c r="L13" s="39" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.01126126126126126</v>
       </c>
       <c r="M13" s="39" t="n">
-        <v>0.02645502645502646</v>
+        <v>0.01091703056768559</v>
       </c>
       <c r="N13" s="39" t="n">
-        <v>0.02583979328165375</v>
+        <v>0.01059322033898305</v>
       </c>
       <c r="O13" s="39" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.0102880658436214</v>
       </c>
       <c r="P13" s="39" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.01</v>
       </c>
       <c r="Q13" s="39" t="n">
-        <v>0.02415458937198068</v>
+        <v>0.009727626459143969</v>
       </c>
       <c r="R13" s="39" t="n">
-        <v>0.02364066193853428</v>
+        <v>0.00946969696969697</v>
       </c>
       <c r="S13" s="39" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.009225092250922509</v>
       </c>
       <c r="T13" s="39" t="n">
-        <v>0.02267573696145125</v>
+        <v>0.008992805755395683</v>
       </c>
       <c r="U13" s="39" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.008771929824561403</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Risk  (wt 2)</t>
+          <t>Support  (wt 1)</t>
         </is>
       </c>
       <c r="B14" s="40" t="n">
-        <v>0.04413619167717528</v>
+        <v>0.02152521525215252</v>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0.04214328717639976</v>
+        <v>0.01998857795545403</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>0.04032258064516129</v>
+        <v>0.01865671641791045</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>0.03646308113035551</v>
+        <v>0.01616814874696847</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>0.03327787021630615</v>
+        <v>0.01426533523537803</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>0.03201024327784891</v>
+        <v>0.01364628820960699</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>0.03083564600678384</v>
+        <v>0.01307873397855088</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>0.0297441998810232</v>
+        <v>0.01255650426921145</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>0.02872737719046252</v>
+        <v>0.01207437816952427</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>0.02777777777777778</v>
+        <v>0.01162790697674419</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>0.02710027100271003</v>
+        <v>0.01126126126126126</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>0.02645502645502646</v>
+        <v>0.01091703056768559</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>0.02583979328165375</v>
+        <v>0.01059322033898305</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>0.02525252525252525</v>
+        <v>0.0102880658436214</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>0.02469135802469136</v>
+        <v>0.01</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>0.02415458937198068</v>
+        <v>0.009727626459143969</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>0.02364066193853428</v>
+        <v>0.00946969696969697</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>0.02314814814814815</v>
+        <v>0.009225092250922509</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>0.02267573696145125</v>
+        <v>0.008992805755395683</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>0.02222222222222222</v>
+        <v>0.008771929824561403</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
+          <t>Execution  (wt 2)</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="n">
+        <v>0.04305043050430504</v>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>0.03997715591090805</v>
+      </c>
+      <c r="D15" s="39" t="n">
+        <v>0.03731343283582089</v>
+      </c>
+      <c r="E15" s="39" t="n">
+        <v>0.03233629749393695</v>
+      </c>
+      <c r="F15" s="39" t="n">
+        <v>0.02853067047075606</v>
+      </c>
+      <c r="G15" s="39" t="n">
+        <v>0.02729257641921397</v>
+      </c>
+      <c r="H15" s="39" t="n">
+        <v>0.02615746795710176</v>
+      </c>
+      <c r="I15" s="39" t="n">
+        <v>0.0251130085384229</v>
+      </c>
+      <c r="J15" s="39" t="n">
+        <v>0.02414875633904854</v>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="L15" s="39" t="n">
+        <v>0.02252252252252252</v>
+      </c>
+      <c r="M15" s="39" t="n">
+        <v>0.02183406113537118</v>
+      </c>
+      <c r="N15" s="39" t="n">
+        <v>0.0211864406779661</v>
+      </c>
+      <c r="O15" s="39" t="n">
+        <v>0.0205761316872428</v>
+      </c>
+      <c r="P15" s="39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q15" s="39" t="n">
+        <v>0.01945525291828794</v>
+      </c>
+      <c r="R15" s="39" t="n">
+        <v>0.01893939393939394</v>
+      </c>
+      <c r="S15" s="39" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="T15" s="39" t="n">
+        <v>0.01798561151079137</v>
+      </c>
+      <c r="U15" s="39" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Risk  (wt 2)</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="n">
+        <v>0.04305043050430504</v>
+      </c>
+      <c r="C16" s="40" t="n">
+        <v>0.03997715591090805</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>0.03731343283582089</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>0.03233629749393695</v>
+      </c>
+      <c r="F16" s="40" t="n">
+        <v>0.02853067047075606</v>
+      </c>
+      <c r="G16" s="40" t="n">
+        <v>0.02729257641921397</v>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>0.02615746795710176</v>
+      </c>
+      <c r="I16" s="40" t="n">
+        <v>0.0251130085384229</v>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>0.02414875633904854</v>
+      </c>
+      <c r="K16" s="40" t="n">
+        <v>0.02325581395348837</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>0.02252252252252252</v>
+      </c>
+      <c r="M16" s="40" t="n">
+        <v>0.02183406113537118</v>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>0.0211864406779661</v>
+      </c>
+      <c r="O16" s="40" t="n">
+        <v>0.0205761316872428</v>
+      </c>
+      <c r="P16" s="40" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q16" s="40" t="n">
+        <v>0.01945525291828794</v>
+      </c>
+      <c r="R16" s="40" t="n">
+        <v>0.01893939393939394</v>
+      </c>
+      <c r="S16" s="40" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="T16" s="40" t="n">
+        <v>0.01798561151079137</v>
+      </c>
+      <c r="U16" s="40" t="n">
+        <v>0.01754385964912281</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
           <t>Compliance  (wt 1)</t>
         </is>
       </c>
-      <c r="B15" s="39" t="n">
-        <v>0.02206809583858764</v>
-      </c>
-      <c r="C15" s="39" t="n">
-        <v>0.02107164358819988</v>
-      </c>
-      <c r="D15" s="39" t="n">
-        <v>0.02016129032258064</v>
-      </c>
-      <c r="E15" s="39" t="n">
-        <v>0.01823154056517776</v>
-      </c>
-      <c r="F15" s="39" t="n">
-        <v>0.01663893510815308</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>0.01600512163892446</v>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>0.01541782300339192</v>
-      </c>
-      <c r="I15" s="39" t="n">
-        <v>0.0148720999405116</v>
-      </c>
-      <c r="J15" s="39" t="n">
-        <v>0.01436368859523126</v>
-      </c>
-      <c r="K15" s="39" t="n">
-        <v>0.01388888888888889</v>
-      </c>
-      <c r="L15" s="39" t="n">
-        <v>0.01355013550135501</v>
-      </c>
-      <c r="M15" s="39" t="n">
-        <v>0.01322751322751323</v>
-      </c>
-      <c r="N15" s="39" t="n">
-        <v>0.01291989664082687</v>
-      </c>
-      <c r="O15" s="39" t="n">
-        <v>0.01262626262626263</v>
-      </c>
-      <c r="P15" s="39" t="n">
-        <v>0.01234567901234568</v>
-      </c>
-      <c r="Q15" s="39" t="n">
-        <v>0.01207729468599034</v>
-      </c>
-      <c r="R15" s="39" t="n">
-        <v>0.01182033096926714</v>
-      </c>
-      <c r="S15" s="39" t="n">
-        <v>0.01157407407407407</v>
-      </c>
-      <c r="T15" s="39" t="n">
-        <v>0.01133786848072562</v>
-      </c>
-      <c r="U15" s="39" t="n">
-        <v>0.01111111111111111</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="B17" s="39" t="n">
+        <v>0.02152521525215252</v>
+      </c>
+      <c r="C17" s="39" t="n">
+        <v>0.01998857795545403</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>0.01865671641791045</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>0.01616814874696847</v>
+      </c>
+      <c r="F17" s="39" t="n">
+        <v>0.01426533523537803</v>
+      </c>
+      <c r="G17" s="39" t="n">
+        <v>0.01364628820960699</v>
+      </c>
+      <c r="H17" s="39" t="n">
+        <v>0.01307873397855088</v>
+      </c>
+      <c r="I17" s="39" t="n">
+        <v>0.01255650426921145</v>
+      </c>
+      <c r="J17" s="39" t="n">
+        <v>0.01207437816952427</v>
+      </c>
+      <c r="K17" s="39" t="n">
+        <v>0.01162790697674419</v>
+      </c>
+      <c r="L17" s="39" t="n">
+        <v>0.01126126126126126</v>
+      </c>
+      <c r="M17" s="39" t="n">
+        <v>0.01091703056768559</v>
+      </c>
+      <c r="N17" s="39" t="n">
+        <v>0.01059322033898305</v>
+      </c>
+      <c r="O17" s="39" t="n">
+        <v>0.0102880658436214</v>
+      </c>
+      <c r="P17" s="39" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q17" s="39" t="n">
+        <v>0.009727626459143969</v>
+      </c>
+      <c r="R17" s="39" t="n">
+        <v>0.00946969696969697</v>
+      </c>
+      <c r="S17" s="39" t="n">
+        <v>0.009225092250922509</v>
+      </c>
+      <c r="T17" s="39" t="n">
+        <v>0.008992805755395683</v>
+      </c>
+      <c r="U17" s="39" t="n">
+        <v>0.008771929824561403</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>Total units (denominator)</t>
         </is>
       </c>
-      <c r="B16" s="44" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="C16" s="44" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="D16" s="44" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="E16" s="44" t="n">
-        <v>54.9</v>
-      </c>
-      <c r="F16" s="44" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="G16" s="44" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="H16" s="44" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="I16" s="44" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="J16" s="44" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="K16" s="44" t="n">
-        <v>72</v>
-      </c>
-      <c r="L16" s="44" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="M16" s="44" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="N16" s="44" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="O16" s="44" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="P16" s="44" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q16" s="44" t="n">
+      <c r="B18" s="44" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="C18" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="E18" s="44" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F18" s="44" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G18" s="44" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="H18" s="44" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="I18" s="44" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="J18" s="44" t="n">
         <v>82.8</v>
       </c>
-      <c r="R16" s="44" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="S16" s="44" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="T16" s="44" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="U16" s="44" t="n">
-        <v>90</v>
+      <c r="K18" s="44" t="n">
+        <v>86</v>
+      </c>
+      <c r="L18" s="44" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="M18" s="44" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="N18" s="44" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="O18" s="44" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="P18" s="44" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q18" s="44" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="R18" s="44" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="S18" s="44" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="T18" s="44" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="U18" s="44" t="n">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Static" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Take by AUM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Take per Person" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Profit Simulation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +81,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -122,8 +123,13 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +151,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -269,6 +319,59 @@
     <xf numFmtId="165" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -347,7 +450,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -851,7 +953,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1353,6 +1454,287 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Firm EBIT by AUM level (millions)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Profit Simulation'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Profit Simulation'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profit Simulation'!$B$14:$G$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Profit to each owner (millions)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Profit Simulation'!A18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profit Simulation'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profit Simulation'!$B$18:$G$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Profit Simulation'!A19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profit Simulation'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profit Simulation'!$B$19:$G$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Profit Simulation'!A20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profit Simulation'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profit Simulation'!$B$20:$G$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Profit Simulation'!A21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Profit Simulation'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Profit Simulation'!$B$21:$G$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>millions</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1399,6 +1781,55 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1741,6 +2172,10 @@
           <t>Performance-fee rate (of profits)</t>
         </is>
       </c>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="45" t="n"/>
+      <c r="D5" s="45" t="n"/>
+      <c r="E5" s="46" t="n"/>
       <c r="F5" s="5" t="n">
         <v>0.2</v>
       </c>
@@ -1751,6 +2186,10 @@
           <t>Firm take rate — share of perf-fee to the comp pool</t>
         </is>
       </c>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="45" t="n"/>
+      <c r="E6" s="46" t="n"/>
       <c r="F6" s="5" t="n">
         <v>0.6</v>
       </c>
@@ -1761,6 +2200,10 @@
           <t>Assumed gross return on AUM</t>
         </is>
       </c>
+      <c r="B7" s="45" t="n"/>
+      <c r="C7" s="45" t="n"/>
+      <c r="D7" s="45" t="n"/>
+      <c r="E7" s="46" t="n"/>
       <c r="F7" s="5" t="n">
         <v>0.12</v>
       </c>
@@ -1771,6 +2214,10 @@
           <t>Management fee (of AUM)</t>
         </is>
       </c>
+      <c r="B8" s="45" t="n"/>
+      <c r="C8" s="45" t="n"/>
+      <c r="D8" s="45" t="n"/>
+      <c r="E8" s="46" t="n"/>
       <c r="F8" s="5" t="n">
         <v>0.015</v>
       </c>
@@ -1781,6 +2228,10 @@
           <t>AUM tier threshold (millions)</t>
         </is>
       </c>
+      <c r="B9" s="45" t="n"/>
+      <c r="C9" s="45" t="n"/>
+      <c r="D9" s="45" t="n"/>
+      <c r="E9" s="46" t="n"/>
       <c r="F9" s="6" t="n">
         <v>300</v>
       </c>
@@ -1791,6 +2242,10 @@
           <t>Employer cost loading on salary</t>
         </is>
       </c>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="45" t="n"/>
+      <c r="E10" s="46" t="n"/>
       <c r="F10" s="7" t="n">
         <v>1.62</v>
       </c>
@@ -6291,4 +6746,608 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>Profit simulation by AUM level, with ownership distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Firm EBIT = management fee + equity take (40% of perf fee) − operating costs. Distributed to owners. Millions; links to Static.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>P&amp;L line  (millions)</t>
+        </is>
+      </c>
+      <c r="H4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $20m</t>
+        </is>
+      </c>
+      <c r="I4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $300m</t>
+        </is>
+      </c>
+      <c r="J4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $500m</t>
+        </is>
+      </c>
+      <c r="K4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $1,000m</t>
+        </is>
+      </c>
+      <c r="L4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $2,000m</t>
+        </is>
+      </c>
+      <c r="M4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $5,000m</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>AUM</t>
+        </is>
+      </c>
+      <c r="H5" s="50">
+        <f>Static!H15</f>
+        <v/>
+      </c>
+      <c r="I5" s="50">
+        <f>Static!I15</f>
+        <v/>
+      </c>
+      <c r="J5" s="50">
+        <f>Static!J15</f>
+        <v/>
+      </c>
+      <c r="K5" s="50">
+        <f>Static!K15</f>
+        <v/>
+      </c>
+      <c r="L5" s="50">
+        <f>Static!L15</f>
+        <v/>
+      </c>
+      <c r="M5" s="50">
+        <f>Static!M15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Management fee  (1.5% × AUM)</t>
+        </is>
+      </c>
+      <c r="H6" s="51">
+        <f>Static!H15*Static!$F$8</f>
+        <v/>
+      </c>
+      <c r="I6" s="51">
+        <f>Static!I15*Static!$F$8</f>
+        <v/>
+      </c>
+      <c r="J6" s="51">
+        <f>Static!J15*Static!$F$8</f>
+        <v/>
+      </c>
+      <c r="K6" s="51">
+        <f>Static!K15*Static!$F$8</f>
+        <v/>
+      </c>
+      <c r="L6" s="51">
+        <f>Static!L15*Static!$F$8</f>
+        <v/>
+      </c>
+      <c r="M6" s="51">
+        <f>Static!M15*Static!$F$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Performance fee  (20% × profit)</t>
+        </is>
+      </c>
+      <c r="H7" s="51">
+        <f>Static!H15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+      <c r="I7" s="51">
+        <f>Static!I15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+      <c r="J7" s="51">
+        <f>Static!J15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+      <c r="K7" s="51">
+        <f>Static!K15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+      <c r="L7" s="51">
+        <f>Static!L15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+      <c r="M7" s="51">
+        <f>Static!M15*Static!$F$7*Static!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which team take (60%) → staff</t>
+        </is>
+      </c>
+      <c r="H8" s="53">
+        <f>H7*Static!$F$6</f>
+        <v/>
+      </c>
+      <c r="I8" s="53">
+        <f>I7*Static!$F$6</f>
+        <v/>
+      </c>
+      <c r="J8" s="53">
+        <f>J7*Static!$F$6</f>
+        <v/>
+      </c>
+      <c r="K8" s="53">
+        <f>K7*Static!$F$6</f>
+        <v/>
+      </c>
+      <c r="L8" s="53">
+        <f>L7*Static!$F$6</f>
+        <v/>
+      </c>
+      <c r="M8" s="53">
+        <f>M7*Static!$F$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which equity take (40%) → firm</t>
+        </is>
+      </c>
+      <c r="H9" s="51">
+        <f>H7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+      <c r="I9" s="51">
+        <f>I7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+      <c r="J9" s="51">
+        <f>J7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+      <c r="K9" s="51">
+        <f>K7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+      <c r="L9" s="51">
+        <f>L7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+      <c r="M9" s="51">
+        <f>M7*(1-Static!$F$6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Firm revenue  (mgmt fee + equity take)</t>
+        </is>
+      </c>
+      <c r="H10" s="54">
+        <f>H6+H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="54">
+        <f>I6+I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="54">
+        <f>J6+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="54">
+        <f>K6+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="54">
+        <f>L6+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="54">
+        <f>M6+M9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Operating cost: loaded salaries</t>
+        </is>
+      </c>
+      <c r="H11" s="51">
+        <f>Static!H36</f>
+        <v/>
+      </c>
+      <c r="I11" s="51">
+        <f>Static!I36</f>
+        <v/>
+      </c>
+      <c r="J11" s="51">
+        <f>Static!J36</f>
+        <v/>
+      </c>
+      <c r="K11" s="51">
+        <f>Static!K36</f>
+        <v/>
+      </c>
+      <c r="L11" s="51">
+        <f>Static!L36</f>
+        <v/>
+      </c>
+      <c r="M11" s="51">
+        <f>Static!M36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>Operating cost: other costs</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I12" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K12" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="56" t="n">
+        <v>4.301</v>
+      </c>
+      <c r="M12" s="56" t="n">
+        <v>4.301</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>Total operating costs</t>
+        </is>
+      </c>
+      <c r="H13" s="58">
+        <f>H11+H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="58">
+        <f>I11+I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="58">
+        <f>J11+J12</f>
+        <v/>
+      </c>
+      <c r="K13" s="58">
+        <f>K11+K12</f>
+        <v/>
+      </c>
+      <c r="L13" s="58">
+        <f>L11+L12</f>
+        <v/>
+      </c>
+      <c r="M13" s="58">
+        <f>M11+M12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>EBIT  (profit to owners)</t>
+        </is>
+      </c>
+      <c r="H14" s="59">
+        <f>H10-H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="59">
+        <f>I10-I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="59">
+        <f>J10-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="59">
+        <f>K10-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="59">
+        <f>L10-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="59">
+        <f>M10-M13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="inlineStr">
+        <is>
+          <t>EBIT margin (on firm revenue)</t>
+        </is>
+      </c>
+      <c r="H15" s="60">
+        <f>IF(H10=0,0,H14/H10)</f>
+        <v/>
+      </c>
+      <c r="I15" s="60">
+        <f>IF(I10=0,0,I14/I10)</f>
+        <v/>
+      </c>
+      <c r="J15" s="60">
+        <f>IF(J10=0,0,J14/J10)</f>
+        <v/>
+      </c>
+      <c r="K15" s="60">
+        <f>IF(K10=0,0,K14/K10)</f>
+        <v/>
+      </c>
+      <c r="L15" s="60">
+        <f>IF(L10=0,0,L14/L10)</f>
+        <v/>
+      </c>
+      <c r="M15" s="60">
+        <f>IF(M10=0,0,M14/M10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Ownership distribution of EBIT</t>
+        </is>
+      </c>
+      <c r="H17" s="49" t="inlineStr"/>
+      <c r="I17" s="49" t="inlineStr"/>
+      <c r="J17" s="49" t="inlineStr"/>
+      <c r="K17" s="49" t="inlineStr"/>
+      <c r="L17" s="49" t="inlineStr"/>
+      <c r="M17" s="49" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>CIO</t>
+        </is>
+      </c>
+      <c r="G18" s="61" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H18" s="62">
+        <f>H14*$G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="62">
+        <f>I14*$G18</f>
+        <v/>
+      </c>
+      <c r="J18" s="62">
+        <f>J14*$G18</f>
+        <v/>
+      </c>
+      <c r="K18" s="62">
+        <f>K14*$G18</f>
+        <v/>
+      </c>
+      <c r="L18" s="62">
+        <f>L14*$G18</f>
+        <v/>
+      </c>
+      <c r="M18" s="62">
+        <f>M14*$G18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Portfolio Manager 1</t>
+        </is>
+      </c>
+      <c r="G19" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" s="51">
+        <f>H14*$G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="51">
+        <f>I14*$G19</f>
+        <v/>
+      </c>
+      <c r="J19" s="51">
+        <f>J14*$G19</f>
+        <v/>
+      </c>
+      <c r="K19" s="51">
+        <f>K14*$G19</f>
+        <v/>
+      </c>
+      <c r="L19" s="51">
+        <f>L14*$G19</f>
+        <v/>
+      </c>
+      <c r="M19" s="51">
+        <f>M14*$G19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Portfolio Manager 2</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="62">
+        <f>H14*$G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="62">
+        <f>I14*$G20</f>
+        <v/>
+      </c>
+      <c r="J20" s="62">
+        <f>J14*$G20</f>
+        <v/>
+      </c>
+      <c r="K20" s="62">
+        <f>K14*$G20</f>
+        <v/>
+      </c>
+      <c r="L20" s="62">
+        <f>L14*$G20</f>
+        <v/>
+      </c>
+      <c r="M20" s="62">
+        <f>M14*$G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Other owners</t>
+        </is>
+      </c>
+      <c r="G21" s="61" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="H21" s="51">
+        <f>H14*$G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="51">
+        <f>I14*$G21</f>
+        <v/>
+      </c>
+      <c r="J21" s="51">
+        <f>J14*$G21</f>
+        <v/>
+      </c>
+      <c r="K21" s="51">
+        <f>K14*$G21</f>
+        <v/>
+      </c>
+      <c r="L21" s="51">
+        <f>L14*$G21</f>
+        <v/>
+      </c>
+      <c r="M21" s="51">
+        <f>M14*$G21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Total distributed</t>
+        </is>
+      </c>
+      <c r="G22" s="63">
+        <f>SUM(G18:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="54">
+        <f>SUM(H18:H21)</f>
+        <v/>
+      </c>
+      <c r="I22" s="54">
+        <f>SUM(I18:I21)</f>
+        <v/>
+      </c>
+      <c r="J22" s="54">
+        <f>SUM(J18:J21)</f>
+        <v/>
+      </c>
+      <c r="K22" s="54">
+        <f>SUM(K18:K21)</f>
+        <v/>
+      </c>
+      <c r="L22" s="54">
+        <f>SUM(L18:L21)</f>
+        <v/>
+      </c>
+      <c r="M22" s="54">
+        <f>SUM(M18:M21)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Performance_Fee_Framework.xlsx
+++ b/Performance_Fee_Framework.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Take by AUM" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Take per Person" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Profit Simulation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Owner Total Comp" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,6 +80,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="10">
@@ -199,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -370,6 +376,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1735,6 +1754,112 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Total comp: CIO vs PM (each), by AUM (millions)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Owner Total Comp'!A9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Owner Total Comp'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Owner Total Comp'!$B$9:$G$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Owner Total Comp'!A14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Owner Total Comp'!$H$4:$M$4</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Owner Total Comp'!$B$14:$G$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1830,6 +1955,33 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -7350,4 +7502,540 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="47" t="inlineStr">
+        <is>
+          <t>Total compensation for equity owners — CIO and the two PMs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Total comp = base salary + performance take (weight × unit value) + equity distribution (ownership × EBIT). Millions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Component  (millions)</t>
+        </is>
+      </c>
+      <c r="H4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $20m</t>
+        </is>
+      </c>
+      <c r="I4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $300m</t>
+        </is>
+      </c>
+      <c r="J4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $500m</t>
+        </is>
+      </c>
+      <c r="K4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $1,000m</t>
+        </is>
+      </c>
+      <c r="L4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $2,000m</t>
+        </is>
+      </c>
+      <c r="M4" s="49" t="inlineStr">
+        <is>
+          <t>AUM $5,000m</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>CIO  (wt 16, equity 63.6%)</t>
+        </is>
+      </c>
+      <c r="H5" s="65" t="inlineStr"/>
+      <c r="I5" s="65" t="inlineStr"/>
+      <c r="J5" s="65" t="inlineStr"/>
+      <c r="K5" s="65" t="inlineStr"/>
+      <c r="L5" s="65" t="inlineStr"/>
+      <c r="M5" s="65" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base salary</t>
+        </is>
+      </c>
+      <c r="H6" s="51">
+        <f>IF(Static!H15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+      <c r="I6" s="51">
+        <f>IF(Static!I15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+      <c r="J6" s="51">
+        <f>IF(Static!J15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+      <c r="K6" s="51">
+        <f>IF(Static!K15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+      <c r="L6" s="51">
+        <f>IF(Static!L15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+      <c r="M6" s="51">
+        <f>IF(Static!M15&lt;Static!$F$9,Static!$B$21,Static!$C$21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Performance take  (weight × unit value)</t>
+        </is>
+      </c>
+      <c r="H7" s="51">
+        <f>Static!$D$21*Static!H$35</f>
+        <v/>
+      </c>
+      <c r="I7" s="51">
+        <f>Static!$D$21*Static!I$35</f>
+        <v/>
+      </c>
+      <c r="J7" s="51">
+        <f>Static!$D$21*Static!J$35</f>
+        <v/>
+      </c>
+      <c r="K7" s="51">
+        <f>Static!$D$21*Static!K$35</f>
+        <v/>
+      </c>
+      <c r="L7" s="51">
+        <f>Static!$D$21*Static!L$35</f>
+        <v/>
+      </c>
+      <c r="M7" s="51">
+        <f>Static!$D$21*Static!M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equity distribution  (63.6% × EBIT)</t>
+        </is>
+      </c>
+      <c r="G8" s="61" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H8" s="66">
+        <f>'Profit Simulation'!H14*$G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="66">
+        <f>'Profit Simulation'!I14*$G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="66">
+        <f>'Profit Simulation'!J14*$G8</f>
+        <v/>
+      </c>
+      <c r="K8" s="66">
+        <f>'Profit Simulation'!K14*$G8</f>
+        <v/>
+      </c>
+      <c r="L8" s="66">
+        <f>'Profit Simulation'!L14*$G8</f>
+        <v/>
+      </c>
+      <c r="M8" s="66">
+        <f>'Profit Simulation'!M14*$G8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL COMP — CIO</t>
+        </is>
+      </c>
+      <c r="H9" s="54">
+        <f>SUM(H6:H8)</f>
+        <v/>
+      </c>
+      <c r="I9" s="54">
+        <f>SUM(I6:I8)</f>
+        <v/>
+      </c>
+      <c r="J9" s="54">
+        <f>SUM(J6:J8)</f>
+        <v/>
+      </c>
+      <c r="K9" s="54">
+        <f>SUM(K6:K8)</f>
+        <v/>
+      </c>
+      <c r="L9" s="54">
+        <f>SUM(L6:L8)</f>
+        <v/>
+      </c>
+      <c r="M9" s="54">
+        <f>SUM(M6:M8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="64" t="inlineStr">
+        <is>
+          <t>Portfolio Manager 1  (wt 8, equity 10.0%)</t>
+        </is>
+      </c>
+      <c r="H11" s="65" t="inlineStr"/>
+      <c r="I11" s="65" t="inlineStr"/>
+      <c r="J11" s="65" t="inlineStr"/>
+      <c r="K11" s="65" t="inlineStr"/>
+      <c r="L11" s="65" t="inlineStr"/>
+      <c r="M11" s="65" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base salary</t>
+        </is>
+      </c>
+      <c r="H12" s="51">
+        <f>IF(Static!H15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="I12" s="51">
+        <f>IF(Static!I15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="J12" s="51">
+        <f>IF(Static!J15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="K12" s="51">
+        <f>IF(Static!K15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L12" s="51">
+        <f>IF(Static!L15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="M12" s="51">
+        <f>IF(Static!M15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Performance take  (weight × unit value)</t>
+        </is>
+      </c>
+      <c r="H13" s="51">
+        <f>Static!$D$22*Static!H$35</f>
+        <v/>
+      </c>
+      <c r="I13" s="51">
+        <f>Static!$D$22*Static!I$35</f>
+        <v/>
+      </c>
+      <c r="J13" s="51">
+        <f>Static!$D$22*Static!J$35</f>
+        <v/>
+      </c>
+      <c r="K13" s="51">
+        <f>Static!$D$22*Static!K$35</f>
+        <v/>
+      </c>
+      <c r="L13" s="51">
+        <f>Static!$D$22*Static!L$35</f>
+        <v/>
+      </c>
+      <c r="M13" s="51">
+        <f>Static!$D$22*Static!M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equity distribution  (10.0% × EBIT)</t>
+        </is>
+      </c>
+      <c r="G14" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="66">
+        <f>'Profit Simulation'!H14*$G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="66">
+        <f>'Profit Simulation'!I14*$G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="66">
+        <f>'Profit Simulation'!J14*$G14</f>
+        <v/>
+      </c>
+      <c r="K14" s="66">
+        <f>'Profit Simulation'!K14*$G14</f>
+        <v/>
+      </c>
+      <c r="L14" s="66">
+        <f>'Profit Simulation'!L14*$G14</f>
+        <v/>
+      </c>
+      <c r="M14" s="66">
+        <f>'Profit Simulation'!M14*$G14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL COMP — Portfolio Manager 1</t>
+        </is>
+      </c>
+      <c r="H15" s="54">
+        <f>SUM(H12:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="54">
+        <f>SUM(I12:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="54">
+        <f>SUM(J12:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="54">
+        <f>SUM(K12:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="54">
+        <f>SUM(L12:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="54">
+        <f>SUM(M12:M14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>Portfolio Manager 2  (wt 8, equity 10.0%)</t>
+        </is>
+      </c>
+      <c r="H17" s="65" t="inlineStr"/>
+      <c r="I17" s="65" t="inlineStr"/>
+      <c r="J17" s="65" t="inlineStr"/>
+      <c r="K17" s="65" t="inlineStr"/>
+      <c r="L17" s="65" t="inlineStr"/>
+      <c r="M17" s="65" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Base salary</t>
+        </is>
+      </c>
+      <c r="H18" s="51">
+        <f>IF(Static!H15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="I18" s="51">
+        <f>IF(Static!I15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="J18" s="51">
+        <f>IF(Static!J15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="K18" s="51">
+        <f>IF(Static!K15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="L18" s="51">
+        <f>IF(Static!L15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+      <c r="M18" s="51">
+        <f>IF(Static!M15&lt;Static!$F$9,Static!$B$22,Static!$C$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Performance take  (weight × unit value)</t>
+        </is>
+      </c>
+      <c r="H19" s="51">
+        <f>Static!$D$22*Static!H$35</f>
+        <v/>
+      </c>
+      <c r="I19" s="51">
+        <f>Static!$D$22*Static!I$35</f>
+        <v/>
+      </c>
+      <c r="J19" s="51">
+        <f>Static!$D$22*Static!J$35</f>
+        <v/>
+      </c>
+      <c r="K19" s="51">
+        <f>Static!$D$22*Static!K$35</f>
+        <v/>
+      </c>
+      <c r="L19" s="51">
+        <f>Static!$D$22*Static!L$35</f>
+        <v/>
+      </c>
+      <c r="M19" s="51">
+        <f>Static!$D$22*Static!M$35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equity distribution  (10.0% × EBIT)</t>
+        </is>
+      </c>
+      <c r="G20" s="61" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="66">
+        <f>'Profit Simulation'!H14*$G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="66">
+        <f>'Profit Simulation'!I14*$G20</f>
+        <v/>
+      </c>
+      <c r="J20" s="66">
+        <f>'Profit Simulation'!J14*$G20</f>
+        <v/>
+      </c>
+      <c r="K20" s="66">
+        <f>'Profit Simulation'!K14*$G20</f>
+        <v/>
+      </c>
+      <c r="L20" s="66">
+        <f>'Profit Simulation'!L14*$G20</f>
+        <v/>
+      </c>
+      <c r="M20" s="66">
+        <f>'Profit Simulation'!M14*$G20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL COMP — Portfolio Manager 2</t>
+        </is>
+      </c>
+      <c r="H21" s="54">
+        <f>SUM(H18:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="54">
+        <f>SUM(I18:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="54">
+        <f>SUM(J18:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="54">
+        <f>SUM(K18:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="54">
+        <f>SUM(L18:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="54">
+        <f>SUM(M18:M20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>Both PMs combined (equity 20%)</t>
+        </is>
+      </c>
+      <c r="H23" s="68">
+        <f>H13*2</f>
+        <v/>
+      </c>
+      <c r="I23" s="68">
+        <f>I13*2</f>
+        <v/>
+      </c>
+      <c r="J23" s="68">
+        <f>J13*2</f>
+        <v/>
+      </c>
+      <c r="K23" s="68">
+        <f>K13*2</f>
+        <v/>
+      </c>
+      <c r="L23" s="68">
+        <f>L13*2</f>
+        <v/>
+      </c>
+      <c r="M23" s="68">
+        <f>M13*2</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>